--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-09T14:13:30+00:00</t>
+          <t>2026-01-10T04:04:15+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282081.222461.1.aa27d5a4cff39529aed6b77e05a4f515",
-  "updated_at": "2026-01-09T14:13:30.494741+00:00",
-  "pages_done": 100,
-  "tenders_scanned": 10000,
-  "tenders_fetched": 10000,
-  "milk_tenders": 101,
-  "milk_items": 105
+  "offset": "1478282201.539197.1.a66672a13d1cb6ac87a6aa2598195569",
+  "updated_at": "2026-01-10T04:04:14.647870+00:00",
+  "pages_done": 125,
+  "tenders_scanned": 12500,
+  "tenders_fetched": 12500,
+  "milk_tenders": 105,
+  "milk_items": 109
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7323,6 +7323,218 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bf560e6205534e159a359e2f44638f6e</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7c1701269f544ed18f34fbbe83962e7e</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10.51.1 Молоко та вершки, рідинні, оброблені (10.51.11-42.00 молоко)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:07.272506+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>e8354bf0d23b4ff58d9492de3d537b95</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>e5433dcde8634970a4e277c9342e3100</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Молоко та вершки рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:29.388767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3ad3c0ec445a459f905c9e566cccfdda</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>9ac2fc11687f4b1ea971ff04d5906b12</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Молоко питне ультрапастеризоване за кодом ДК 016:2010 – 10.51.1- «Молоко та вершки, рідинні, оброблені»</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>4495</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:37.273894+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9373b16c10bc4c89b1a584fba7054422</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bdf926b898d7446fa918f262fc1f2e16</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.	Кава у зернах, 500 гр	30 	шт 2.	Цукор пресований у кубиках (500 г)	10 	шт 3.	 Вершки сухі для напоїв Coffee-mate, 400 гр.	10 	шт 4.	Серветки столові білі, одношарові, в упаковці 500 штук	10 	шт 5.	 Чай зелений Greenfield Flying Dragon, в упаковці 100 пак.	5 	шт 6.	 Чай чорний Greenfield Golden Ceylon, в упаковці 100 пак.	5 	шт 7.	Цукор-пісок, 1 кг	10 	шт 8.	Палички для розмішування напоїв, в упаковці 1000 шт.	5  	шт</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>15860000-4</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>85</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2015-08-10T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2015-08-11T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Київськая</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:11.256963+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7334,7 +7546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12744,6 +12956,218 @@
       <c r="K102" t="inlineStr">
         <is>
           <t>2026-01-09T14:12:54.405696+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bf560e6205534e159a359e2f44638f6e</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>UA-2015-07-07-000020</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:07.272506+02:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ "Донбаська електроенергетична система" ДП "НЕК "Укренерго"</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>23344104</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>20160</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:03:23.262021+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>e8354bf0d23b4ff58d9492de3d537b95</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UA-2015-07-14-000086</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:29.388767+02:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ДП "Київська міська дирекція УДППЗ "Укрпошта""</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01189979</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:03:23.262021+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3ad3c0ec445a459f905c9e566cccfdda</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UA-2015-07-17-000044</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:37.273894+02:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Білгород-Дністровська філія державного підпириємства "Адміністрація морських портів України" (адміністрація Білгород-Дністровського морського порту)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>38728376</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>24497.75</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:03:23.262021+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9373b16c10bc4c89b1a584fba7054422</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UA-2015-07-28-000156</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:11.256963+02:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ДП "УКРІНТЕРАВТОСЕРВІС"</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>21536845</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:03:23.262021+00:00</t>
         </is>
       </c>
     </row>
@@ -12758,7 +13182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12919,6 +13343,164 @@
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-09T14:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{"bytes": 39861}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-10T04:04:15+00:00</t>
+          <t>2026-01-11T04:18:58+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282201.539197.1.a66672a13d1cb6ac87a6aa2598195569",
-  "updated_at": "2026-01-10T04:04:14.647870+00:00",
-  "pages_done": 125,
-  "tenders_scanned": 12500,
-  "tenders_fetched": 12500,
-  "milk_tenders": 105,
-  "milk_items": 109
+  "offset": "1478282349.043586.1.d0a1099efcee93f25a6d54a870cbb3fb",
+  "updated_at": "2026-01-11T04:18:58.154506+00:00",
+  "pages_done": 150,
+  "tenders_scanned": 15000,
+  "tenders_fetched": 15000,
+  "milk_tenders": 122,
+  "milk_items": 126
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7535,6 +7535,883 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>916a88cc63914fccb0b4f64c30c21448</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>94a4eff26f8d41e2ac8176da6a026476</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>молоко коров’яче питне пастеризоване жирністю 2,5% (код 10.51.1 згідно ДК 016-2010 Молоко та вершки рідинні, оброблені)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2015-12-27T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:54.645091+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ca282f2cafb64b7eb7bfd9c7444729e9</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>d6b5655ca6c3436e9ed14ef3a5100c9b</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>«Молоко та вершки, рідинні, оброблені» (молоко).</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2015-09-20T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:56.948559+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0501d112b17740179b6dfe222d741b2f</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>d8276df064874ad99ad611a109b11e40</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Молоко фас 1 літр п/е, 2.5%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2015-08-24T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:59.231733+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9cc032b602cc46e6b2d6d2837ea41dba</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>f366ed4468884fe3913bf24ab5e82124</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ДНЕПРОПЕТРОВСКАЯ ОБЛ.</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:06.394159+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9407598a5564447381e1ee10856e3668</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>6fa3b4421be64b31be89a1707220e910</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен 1 л</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>600</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.626309+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>b4e8d08a57e848238c6cc2cca30bf223</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ad13743cfee3465fbbb6abde5a77ef53</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен 1 л</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>600</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.814561+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0161f1d8ae954179af635e147f4cbf74</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>606b65025a6f466c87d663620629c54e</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Молоко 3,2 % пастеризоване поліетилен 0,5 л</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>600</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.478429+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>dff9746856564cd2b249d8612a56fa43</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>17748e8984184102b9e14950a033c317</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % пастеризоване поліетилен  1 л</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>450</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.624524+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>eeea13766d6b49c2b30087060f6573e3</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>12af1eef216343a4ad29a76a14122b4d</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен  0,5 л</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2082</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:34.294837+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>89c1f871adc44165a78dec1a036dc3db</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5971f193a4214591b2bd526f1465b812</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен  0,5 л</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>3920</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:37.074563+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20fc3534a32e4e98a37e1fc41ce4adb8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4b49b8426886471a89bcf13d76ec9d9b</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2.7% 500г.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1102</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:42.706161+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>c9a4c99b475342b1b3e707cafd1feea3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>c3cef331746e42af9d3dc2024028f064</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>молоко 2,5 % жир.(10.51.11-42.00)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>22360</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:04.492396+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>fca11035a4d742b1b9efb53c84254420</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>d70a355ef0c048b4b14b06b3a69894c6</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:21.863187+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>05b4cac24a3d43bf95917a444541ba85</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6b50aa94de2045a09f7f008672b70b78</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>молоко сухе знежирене</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>500</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2015-11-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2015-11-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:34.794793+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>8aea2333476c49ef8249f9cf7208fc80</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>be7fb4b2a8e347399d423d1926f86cf2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Молоко 2,6 % жирность ДСТУ 2661-94</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>42000000-6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ХАРЬКОВСКАЯ ОБЛ.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Харьков</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:39.134971+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>fb24e47fbd424063be7640428411abca</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>a214e419e3b74caf95a6393467937c83</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Молоко тривалого зберігання 2,6% 1 л</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>65</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.100157+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>a87b459aa61d4bb0876a8f142170b2bb</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6d90ce275da046bca5a0e9412e15dea3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>молоко жирність 2,6% плівка по 1л</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2015-09-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.363048+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7546,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13168,6 +14045,907 @@
       <c r="K106" t="inlineStr">
         <is>
           <t>2026-01-10T04:03:23.262021+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>916a88cc63914fccb0b4f64c30c21448</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UA-2015-08-10-000028</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:54.645091+02:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ВП ХАЕС ДП "НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>21313677</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>92700</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ca282f2cafb64b7eb7bfd9c7444729e9</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UA-2015-08-11-000019</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:56.948559+02:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ВП Запорізька АЕС ДП НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>19355964</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>31486</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0501d112b17740179b6dfe222d741b2f</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UA-2015-08-11-000073</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:59.231733+02:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна лікарня № 2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>05415941</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>99750</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9cc032b602cc46e6b2d6d2837ea41dba</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UA-2015-08-12-000118</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:06.394159+02:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>20500</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9407598a5564447381e1ee10856e3668</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UA-2015-08-14-000057</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.626309+02:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>b4e8d08a57e848238c6cc2cca30bf223</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UA-2015-08-14-000061</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.814561+02:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0161f1d8ae954179af635e147f4cbf74</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000071</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.478429+02:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>3360</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>dff9746856564cd2b249d8612a56fa43</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000078</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.624524+02:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>8280</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>eeea13766d6b49c2b30087060f6573e3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000102</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:34.294837+02:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>9993.6</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>89c1f871adc44165a78dec1a036dc3db</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UA-2015-08-20-000066</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:37.074563+02:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>19992</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20fc3534a32e4e98a37e1fc41ce4adb8</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UA-2015-08-21-000105</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:42.706161+02:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>6820</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>c9a4c99b475342b1b3e707cafd1feea3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UA-2015-08-28-000048</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:04.492396+02:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Київський національний університет імені Тараса Шевченка</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>02070944</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>178880</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>fca11035a4d742b1b9efb53c84254420</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UA-2015-09-01-000137</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:21.863187+02:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>КМКЛ № 4</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>30212155</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>28800</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>05b4cac24a3d43bf95917a444541ba85</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UA-2015-09-03-000113</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:34.794793+02:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>відокремлений підрозділ „Рівненська АЕС” державного підприємства   „Національна атомна енергогенеруюча компанія “Енергоатом”</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>05425046</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>8aea2333476c49ef8249f9cf7208fc80</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UA-2015-09-04-000028</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:39.134971+02:00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Український державний центр по експлуатації спеціалізованих вагонів"</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01056362</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>368000</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>fb24e47fbd424063be7640428411abca</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UA-2015-09-08-000196</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.100157+02:00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>806</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>a87b459aa61d4bb0876a8f142170b2bb</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UA-2015-09-08-000199</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.363048+02:00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>46800</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:19.183418+00:00</t>
         </is>
       </c>
     </row>
@@ -13182,7 +14960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13501,6 +15279,164 @@
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-10T04:04:15+00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{"bytes": 41407}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-11T04:18:58+00:00</t>
+          <t>2026-01-12T04:20:03+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282349.043586.1.d0a1099efcee93f25a6d54a870cbb3fb",
-  "updated_at": "2026-01-11T04:18:58.154506+00:00",
-  "pages_done": 150,
-  "tenders_scanned": 15000,
-  "tenders_fetched": 15000,
-  "milk_tenders": 122,
-  "milk_items": 126
+  "offset": "1478282499.303665.1.02997663a538d93c316c3093058128e8",
+  "updated_at": "2026-01-12T04:20:03.320708+00:00",
+  "pages_done": 175,
+  "tenders_scanned": 17500,
+  "tenders_fetched": 17500,
+  "milk_tenders": 135,
+  "milk_items": 140
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8412,6 +8412,862 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>fb1093c1aeab497c81d927bbd9d38540</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7a36d4d9884143de8732c09da779c22c</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Скло предметне з полем для запису 1 мм
+Скло предметне 2 мм
+Скло предметне25,4х76,2з шліф краєм 
+Піпетка до ШОЕ-метру (капіляр Панченкова)
+Пiпетка Пастера  3мл поліетиленова  стерильна
+PW297Лінійка для вимірювання зон затримки росту</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>14820000-5</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>6152</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2015-09-27T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:17.543930+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>07131640926148bdbaf4b7b763911360</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>f1e0e8a3006345c0be0a3d795a5d5065</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Молоко 2.5 %, 1 л</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2015-09-15T18:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2015-09-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:19.440248+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>42e4042644864375b9011dec999d40fa</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>088f685ddf634a43862edf456708c8b1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Молоко пастерізоване жирністю до 2,5%включно. Місце поставкі - м.Київ, вул.Волинська,21. Надання всіх установчих документів ві "Постачальника", сертифікатів качества на продукцію. Наявність холодільного устаткування для перевезення продуктів харчування. Склад "Постачальника" повинен бути розташованим в м.Києві.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1201</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2015-10-01T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:46.253275+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cdb4b46524444ee5a37ea3f976d152b5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0d31e63121c54817bf131b65f6d42af0</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>молоко жирність 2,5% плівка по 1 л</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:03.079468+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>fd43e8f669164cbab24619fba05910b2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>4e6715a5af4449eaa55db65f31e7df7d</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Молоко з умістом жиру не більше 2,6% неконцентроване</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>м.Котовськ</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:22.508365+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>48bb6d4d96b6491e84622c5bc31bb971</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>87dfd26d542d4e43887cc19f84e7c318</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Молоко сгущене</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>15551000-5</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>50</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>м.Котовськ</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.202533+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3ef311379a1744b99e0fde2008c05644</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>d95238687e324ae0a9f1e70627e171db</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Детальний опис предмета закупівлі визначено в оголошенні (додається)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>2870</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Херсонська</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.527835+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>c0d950569a254da99898b8a3cfe61a93</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0b4789d34df94f2a898fa07134454227</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - плівка по 1 л.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>800</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2015-09-30T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2015-12-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:03.782027+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>6bd5210dca3c4c78ac25a3d7e4c7d5c5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>def22b77408947b985761d8818fbfb64</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Фасовка - банка бляшана, маса 380г, молоко згущене з цукром 8,5%, ДСТУ 4274:2003 Продукція повинна мати сертифікат відповідності.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2015-10-08T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.562834+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ebeccf44d28348a682a78050eea66eba</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>a2aefd913ffd44dc83f229b928d73c7c</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>молоко ультрапастеризоване</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>192</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2015-10-15T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2015-10-22T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.618438+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>db000ae876f24652b49f134d5e88a041</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>e0a62917e3694820ab255a46169065e4</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1. Виготовлення листівки для школи, формат: А2, офсетний тип друку; кольоровість: Pantone Black + Pantone 802; рекомендований матеріал: папір munken print cream 150 г/м2 (альтернативою може буті матовий папір з кремовим відтінком, не нижче 150 г/м2) з розробкою брендового дзайну макету - 2000 шт.
+2. Виготовлення календаря-будиночка, перекидний лист 13 штук, розмір 210х115 мм, двосторонній картон 230 гр, Друк 4 + 4, підкладка картон 300 гр, Розмір 340х210 мм, 4 + 0, захисний лак, палітурка - пружина з розробкою брендового дизайну макету - 2000 шт.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>79811000-2</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2015-09-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2015-10-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.753798+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>e575d57e46b446b5b1795b1c5b16ad65</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Молоко, 2,5%</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>72</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Марганець</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0badf50e9f1542eb9d9baf5c1312bfcf</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>180</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Марганець</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2e1f692b5a3f4cc2b1de2c8ed5d0ccef</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>d7505dfbe3c442a2acad528932943a5e</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Продукти молочні, інші  (молоко згущене 370г) (код ДК 016-2010 – 10.51.5).</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2015-12-30T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:34.855636+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8423,7 +9279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14946,6 +15802,695 @@
       <c r="K123" t="inlineStr">
         <is>
           <t>2026-01-11T04:18:19.183418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fb1093c1aeab497c81d927bbd9d38540</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UA-2015-09-09-000193</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:17.543930+02:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>6816</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>07131640926148bdbaf4b7b763911360</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UA-2015-09-09-000212</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:19.440248+02:00</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42e4042644864375b9011dec999d40fa</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UA-2015-09-11-000171</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:46.253275+02:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 3 Солом"янського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>01993747</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cdb4b46524444ee5a37ea3f976d152b5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UA-2015-09-15-000097</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:03.079468+02:00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Клінічна лікарня №15 Подільського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>26199074</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>45400</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>fd43e8f669164cbab24619fba05910b2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UA-2015-09-16-000204</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:22.508365+02:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>КУ "Котовська загальноосвітня школа-інтернат I-II ступенів для дітей-сиріт і дітей, позбавлених батьківського піклування"</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20987480</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>48bb6d4d96b6491e84622c5bc31bb971</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UA-2015-09-17-000144</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.202533+02:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>КУ "Котовська загальноосвітня школа-інтернат I-II ступенів для дітей-сиріт і дітей, позбавлених батьківського піклування"</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20987480</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3ef311379a1744b99e0fde2008c05644</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UA-2015-09-17-000157</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.527835+02:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Херсонська філія Державного підприємства "Адміністрація морських портів України" (адміністрація Херсонського морського порту)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>38728533</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>24969</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>c0d950569a254da99898b8a3cfe61a93</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000142</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:03.782027+02:00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>9656</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>6bd5210dca3c4c78ac25a3d7e4c7d5c5</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000262</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.562834+02:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>25637595</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>44000</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ebeccf44d28348a682a78050eea66eba</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000263</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.618438+02:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Київський національний торговельно-економічний університет</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>01566117</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>3264</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>db000ae876f24652b49f134d5e88a041</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000266</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.753798+02:00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Київський зоологічний парк загальнодержавного значення</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>02221171</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UA-2015-09-23-000393</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Державний професійно-технічний навчальний заклад "Марганецький професійний ліцей"</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>21902304</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>16485</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2e1f692b5a3f4cc2b1de2c8ed5d0ccef</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UA-2015-09-24-000168</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:34.855636+02:00</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Олександрівська клінічна лікарня м.Києва</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>01994095</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>31100</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:19:10.770119+00:00</t>
         </is>
       </c>
     </row>
@@ -14960,7 +16505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15437,6 +16982,164 @@
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-11T04:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>{"bytes": 45504}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-12T04:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-13T04:10:47+00:00</t>
+          <t>2026-01-14T04:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1456743639.266188.1.913accb57722c3e80ff303bcfd7b9b87",
-  "updated_at": "2026-01-13T04:10:46.865874+00:00",
-  "pages_done": 25,
-  "tenders_scanned": 2500,
-  "tenders_fetched": 2500,
-  "milk_tenders": 40,
-  "milk_items": 40
+  "offset": "1475614968.198803.1.21a7d17d4ff56ac9bb816d43a8166281",
+  "updated_at": "2026-01-14T04:17:26.048426+00:00",
+  "pages_done": 50,
+  "tenders_scanned": 5000,
+  "tenders_fetched": 5000,
+  "milk_tenders": 71,
+  "milk_items": 74
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3177,2153 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>95e2bd4419904121aaf6f451f0c1a926</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>429277b42e494cea976a91f87b49f13a</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>молоко, свіже, пастеризоване, в поліетиленових пакетах, неконцентроване 0,900 г</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1444</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2016-03-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>с.Черна</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2016-03-06T12:00:00.168064+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>396f7e2fafa34241bb9df1942e2d72f1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>eab8445409b4feed5c6aed8b15fdad91</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>молоко великої рогатої худоби молочних порід (сире), 3,2% жирності, свіже</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>8250</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Закарпатська область</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Ужгород</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2016-03-07T16:00:51.010466+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fb8e1ccd143b462aa070ad605b7cad0b</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cdbf193a85e749a58cc57d41ce1fef43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>31</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2016-03-28T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2016-04-01T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Черновицкая область</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>м. Чернівці</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2016-03-29T18:01:13.268814+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>e045963bffcd43459b058fd175ce4652</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11aa65e9bc934127889f83edaa604765</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>молоко -567,5л по 12грн. за літр
+продуктовий набір для лікувально-профілактичного харчування - 212 наборів по 31,81 грн. за набір
+з помісячною поставкою в м.Вишгород Київська область та помісячною оплатою згідно поданих заявок.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>779</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2016-04-10T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Вишгород</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2016-03-31T15:00:07.477470+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>57dadd949dc6440c91d24d63604586e3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>62a4ed5203ec033ca793f8bd51f6fc48</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>молоко пстеризоване 2,6%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>840</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2016-05-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Львівська область</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Краковець</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2016-04-04T16:01:13.624454+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>57dadd949dc6440c91d24d63604586e3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7fd96e55d98dc111c2b66186005189dc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>сметана 21%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>55</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2016-05-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Львівська область</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Краковець</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2016-04-04T16:01:13.624454+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>26cb4241c29e422a9fc783cafc2be264</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7f97914b053b467195817d7a4e497e69</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Молоко тривалого зберігання 2,5% 900г. Тетра Фин</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>650</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2016-04-11T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>м.Гірник</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2016-04-05T13:24:00.239412+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>f8f8fa91bd4b442897a59641ff209358</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6bc3f99d29a145b6b7a375df67f87b72</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>784</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2016-04-25T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Чернігів</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2016-04-18T11:05:01.239994+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5bbb4086c3fc4a33a5fa19c677a143db</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>6f1f49c3991244359679a2ae36ceb87b</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Чай чорний (подарунковий варіант) - 20 шт. герметичних жерстяних бляшанок. Чорний, байховий, розсипний, крупнолистий чай. Традиційний англійський чай з ароматом бергамоту. вищого гатунку. Маса нетто - 100 гр.
+20 коробок шоколадних цукерок. (Сувенірний набір з міні-плиток темного та молочного шоколаду. Склад - цукор, терте какао, какао-олія, молоко сухе незбиране, какао-порошок, емульгатор соєвий лецитин, ароматизатор "ваніль", Допустимий невеличкий домішок шматочків горіхів.)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>15863200-7</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2016-04-20T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2016-04-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2016-04-20T10:00:16.763016+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fd33b994439c4cf8b002388fdd5c5f51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>afb3e90845904c0fb3aae21c79da1147</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, питне, коров'яче, розфасовка по 1л. в п/п з доставкою по Чернігову два рази на місяць по 49л.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>784</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2016-05-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Чернігів</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2016-04-22T15:53:00.200110+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dab28dcdb5c34f1580b32769e6830df5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7f5aeb68a1f642da84da6a71498e3013</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2,5%, п/е фас 1л</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>700</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2016-04-25T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2016-04-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2016-04-25T15:00:04.810081+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5a8e176e1db84fb38831eb25e81c1075</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2f9c87780371818fc34f8a293a889c99</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Молоко свіже для дитячих садочків</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>600</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2016-08-01T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>с.Війтівка</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2016-07-31T16:03:00.282983+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>926c66ee53d24365800430568f6f20ad</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>e143a982c5c34ff09104ae4d18f45dea</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, 3,4 % жирності, по 930 гр. в упаковці, плівка, всього 7000 упак.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2016-08-02T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Рівненська область</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Дубно</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2016-08-02T00:04:54.057795+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4c537bd113904f4a957b598852dd07e2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>c6fb54a372a44dad801bb57cfeed57a6</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>320</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2016-07-27T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2016-08-03T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>с. Ясининичі</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2016-08-03T13:29:44.138820+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>003e93d6dc40416cbfe22c7f02e34eef</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aec331dcf083c267771f19247be56c3b</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Молоко сире</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>м. Немирів</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2016-08-03T16:04:09.983305+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0de6c09939904e6d8168387046e74af4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9d280f2f374444718f692e2b6be1a234</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>молоко згущене
+жирність - 8,5%
+без пальмового масла</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>250</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2016-08-05T12:03:32.200436+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>f4a74a6064684d07b2ea25ffaa8bc5ef</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0f07013ce3d0caecf2aa86ef110df154</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>15511200-5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>486</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2016-08-09T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Кошаринці</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2016-08-05T16:00:56.288315+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>f4a74a6064684d07b2ea25ffaa8bc5ef</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3f9783554826b2dc919b37b45096742f</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2016-08-09T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Кошаринці</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2016-08-05T16:00:56.288315+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>95f7b32eaef04212bbd7cfb650b646d1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>aec331dcf083c267771f19247be56c3b</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Молоко сире</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>м. Немирів</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2016-08-09T16:04:02.439914+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>d556f20596f34f6daf33df9b78031558</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>26adf673bb9e4edcb58684b7f55b8ab5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2016-08-17T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2016-08-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Луганская область</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2016-08-16T15:04:00.490066+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4a253caab8c24a4fbb5eab91fbda68b9</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>53f6f5d20bfdc5cddf80ee56928a8853</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Молоко пакетіроване (0,900 гр) 150 уп., сметана (0,400 гр) 80 уп., кефір (0,400 гр) 100 уп., йогурт (0,400 гр) 100 уп ., ряжанка (0,400гр) 100 уп,. масло вершкове  (40кг), сир твердий (16кг)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>530</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>уп</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2016-08-17T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Житомирська область</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>м. Баранівка</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2016-08-16T16:02:26.479171+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cd9bfc27e6244814908004f69363fa5b</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3e09b2fc04934258b6c07ed0c4b7647b</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>82</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2016-08-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2016-10-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Чернігівська область</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>смт Холми</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2016-08-18T17:01:49.271918+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>568e59e4490f4c6582834746fb4f646b</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>66cda3527c1d95a50631c469a6e69235</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Молоко сире</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>м. Немирів</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2016-08-22T16:05:00.388460+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9bec0c35802e42048dadd7ad392e90d5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3dcaaa4477f34641abb6d431ecb756f1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>15</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2016-08-22T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2016-08-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Луганская область</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2016-08-22T16:23:05.369248+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>183317f636384503837552b020d30000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>565348a6c073abe978425cf996cc9b2e</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>486</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2016-08-26T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Кошаринці</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2016-08-23T16:01:47.569120+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>183317f636384503837552b020d30000</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>a7ee800c80671635fe3088d517beee8b</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>12</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2016-08-26T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Кошаринці</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2016-08-23T16:01:47.569120+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4227eb11ea9d4e17ae543b1fd346bc58</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>d600b6e6ac014b8ea4c5f9ee7d3ea309</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>30</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2016-09-12T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2016-09-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Луганская область</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2016-09-09T12:30:39.831297+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>d49b635ab0394b89ac2781065313c6e5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3970f00c6146431aa06deb456b6fcb0b</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>30</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2016-09-16T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2016-09-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Луганская область</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2016-09-15T13:43:11.541974+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>09cc339405c84ad785d2fc1a874258b9</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3e932e843c1748379b569dc5fbf2ec62</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>30</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2016-09-20T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2016-09-23T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Житомирская область</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>с. Іванків</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2016-09-15T20:02:18.122741+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fdcf758f81ba44cab2e231fda0ae40a1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>f66829d488bd19116130dc5dce5110c0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>15511500-8</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>270</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2016-12-30T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Черкаська область</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>смт.Чорнобай</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2016-09-23T15:41:34.283805+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>87201b19b3754a4b80ff9b97e81ce291</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>b01ae1b7b40225c91a95efd4012db3c5</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>906</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2016-09-23T14:08:53+03:00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2016-09-24T14:08:53+03:00</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Хмельницька область</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>смт. Меджибіж</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2016-09-30T15:14:31.438882+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>af186de273fd40ccae8d345b12b48ded</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>02582446790e9e1c3bf11f14cffa1f29</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>961</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2016-08-31T13:27:38+03:00</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2016-09-01T13:27:38+03:00</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Хмельницька область</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>смт. Меджибіж</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2016-09-30T15:15:11.894491+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7bd500125b16400c87b762509b07a791</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>bf6d894953feb7eba1a9973f2d3688a3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче  пастеризоване, жирність2,5%, фасовене 0,9-1 кг. та вершки</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ККал</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>K51</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2016-11-30T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Тернопільська область</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>с.Зарваниця</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2016-09-30T16:02:18.598031+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>a48608f8d99640a8b4d6df1accc0ed04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0ea81a3ee3f04c77924f88f9fdd8e3a4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Молоко тривалого зберігання (2,5% 900г. Тетра Фин)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>750</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2016-10-06T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2016-12-31T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Донецька область</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>м.Гірник</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2016-10-04T15:13:39.271969+03:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3188,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5365,6 +7512,1649 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>2026-01-13T04:10:08.573449+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>95e2bd4419904121aaf6f451f0c1a926</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000103-c</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2016-03-06T12:00:00.168064+02:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "ЧОРНЯНСЬКА СПЕЦІАЛЬНА ЗАГАЛЬНООСВІТНЯ ШКОЛА - ІНТЕРНАТ І - ІІ СТУПЕНІВ"</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20989125</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>16692.64</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>396f7e2fafa34241bb9df1942e2d72f1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000092-a</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2016-03-07T16:00:51.010466+02:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ужгородська міська дитяча клінічна лікарня</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01992825</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>84900</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fb8e1ccd143b462aa070ad605b7cad0b</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UA-2016-03-17-000198-c</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2016-03-29T18:01:13.268814+03:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ОБЛАСНА КОМУНАЛЬНА УСТАНОВА"СОЦІАЛЬНИЙ ЦЕНТР МАТЕРІ ТА ДИТИНИ"</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>35659792</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>e045963bffcd43459b058fd175ce4652</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UA-2016-03-24-000071-b</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2016-03-31T15:00:07.477470+03:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Дніпровське басейнове управління водних ресурсів</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>04389466</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>13553.72</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>57dadd949dc6440c91d24d63604586e3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UA-2016-03-25-000291-a</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2016-04-04T16:01:13.624454+03:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>КЗ ЛОР "Краковецька спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22400349</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>26950</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>26cb4241c29e422a9fc783cafc2be264</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UA-2016-03-31-000143-c</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2016-04-05T13:24:00.239412+03:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування ( надання соціальних послуг)м.Селидове Донецької області</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>34766528</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>27965</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>f8f8fa91bd4b442897a59641ff209358</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UA-2016-04-12-000077-a</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2016-04-18T11:05:01.239994+03:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Чернігівський обласний соціальний центр матері та дитини "Батьки й дитина разом"</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>33904244</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>9400</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5bbb4086c3fc4a33a5fa19c677a143db</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UA-2016-04-12-000380-b</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2016-04-20T10:00:16.763016+03:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Відділ у справах сім'ї, молоді та спорту Дніпровської районної в місті Києві державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>37397189</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>4230</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fd33b994439c4cf8b002388fdd5c5f51</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UA-2016-04-18-000283-c</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2016-04-22T15:53:00.200110+03:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Чернігівський обласний соціальний центр матері та дитини "Батьки й дитина разом"</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>33904244</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>9400</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dab28dcdb5c34f1580b32769e6830df5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>UA-2016-04-18-000177-a</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2016-04-25T15:00:04.810081+03:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровська міська клінічна лікарня №8" Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>23644906</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5a8e176e1db84fb38831eb25e81c1075</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UA-2016-07-22-000087-a</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2016-07-31T16:03:00.282983+03:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Війтівська сільська рада</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>04329702</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>3600.01</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>926c66ee53d24365800430568f6f20ad</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UA-2016-07-25-000284-c</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2016-08-02T00:04:54.057795+03:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дубенський будинок-інтернат для громадян похилого віку та інвалідів" Рівненської обласної ради</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>03189274</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>87000</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4c537bd113904f4a957b598852dd07e2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UA-2016-07-25-000250-b</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2016-08-03T13:29:44.138820+03:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>КП "Ясининицький НРЦ"</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>25314596</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>003e93d6dc40416cbfe22c7f02e34eef</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UA-2016-07-29-000060-b</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2016-08-03T16:04:09.983305+03:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Немирівська центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01982614</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0de6c09939904e6d8168387046e74af4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UA-2016-07-31-000010-c</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2016-08-05T12:03:32.200436+03:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство по  утриманню зелених насаджень Печерського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>03359760</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>f4a74a6064684d07b2ea25ffaa8bc5ef</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UA-2016-08-01-000039-a</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2016-08-05T16:00:56.288315+03:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Кошаринецька сільська рада</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20089019</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>95f7b32eaef04212bbd7cfb650b646d1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UA-2016-08-04-000136-a</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2016-08-09T16:04:02.439914+03:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Немирівська центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01982614</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>d556f20596f34f6daf33df9b78031558</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UA-2016-08-11-000643-b</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2016-08-16T15:04:00.490066+03:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>15382.5</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4a253caab8c24a4fbb5eab91fbda68b9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UA-2016-08-11-000453-b</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2016-08-16T16:02:26.479171+03:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування (надання соціальних послуг) Баранівського району</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20406856</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>6800</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cd9bfc27e6244814908004f69363fa5b</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UA-2016-08-11-000332-c</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2016-08-18T17:01:49.271918+03:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування (надання соціальних послуг) Корюківської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>31718361</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>10060</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>568e59e4490f4c6582834746fb4f646b</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UA-2016-08-16-000110-a</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2016-08-22T16:05:00.388460+03:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Немирівська центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01982614</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9bec0c35802e42048dadd7ad392e90d5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UA-2016-08-17-000720-b</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2016-08-22T16:23:05.369248+03:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>15382.5</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>183317f636384503837552b020d30000</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UA-2016-08-18-000031-a</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2016-08-23T16:01:47.569120+03:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Кошаринецька сільська рада</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20089019</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4227eb11ea9d4e17ae543b1fd346bc58</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UA-2016-09-07-000335-c</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2016-09-09T12:30:39.831297+03:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>20030</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>d49b635ab0394b89ac2781065313c6e5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UA-2016-09-13-000433-c</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2016-09-15T13:43:11.541974+03:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>20030</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>09cc339405c84ad785d2fc1a874258b9</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UA-2016-09-13-000862-c</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2016-09-15T20:02:18.122741+03:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>КУ ""Обласний спеціальний будинок-інтернат" житомирської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>33967592</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>3020</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fdcf758f81ba44cab2e231fda0ae40a1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UA-2016-09-23-000488-b</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2016-09-23T15:41:34.283805+03:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Чорнобаївська центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>02005266</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1755</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>87201b19b3754a4b80ff9b97e81ce291</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UA-2016-09-30-000300-a</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2016-09-30T15:14:31.438882+03:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>КЗ КСМЗ"Меджибізький дитячий будинок-інтернат"</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>03191650</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>4530</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>af186de273fd40ccae8d345b12b48ded</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>UA-2016-09-30-000249-a</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2016-09-30T15:15:11.894491+03:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>КЗ КСМЗ"Меджибізький дитячий будинок-інтернат"</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>03191650</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>4805</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7bd500125b16400c87b762509b07a791</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UA-2016-08-31-000054-c</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2016-09-30T16:02:18.598031+03:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>КЗ Колегіум-інтернат "Знамення"</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>34793525</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>7600</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>a48608f8d99640a8b4d6df1accc0ed04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UA-2016-09-28-001264-b</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2016-10-04T15:13:39.271969+03:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування ( надання соціальних послуг)м.Селидове Донецької області</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>34766528</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>42830</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:16:46.484970+00:00</t>
         </is>
       </c>
     </row>
@@ -5379,7 +9169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6172,6 +9962,164 @@
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-13T04:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>{"bytes": 21002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-14T04:17:26+00:00</t>
+          <t>2026-01-15T04:12:50+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1475614968.198803.1.21a7d17d4ff56ac9bb816d43a8166281",
-  "updated_at": "2026-01-14T04:17:26.048426+00:00",
-  "pages_done": 50,
-  "tenders_scanned": 5000,
-  "tenders_fetched": 5000,
-  "milk_tenders": 71,
-  "milk_items": 74
+  "offset": "1478264803.431899.1.cf70551777ed42388a1b5266c5370122",
+  "updated_at": "2026-01-15T04:12:49.740322+00:00",
+  "pages_done": 75,
+  "tenders_scanned": 7500,
+  "tenders_fetched": 7500,
+  "milk_tenders": 88,
+  "milk_items": 92
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5324,6 +5324,1170 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>171cb86eacbc4f8db88df16706d9b205</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7767d2255ad3017d2cd97439368bd26d</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4203</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2016-10-10T17:17:33+03:00</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2016-12-31T17:17:33+02:00</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Хмельницька область</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>м. Хмельницький</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2016-10-10T17:12:34.050442+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>171cb86eacbc4f8db88df16706d9b205</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>eab6e592304f7cceddc8e00c2df9a300</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>вершки</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>76</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2016-10-10T17:17:33+03:00</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2016-12-31T17:17:33+02:00</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Хмельницька область</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>м. Хмельницький</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2016-10-10T17:12:34.050442+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>d09a5c361f4b4a23958be8e3bf215f90</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>d8991e6f3d86430ca9e581b5008a96da</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>30</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2016-10-17T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2016-10-28T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Луганська область</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2016-10-11T18:22:04.062717+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0de34c61dc12489484ddaab672fee9df</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>b3bd3bc73c3c443c9df102f804bc549c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>30</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2016-10-17T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2016-10-28T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Луганська область</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2016-10-17T12:36:57.518123+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>c02e32cbf8644f0ea0ff885598fac917</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>93e9f264ee54421da548a0045e274829</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>м. Харків з 23 жовтня по 04 листопада 2016 року (13 днів). 19 спортсменів, 2 тренери. Жовтневий район.
+Харчування спортсменів 5-6 разове, за узгодженням з тренером. Обов'язковими складовими раціону мають бути фрукти (апельсини, гранати, інжир, виноград), подрібнені горіхи, овочі (капуста, помідори, морква, шпинат), м'ясо (ялов., біле м'ясо курей, нежирна свинина), біла риба та молоко.
+тренери - 3 разове харчування (звичайне).</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>55330000-2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>21</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Людей</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2016-10-23T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2016-11-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2016-10-19T12:04:43.915495+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>f5ecb79b1f5a494ba1ace6db339464d7</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0389e9c68f734c998082890be43ff037</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>30</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2016-10-24T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2016-10-28T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Луганська область</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2016-10-21T14:07:18.890433+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>e88c2a7fa82a49e4bcdc463340c27d26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2ba6f0908d00d08682babc01345ce69d</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>500</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2016-11-01T11:54:33+02:00</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2016-12-31T11:54:33+02:00</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Нова Некрасівка</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2016-10-25T11:49:35.857438+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>f0b86a41bb1d4e5b8d4adb2c2d258928</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>bd8e1115040c4fd69a9cffa283e3f7d0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>30</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2016-10-26T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2016-10-31T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Луганська область</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>смт. Станиця Луганська</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2016-10-26T10:02:12.882259+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9bf286145e94469fb11f149f898e70c6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ec18ef575edd642660d470fc358de593</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Творог 9%, печиво Марія, ізюм, крохмал, молоко, сметана, кефір, кріп, петрушка</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2016-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2016-12-31T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>с.Новопетрівка</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2016-11-04T09:24:36.066381+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fad0ddb403a44935b989782d679d145a</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4449af4ac4f446ec8f9905aa8a6b8dfb</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>молочні продукти</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>400</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	л.	</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2016-10-12T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2016-12-31T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Закарпатська область</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>ЯСІНЯ</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2016-11-04T09:27:41.081128+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9ccbc90e1aba4c0d88500f16abef66aa</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5d42c8e7b640474092fbbb87d409ea9c</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні оброблені</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2016-10-17T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2016-10-17T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Полтавська обл.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Кременчук</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2016-11-04T10:16:33.395830+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2e2a9669f2da4dd391f6ae60f2c7e216</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>d1563c5b1df84025ae6f341959caa572</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>молоко з умістом жиру більш ніж 1%</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2016-11-14T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Донецька область</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>м. Маріуполь</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2016-11-04T11:47:12.900894+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>5f54f477fb7d4d88bd0f8ffa3f5ee2e8</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cc3866e4062841a4bf74768edfaec896</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>10.51.5 Продукти молочні (15511000-3 молоко) згущене молоко (різні найменування)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2016-11-21T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2016-12-31T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2016-11-04T12:16:36.333956+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>c776e7863cf2449eb91a403bb4963b4c</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>9a057bdd69a941d890febe8720256b53</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>молоко з умістом жиру більш ніж 1%</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2016-10-11T00:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Донецька область</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>м. Маріуполь</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2016-11-04T13:26:13.529820+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>e843d7552b85460ea55e81b9f32adff1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>932e1e9cf9377974fed71c0fbf7c87d0</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>сухе молоко незбиране</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>70</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2016-11-07T13:22:35+02:00</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2016-12-31T13:22:35+02:00</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Запорізька область</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>м. Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2016-11-04T13:26:36.174085+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>983fbdb9e6334990b8b237ad26547709</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>db329025c295489bb4c25d8827ae1fb2</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Молоко - детальний опис згідно документації.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1787</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2016-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2016-12-31T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Чернівецька область</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2016-11-04T14:47:32.309552+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0fdc11672ef541039ec84273d3aa85d4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1e9e41293ebe7b231decca9af83cf0de</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче питне пастеризоване</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>2944</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2016-11-01T11:50:20+02:00</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2016-12-31T11:50:20+02:00</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Запорізька область</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2016-11-04T14:51:17.020001+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fbae2368104745a59a432cd0769f10d3</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>d106fa1365d817a1a43c57c210643d43</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>молоко 2,5%  0,9л</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>700</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2016-10-24T15:55:50+03:00</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2016-12-31T15:55:50+02:00</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Донецька область</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>м Маріуполь</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:06:10.034856+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5335,7 +6499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9155,6 +10319,907 @@
       <c r="K72" t="inlineStr">
         <is>
           <t>2026-01-14T04:16:46.484970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>171cb86eacbc4f8db88df16706d9b205</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UA-2016-10-10-001139-b</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2016-10-10T17:12:34.050442+03:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>КЗ Дошкільний навчальний заклад №33 «Джерельце»</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>26216536</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>85212</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>d09a5c361f4b4a23958be8e3bf215f90</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UA-2016-10-07-001131-b</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2016-10-11T18:22:04.062717+03:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>42485</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0de34c61dc12489484ddaab672fee9df</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UA-2016-10-12-000528-b</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2016-10-17T12:36:57.518123+03:00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>42485</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>c02e32cbf8644f0ea0ff885598fac917</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UA-2016-10-12-000291-a</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2016-10-19T12:04:43.915495+03:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Державна установа "Управління збірних команд та забезпечення спортивних заходів "Укрспортзабезпечення"</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>03767831</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>76999</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>f5ecb79b1f5a494ba1ace6db339464d7</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UA-2016-10-19-000560-b</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2016-10-21T14:07:18.890433+03:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>38922</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>e88c2a7fa82a49e4bcdc463340c27d26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>UA-2016-10-25-000174-c</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2016-10-25T11:49:35.857438+03:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Новонекрасівська сільська рада</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>04378563</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>98000</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>f0b86a41bb1d4e5b8d4adb2c2d258928</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UA-2016-10-24-000061-b</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2016-10-26T10:02:12.882259+03:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Станично-Луганське районне територіальне медичне об'єднання</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01983602</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>38922</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>9bf286145e94469fb11f149f898e70c6</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UA-2016-11-04-000081-a</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2016-11-04T09:24:36.066381+02:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Новопетрівська спеціальна загальноосвітня школа-інтернат</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>04590151</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>5850.72</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fad0ddb403a44935b989782d679d145a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UA-2016-11-04-000016-c</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2016-11-04T09:27:41.081128+02:00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ясінянська селищна рада</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>04351452</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9ccbc90e1aba4c0d88500f16abef66aa</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>UA-2016-11-04-000204-b</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2016-11-04T10:16:33.395830+02:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Філія "Придніпровські магістральні нафтопроводи" публічного акціонерного  товариства "Укртранснафта"</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>26113233</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2e2a9669f2da4dd391f6ae60f2c7e216</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UA-2016-10-31-000265-a</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2016-11-04T11:47:12.900894+02:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>КУ "Дошкільний навчальний заклад комбінованого типу "Ясла-садок № 142 "Умка" управління освіти Маріупольської міської ради"</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>26318449</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>44210.17</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5f54f477fb7d4d88bd0f8ffa3f5ee2e8</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UA-2016-10-19-000445-b</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2016-11-04T12:16:36.333956+02:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>aboveThresholdUA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Київський національний університет імені Тараса Шевченка</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>02070944</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>92160</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>c776e7863cf2449eb91a403bb4963b4c</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UA-2016-10-04-000013-b</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2016-11-04T13:26:13.529820+02:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>КУ "КОМУНАЛЬНИЙ ДОШКІЛЬНИЙ НАВЧАЛЬНИЙ ЗАКЛАД ЗАГАЛЬНОГО РОЗВИТКУ "ЯСЛА-САДОК №32 "ДИВОСВІТ" УПРАВЛІННЯ ОСВІТИ МАРІУПОЛЬСЬКОЇ МІСЬКОЇ РАДИ""</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>26443054</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>81894</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>e843d7552b85460ea55e81b9f32adff1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UA-2016-10-31-000181-c</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2016-11-04T13:26:36.174085+02:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>КУ "Обласна інфекційна клінічна лікарня" ЗОР</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>05498849</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>3640</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>983fbdb9e6334990b8b237ad26547709</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>UA-2016-10-18-000170-c</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2016-11-04T14:47:32.309552+02:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська дитяча клінічна лікарня"</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>02005757</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>20550</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0fdc11672ef541039ec84273d3aa85d4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UA-2016-10-26-000600-a</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2016-11-04T14:51:17.020001+02:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>КВНЗ "Хортицька національна навчально-реабілітаційна академія" ЗОР</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>22133718</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>44800</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fbae2368104745a59a432cd0769f10d3</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UA-2016-10-12-000969-b</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:06:10.034856+02:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>КП КПШХ"Восток"</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>13508295</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>127587</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:11.092479+00:00</t>
         </is>
       </c>
     </row>
@@ -9169,7 +11234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10120,6 +12185,164 @@
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>{"bytes": 30415}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-15T04:12:50+00:00</t>
+          <t>2026-01-16T04:10:18+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478264803.431899.1.cf70551777ed42388a1b5266c5370122",
-  "updated_at": "2026-01-15T04:12:49.740322+00:00",
-  "pages_done": 75,
-  "tenders_scanned": 7500,
-  "tenders_fetched": 7500,
-  "milk_tenders": 88,
-  "milk_items": 92
+  "offset": "1478282081.222461.1.aa27d5a4cff39529aed6b77e05a4f515",
+  "updated_at": "2026-01-16T04:10:17.840040+00:00",
+  "pages_done": 100,
+  "tenders_scanned": 10000,
+  "tenders_fetched": 10000,
+  "milk_tenders": 101,
+  "milk_items": 105
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6488,6 +6488,841 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>073bc4eea1ce4a69ba15cda1e82d5fa0</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>96032f37dde98b6150a7fb0e3d8fccfd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жир. 0,9-1 кг; упаковка Пюр-Пак</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>3112</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2016-10-28T16:31:24+03:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:31:24+02:00</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Львівська область</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Школи Стрийського району</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:39:34.056134+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0eeff79d575942a58d2ee44bdb3d6ea0</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>35d5b7da482544378bb248f3411b72c1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Пастеризоване молоко</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2016-11-04T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Рівненська область</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>смт.Квасилів</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:56:57.389078+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>072a97dda76d466986a60437fe42f12f</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>9e567529c0fa4bce9877a78308e51536</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване питне 2.5% </t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2016-10-31T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2016-12-31T22:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Тернопільська область</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>с.Петриків</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2016-11-04T16:07:51.598034+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9d0f471145e44766a3648e3c8c924c6e</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>740296c52779441ca661e65d42057fa2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Молоко згущене в банках.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2015-05-19T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:25.634036+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>882796f080964a8aa85153be69d09973</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7f9f6516eee245319bc42144f397b7a0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Молоко згущене в банках</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2015-07-09T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:42.668938+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>d3330eed3e214635a10e969b17f0789c</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>df6c282771e644bea5fecd9ee0a2645a</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Свинячий балик, філе куряче, стегенця, масло вершкове, маргарин, олія рослинна, чай чорний/зелений, мак-кофе, якобс в стіках, макарони, дріжджі, сир, мед, рис, гречка, арнаутка, повидло, молоко, горох, сахарна пудра,какао, перець, маслини, томатна паста, огірки, ізюм</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>03142300-1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>28229</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2015-06-09T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:43.566806+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3877380a2e5f47e8864ca3051246553f</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>34d74d052eb94aa293b6999acd392986</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>молоко, сметана, йогурт, кефір, масло, сир, яйце у шкаралупі,
+хліб, круасан, сардельки</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1389</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2015-06-02T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2015-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:44.004082+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>a35269cfe2674137b4dea5d656a0b242</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8d2228db74504343959766f9766c85dc</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Береза. брикет Пломбір 90гр; Береза. ст. вафельний Пломбір 70гр; Береза. ст. вафельний Пломбір шоколад 70гр; Береза. ескімо Плодово-ягід без глазуриі77гр; Береза. ескімо Плодово-ягід в глазурі 77гр; Береза. ескімо Пломбір шоколад в глазурі 77гр; Береза. ескімо фрукт. лід в берез. соку 77гр; Рудь. брикет 100 % Морозиво 90гр; Рудь. брикет пломбір Ескімос 90гр; Рудь. вафельний Рожок125 мм; Рудь. вафельний Рожок130 мм; Рудь. ріжок 100% морозиво 70гр; Рудь. ст. 100% морозиво 70гр; Рудь. ст. Дитяче70гр; Рудь. ст. Золотий ключик 70гр;  Рудь. ст. Киви, яблуко, груша 70гр; Рудь. ст. Пролісок (ван) 60гр; Рудь. ст. Пролісок (шок) 60гр; Рудь. ст. Пустунчик згущ. молоко 70гр; Рудь. ст. Щербет султана (чорн. шок. горіх) 70гр; Рудь. ескімо 100% морозиво б/гл. 65гр; Рудь. ескімо 100% морозиво з шок. кр 65гр; Рудь. ескімо Бананчик 60гр; Рудь. ескімо Каштан 70гр; Рудь. ескімо Каштан шоколадний 70гр; Рудь. ескімо Персик-манго 85гр; Рудь. ескімо Плодово-ягідне 80гр ; Рудь. ваг. м’яке 100% морозиво 2500гр ; Рудь. ваг. 100% морозиво 1кг ; Рудь. ескімо фруктовий лід Фрутсік вінт 75гр</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>15555100-4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>7286</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2015-06-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:46.035510+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0c1d7ba393fe437a9061a3833aed7419</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>edae3a1a7e2a4fdd89e166b5a98959b6</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Молоко ультрапастеризоване, жирність 1,5%, ТМ «Селянське, особливе», 1000 мл.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>12600</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2015-06-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:46.836476+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>428415b499704e208a54209356bae230</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>f38c62bb24d1497399332aeecd7a4da4</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені (Молоко з умістом жиру більше ніж 1 мас. %, але не більше від 6 мас. %, неконцентроване, без додання цукру чи інших підсолоджувачів, у первинних пакованнях з чистим умістом не більше ніж 2л) (код за ДК 016:2010 – 10.51.11-42.00)  (Детальний опис див.вкладений файл)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>40468</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2015-06-08T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:50.231639+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>82772acc37d649edb55fd0a72169a05b</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10d5b790e8af47dfb926fb9e4e2e1e06</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Береза брикет Пломбір 90гр 
+Береза ст. вафельний Пломбір 70гр 
+Береза ст. вафельний Пломбір шоколад 70гр 
+Береза ескімо Плодово-ягід без глазуриі77гр 
+Береза. ескімо Плодово-ягід в глазурі 77гр 
+Берез ескімо Пломбір шоколад в глазурі 77гр
+Береза ескімо фрукт. лід в берез. соку 77гр 
+Рудь  брикет 100 % Морозиво 90гр 
+Рудь  брикет пломбір Ескімос 90гр 
+Рудь  вафельний Рожок125 мм 
+Рудь  вафельний Рожок130 мм 
+Рудь  ріжок 100% морозиво 70гр
+Рудь  ст. 100% морозиво 70гр 
+Рудь  ст. Дитяче70гр 
+Рудь  ст. Золотий ключик 70гр  
+Рудь  ст. Киви, яблуко, груша 70гр 
+Рудь  ст. Пролісок (ван) 60гр 
+Рудь  ст. Пролісок (шок) 60гр 
+Рудь  ст. Пустунчик згущ. молоко 70гр 
+Рудь ст. Щербет султана (чорн. шок. горіх) 70гр 
+Рудь  ескімо 100% морозиво б/гл. 65гр 
+Рудь ескімо 100% морозиво з шок. кр 65гр 
+Рудь  ескімо Бананчик 60гр 
+Рудь  ескімо Каштан 70гр 
+Рудь  ескімо Каштан шоколадний 70гр 
+Рудь  ескімо Персик-манго 85гр 
+Рудь. ескімо Плодово-ягідне 80гр 
+Рудь  ваг. м’яке 100% морозиво 2500гр 
+Рудь  ваг. 100% морозиво 1кг 
+Рудь  ескімо фруктовий лід Фрутсік вінт 75гр</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>15555100-4</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>7286</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2015-06-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:09.002742+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>8942ffeb4db84197a6865a5fac60bff5</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3d87f2f16c6246f7a49f90aadf2eafa0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Код ДК 016-2010: 01.11.9. "Насіння інших олійних культур", 01.25.3. "Горіхи (крім дикорослих їстівних горіхів, арахісу та кокосів)", 10.39.1. «Плоди та овочі, оброблені та законсервовані»   10.39.2. «Плоди й горіхи, оброблені та законсервовані», 10.41.5. "Олії рафіновані", 10.42.1. "Маргарин і подібні харчові жири", 01.49.2. "Продукція тваринництва, інша" ("Мед натуральний"), 10.51.1. "Молоко та вершки, рідинні, оброблені", 10.51.4. «Сир сичужний та кисломолочний сир», 10.51.5. «Продукти молочні, інші», 10.84.1. «Оцет; соуси; суміші приправ», 10.84.2. «Прянощі, оброблені» ,  10.84.3. «Сіль харчова», 10.89.1. "Супи, яйця, дріжджі та інші харчові продукти"  (більш детально в додатку до оголошення).</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>25</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2015-06-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:09.267451+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>dc1a638922084128a578c017c98df663</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ed461f7c45a24beb9489f89ac58215dd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Молоко, Жирн. 3,2%, фасоване, пастеризоване, 1/0,900 кг, ДСТУ 2661:2010 - 5690шт.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2015-07-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2016-07-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:18.119813+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6499,7 +7334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11220,6 +12055,695 @@
       <c r="K89" t="inlineStr">
         <is>
           <t>2026-01-15T04:12:11.092479+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>073bc4eea1ce4a69ba15cda1e82d5fa0</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>UA-2016-10-20-000555-a</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:39:34.056134+02:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Відділ освіти Стрийської РДА</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>36742802</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>199957</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0eeff79d575942a58d2ee44bdb3d6ea0</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UA-2016-11-04-001063-b</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2016-11-04T15:56:57.389078+02:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>КВАСИЛІВСЬКИЙ ДОШКІЛЬНИЙ НАВЧАЛЬНИЙ ЗАКЛАД (ЯСЛА-САДОК)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>25315035</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>072a97dda76d466986a60437fe42f12f</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>UA-2016-10-24-000902-b</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2016-11-04T16:07:51.598034+02:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>КУ "Петриківський обласний геріатричний пансіонат"</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>03562589</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>44460</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>9d0f471145e44766a3648e3c8c924c6e</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UA-2015-05-05-000018</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:25.634036+02:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Бердянська філія державного підприємства "Адміністрація морських портів України"</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>38728360</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>41779</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>882796f080964a8aa85153be69d09973</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UA-2015-05-22-000034</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:42.668938+02:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Бердянська філія державного підприємства "Адміністрація морських портів України"</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>38728360</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>41779.2</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>d3330eed3e214635a10e969b17f0789c</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>UA-2015-05-25-000005</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:43.566806+02:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ренійська філія Державного підприємства "Адміністрация морських портів України"</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>38728465</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>156745</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3877380a2e5f47e8864ca3051246553f</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>UA-2015-05-25-000030</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:44.004082+02:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Надвірнянський коледж Національного транспортного університету</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>38651796</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>6307.57</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>a35269cfe2674137b4dea5d656a0b242</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>UA-2015-05-26-000045</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:46.035510+02:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Южненська філія державного підприємства "Адміністрація морських портів України" (адміністрація морського порту "Южний")</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>38728549</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0c1d7ba393fe437a9061a3833aed7419</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>UA-2015-05-27-000032</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:46.836476+02:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Державне підприємство «Ізмаїльський морський торговельний порт»</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>01125815</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>195048</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>428415b499704e208a54209356bae230</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>UA-2015-05-29-000013</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:53:50.231639+02:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНЕ ПІДПРИЄМСТВО "КИЇВПАСТРАНС"</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>31725604</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>308000</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>82772acc37d649edb55fd0a72169a05b</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>UA-2015-06-05-000045</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:09.002742+02:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Южненська філія державного підприємства "Адміністрація морських портів України" (адміністрація морського порту "Южний")</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>38728549</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>8942ffeb4db84197a6865a5fac60bff5</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>UA-2015-06-05-000059</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:09.267451+02:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Іллічівська філія державного підприємства “Адміністрація морських портів України” (Адміністрація Іллічівського морського порту)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>38728418</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>190146</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>dc1a638922084128a578c017c98df663</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>UA-2015-06-15-000016</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:54:18.119813+02:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Державне підприємство «Маріупольський морський торговельний порт»</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>01125755</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>69304.2</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:09:41.326400+00:00</t>
         </is>
       </c>
     </row>
@@ -11234,7 +12758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12343,6 +13867,164 @@
       </c>
       <c r="E42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:12:50+00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>{"bytes": 35828}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-16T04:10:18+00:00</t>
+          <t>2026-01-17T04:02:59+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282081.222461.1.aa27d5a4cff39529aed6b77e05a4f515",
-  "updated_at": "2026-01-16T04:10:17.840040+00:00",
-  "pages_done": 100,
-  "tenders_scanned": 10000,
-  "tenders_fetched": 10000,
-  "milk_tenders": 101,
-  "milk_items": 105
+  "offset": "1478282201.539197.1.a66672a13d1cb6ac87a6aa2598195569",
+  "updated_at": "2026-01-17T04:02:59.446200+00:00",
+  "pages_done": 125,
+  "tenders_scanned": 12500,
+  "tenders_fetched": 12500,
+  "milk_tenders": 105,
+  "milk_items": 109
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7323,6 +7323,218 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bf560e6205534e159a359e2f44638f6e</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7c1701269f544ed18f34fbbe83962e7e</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10.51.1 Молоко та вершки, рідинні, оброблені (10.51.11-42.00 молоко)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:07.272506+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>e8354bf0d23b4ff58d9492de3d537b95</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>e5433dcde8634970a4e277c9342e3100</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Молоко та вершки рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:29.388767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3ad3c0ec445a459f905c9e566cccfdda</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>9ac2fc11687f4b1ea971ff04d5906b12</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Молоко питне ультрапастеризоване за кодом ДК 016:2010 – 10.51.1- «Молоко та вершки, рідинні, оброблені»</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>4495</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:37.273894+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9373b16c10bc4c89b1a584fba7054422</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bdf926b898d7446fa918f262fc1f2e16</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.	Кава у зернах, 500 гр	30 	шт 2.	Цукор пресований у кубиках (500 г)	10 	шт 3.	 Вершки сухі для напоїв Coffee-mate, 400 гр.	10 	шт 4.	Серветки столові білі, одношарові, в упаковці 500 штук	10 	шт 5.	 Чай зелений Greenfield Flying Dragon, в упаковці 100 пак.	5 	шт 6.	 Чай чорний Greenfield Golden Ceylon, в упаковці 100 пак.	5 	шт 7.	Цукор-пісок, 1 кг	10 	шт 8.	Палички для розмішування напоїв, в упаковці 1000 шт.	5  	шт</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>15860000-4</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>85</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2015-08-10T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2015-08-11T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Київськая</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:11.256963+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7334,7 +7546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12744,6 +12956,218 @@
       <c r="K102" t="inlineStr">
         <is>
           <t>2026-01-16T04:09:41.326400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bf560e6205534e159a359e2f44638f6e</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>UA-2015-07-07-000020</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:07.272506+02:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ "Донбаська електроенергетична система" ДП "НЕК "Укренерго"</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>23344104</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>20160</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:23.561319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>e8354bf0d23b4ff58d9492de3d537b95</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UA-2015-07-14-000086</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:29.388767+02:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ДП "Київська міська дирекція УДППЗ "Укрпошта""</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01189979</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:23.561319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3ad3c0ec445a459f905c9e566cccfdda</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UA-2015-07-17-000044</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:55:37.273894+02:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Білгород-Дністровська філія державного підпириємства "Адміністрація морських портів України" (адміністрація Білгород-Дністровського морського порту)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>38728376</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>24497.75</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:23.561319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9373b16c10bc4c89b1a584fba7054422</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UA-2015-07-28-000156</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:11.256963+02:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ДП "УКРІНТЕРАВТОСЕРВІС"</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>21536845</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:23.561319+00:00</t>
         </is>
       </c>
     </row>
@@ -12758,7 +13182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14025,6 +14449,164 @@
       </c>
       <c r="E48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-16T04:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>{"bytes": 40931}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:59+00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:02:59+00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:00+00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:00+00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:00+00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-17T04:02:59+00:00</t>
+          <t>2026-01-17T04:04:06+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282201.539197.1.a66672a13d1cb6ac87a6aa2598195569",
-  "updated_at": "2026-01-17T04:02:59.446200+00:00",
-  "pages_done": 125,
-  "tenders_scanned": 12500,
-  "tenders_fetched": 12500,
-  "milk_tenders": 105,
-  "milk_items": 109
+  "offset": "1478282349.043586.1.d0a1099efcee93f25a6d54a870cbb3fb",
+  "updated_at": "2026-01-17T04:04:06.092895+00:00",
+  "pages_done": 150,
+  "tenders_scanned": 15000,
+  "tenders_fetched": 15000,
+  "milk_tenders": 122,
+  "milk_items": 126
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7535,6 +7535,883 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>916a88cc63914fccb0b4f64c30c21448</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>94a4eff26f8d41e2ac8176da6a026476</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>молоко коров’яче питне пастеризоване жирністю 2,5% (код 10.51.1 згідно ДК 016-2010 Молоко та вершки рідинні, оброблені)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2015-12-27T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:54.645091+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ca282f2cafb64b7eb7bfd9c7444729e9</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>d6b5655ca6c3436e9ed14ef3a5100c9b</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>«Молоко та вершки, рідинні, оброблені» (молоко).</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2015-09-20T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:56.948559+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0501d112b17740179b6dfe222d741b2f</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>d8276df064874ad99ad611a109b11e40</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Молоко фас 1 літр п/е, 2.5%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2015-08-24T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:59.231733+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9cc032b602cc46e6b2d6d2837ea41dba</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>f366ed4468884fe3913bf24ab5e82124</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ДНЕПРОПЕТРОВСКАЯ ОБЛ.</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:06.394159+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9407598a5564447381e1ee10856e3668</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>6fa3b4421be64b31be89a1707220e910</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен 1 л</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>600</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.626309+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>b4e8d08a57e848238c6cc2cca30bf223</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ad13743cfee3465fbbb6abde5a77ef53</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен 1 л</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>600</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.814561+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0161f1d8ae954179af635e147f4cbf74</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>606b65025a6f466c87d663620629c54e</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Молоко 3,2 % пастеризоване поліетилен 0,5 л</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>600</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.478429+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>dff9746856564cd2b249d8612a56fa43</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>17748e8984184102b9e14950a033c317</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % пастеризоване поліетилен  1 л</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>450</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.624524+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>eeea13766d6b49c2b30087060f6573e3</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>12af1eef216343a4ad29a76a14122b4d</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен  0,5 л</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2082</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:34.294837+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>89c1f871adc44165a78dec1a036dc3db</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5971f193a4214591b2bd526f1465b812</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 % поліетилен  0,5 л</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>3920</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:37.074563+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20fc3534a32e4e98a37e1fc41ce4adb8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4b49b8426886471a89bcf13d76ec9d9b</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2.7% 500г.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1102</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:42.706161+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>c9a4c99b475342b1b3e707cafd1feea3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>c3cef331746e42af9d3dc2024028f064</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>молоко 2,5 % жир.(10.51.11-42.00)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>22360</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:04.492396+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>fca11035a4d742b1b9efb53c84254420</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>d70a355ef0c048b4b14b06b3a69894c6</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:21.863187+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>05b4cac24a3d43bf95917a444541ba85</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6b50aa94de2045a09f7f008672b70b78</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>молоко сухе знежирене</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>500</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2015-11-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2015-11-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:34.794793+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>8aea2333476c49ef8249f9cf7208fc80</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>be7fb4b2a8e347399d423d1926f86cf2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Молоко 2,6 % жирность ДСТУ 2661-94</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>42000000-6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ХАРЬКОВСКАЯ ОБЛ.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Харьков</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:39.134971+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>fb24e47fbd424063be7640428411abca</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>a214e419e3b74caf95a6393467937c83</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Молоко тривалого зберігання 2,6% 1 л</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>65</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.100157+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>a87b459aa61d4bb0876a8f142170b2bb</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6d90ce275da046bca5a0e9412e15dea3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>молоко жирність 2,6% плівка по 1л</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2015-09-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.363048+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7546,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13168,6 +14045,907 @@
       <c r="K106" t="inlineStr">
         <is>
           <t>2026-01-17T04:02:23.561319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>916a88cc63914fccb0b4f64c30c21448</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UA-2015-08-10-000028</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:54.645091+02:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ВП ХАЕС ДП "НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>21313677</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>92700</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ca282f2cafb64b7eb7bfd9c7444729e9</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UA-2015-08-11-000019</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:56.948559+02:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ВП Запорізька АЕС ДП НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>19355964</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>31486</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0501d112b17740179b6dfe222d741b2f</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UA-2015-08-11-000073</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:56:59.231733+02:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна лікарня № 2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>05415941</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>99750</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9cc032b602cc46e6b2d6d2837ea41dba</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UA-2015-08-12-000118</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:06.394159+02:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>20500</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9407598a5564447381e1ee10856e3668</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UA-2015-08-14-000057</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.626309+02:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>b4e8d08a57e848238c6cc2cca30bf223</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UA-2015-08-14-000061</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:14.814561+02:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0161f1d8ae954179af635e147f4cbf74</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000071</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.478429+02:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>3360</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>dff9746856564cd2b249d8612a56fa43</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000078</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:33.624524+02:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>8280</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>eeea13766d6b49c2b30087060f6573e3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UA-2015-08-19-000102</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:34.294837+02:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>9993.6</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>89c1f871adc44165a78dec1a036dc3db</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UA-2015-08-20-000066</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:37.074563+02:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>19992</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20fc3534a32e4e98a37e1fc41ce4adb8</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UA-2015-08-21-000105</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:57:42.706161+02:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>6820</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>c9a4c99b475342b1b3e707cafd1feea3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UA-2015-08-28-000048</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:04.492396+02:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Київський національний університет імені Тараса Шевченка</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>02070944</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>178880</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>fca11035a4d742b1b9efb53c84254420</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UA-2015-09-01-000137</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:21.863187+02:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>КМКЛ № 4</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>30212155</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>28800</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>05b4cac24a3d43bf95917a444541ba85</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UA-2015-09-03-000113</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:34.794793+02:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>відокремлений підрозділ „Рівненська АЕС” державного підприємства   „Національна атомна енергогенеруюча компанія “Енергоатом”</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>05425046</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>8aea2333476c49ef8249f9cf7208fc80</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UA-2015-09-04-000028</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:58:39.134971+02:00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Український державний центр по експлуатації спеціалізованих вагонів"</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01056362</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>368000</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>fb24e47fbd424063be7640428411abca</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UA-2015-09-08-000196</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.100157+02:00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Придніпровська залізниця"</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01073828</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>806</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>a87b459aa61d4bb0876a8f142170b2bb</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UA-2015-09-08-000199</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:08.363048+02:00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>46800</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:28.335701+00:00</t>
         </is>
       </c>
     </row>
@@ -13182,7 +14960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14607,6 +16385,164 @@
       </c>
       <c r="E54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:03:00+00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>{"bytes": 42445}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-17T04:04:06+00:00</t>
+          <t>2026-01-18T04:14:24+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282349.043586.1.d0a1099efcee93f25a6d54a870cbb3fb",
-  "updated_at": "2026-01-17T04:04:06.092895+00:00",
-  "pages_done": 150,
-  "tenders_scanned": 15000,
-  "tenders_fetched": 15000,
-  "milk_tenders": 122,
-  "milk_items": 126
+  "offset": "1478282499.303665.1.02997663a538d93c316c3093058128e8",
+  "updated_at": "2026-01-18T04:14:24.070183+00:00",
+  "pages_done": 175,
+  "tenders_scanned": 17500,
+  "tenders_fetched": 17500,
+  "milk_tenders": 135,
+  "milk_items": 140
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8412,6 +8412,862 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>fb1093c1aeab497c81d927bbd9d38540</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7a36d4d9884143de8732c09da779c22c</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Скло предметне з полем для запису 1 мм
+Скло предметне 2 мм
+Скло предметне25,4х76,2з шліф краєм 
+Піпетка до ШОЕ-метру (капіляр Панченкова)
+Пiпетка Пастера  3мл поліетиленова  стерильна
+PW297Лінійка для вимірювання зон затримки росту</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>14820000-5</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>6152</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2015-09-27T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:17.543930+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>07131640926148bdbaf4b7b763911360</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>f1e0e8a3006345c0be0a3d795a5d5065</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Молоко 2.5 %, 1 л</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2015-09-15T18:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2015-09-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:19.440248+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>42e4042644864375b9011dec999d40fa</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>088f685ddf634a43862edf456708c8b1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Молоко пастерізоване жирністю до 2,5%включно. Місце поставкі - м.Київ, вул.Волинська,21. Надання всіх установчих документів ві "Постачальника", сертифікатів качества на продукцію. Наявність холодільного устаткування для перевезення продуктів харчування. Склад "Постачальника" повинен бути розташованим в м.Києві.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1201</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2015-10-01T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:46.253275+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cdb4b46524444ee5a37ea3f976d152b5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0d31e63121c54817bf131b65f6d42af0</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>молоко жирність 2,5% плівка по 1 л</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:03.079468+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>fd43e8f669164cbab24619fba05910b2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>4e6715a5af4449eaa55db65f31e7df7d</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Молоко з умістом жиру не більше 2,6% неконцентроване</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>м.Котовськ</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:22.508365+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>48bb6d4d96b6491e84622c5bc31bb971</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>87dfd26d542d4e43887cc19f84e7c318</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Молоко сгущене</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>15551000-5</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>50</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>м.Котовськ</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.202533+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3ef311379a1744b99e0fde2008c05644</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>d95238687e324ae0a9f1e70627e171db</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Детальний опис предмета закупівлі визначено в оголошенні (додається)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>2870</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Херсонська</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.527835+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>c0d950569a254da99898b8a3cfe61a93</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0b4789d34df94f2a898fa07134454227</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - плівка по 1 л.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>800</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2015-09-30T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2015-12-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:03.782027+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>6bd5210dca3c4c78ac25a3d7e4c7d5c5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>def22b77408947b985761d8818fbfb64</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Фасовка - банка бляшана, маса 380г, молоко згущене з цукром 8,5%, ДСТУ 4274:2003 Продукція повинна мати сертифікат відповідності.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2015-09-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2015-10-08T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.562834+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ebeccf44d28348a682a78050eea66eba</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>a2aefd913ffd44dc83f229b928d73c7c</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>молоко ультрапастеризоване</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>192</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2015-10-15T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2015-10-22T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.618438+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>db000ae876f24652b49f134d5e88a041</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>e0a62917e3694820ab255a46169065e4</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1. Виготовлення листівки для школи, формат: А2, офсетний тип друку; кольоровість: Pantone Black + Pantone 802; рекомендований матеріал: папір munken print cream 150 г/м2 (альтернативою може буті матовий папір з кремовим відтінком, не нижче 150 г/м2) з розробкою брендового дзайну макету - 2000 шт.
+2. Виготовлення календаря-будиночка, перекидний лист 13 штук, розмір 210х115 мм, двосторонній картон 230 гр, Друк 4 + 4, підкладка картон 300 гр, Розмір 340х210 мм, 4 + 0, захисний лак, палітурка - пружина з розробкою брендового дизайну макету - 2000 шт.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>79811000-2</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2015-09-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2015-10-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.753798+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>e575d57e46b446b5b1795b1c5b16ad65</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Молоко, 2,5%</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>72</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Марганець</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0badf50e9f1542eb9d9baf5c1312bfcf</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>180</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2015-10-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Марганець</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2e1f692b5a3f4cc2b1de2c8ed5d0ccef</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>d7505dfbe3c442a2acad528932943a5e</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Продукти молочні, інші  (молоко згущене 370г) (код ДК 016-2010 – 10.51.5).</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2015-12-30T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:34.855636+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8423,7 +9279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14946,6 +15802,695 @@
       <c r="K123" t="inlineStr">
         <is>
           <t>2026-01-17T04:03:28.335701+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fb1093c1aeab497c81d927bbd9d38540</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UA-2015-09-09-000193</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:17.543930+02:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>6816</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>07131640926148bdbaf4b7b763911360</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UA-2015-09-09-000212</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:19.440248+02:00</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42e4042644864375b9011dec999d40fa</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UA-2015-09-11-000171</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2016-11-04T19:59:46.253275+02:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 3 Солом"янського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>01993747</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cdb4b46524444ee5a37ea3f976d152b5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UA-2015-09-15-000097</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:03.079468+02:00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Клінічна лікарня №15 Подільського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>26199074</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>45400</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>fd43e8f669164cbab24619fba05910b2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UA-2015-09-16-000204</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:22.508365+02:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>КУ "Котовська загальноосвітня школа-інтернат I-II ступенів для дітей-сиріт і дітей, позбавлених батьківського піклування"</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20987480</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>48bb6d4d96b6491e84622c5bc31bb971</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UA-2015-09-17-000144</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.202533+02:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>КУ "Котовська загальноосвітня школа-інтернат I-II ступенів для дітей-сиріт і дітей, позбавлених батьківського піклування"</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20987480</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3ef311379a1744b99e0fde2008c05644</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UA-2015-09-17-000157</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:00:30.527835+02:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Херсонська філія Державного підприємства "Адміністрація морських портів України" (адміністрація Херсонського морського порту)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>38728533</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>24969</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>c0d950569a254da99898b8a3cfe61a93</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000142</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:03.782027+02:00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>9656</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>6bd5210dca3c4c78ac25a3d7e4c7d5c5</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000262</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.562834+02:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>25637595</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>44000</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ebeccf44d28348a682a78050eea66eba</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000263</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.618438+02:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Київський національний торговельно-економічний університет</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>01566117</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>3264</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>db000ae876f24652b49f134d5e88a041</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UA-2015-09-22-000266</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:09.753798+02:00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Київський зоологічний парк загальнодержавного значення</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>02221171</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>96db9d7330464c1f8838b4f79661f7bc</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UA-2015-09-23-000393</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:28.781291+02:00</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Державний професійно-технічний навчальний заклад "Марганецький професійний ліцей"</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>21902304</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>16485</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2e1f692b5a3f4cc2b1de2c8ed5d0ccef</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UA-2015-09-24-000168</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:01:34.855636+02:00</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Олександрівська клінічна лікарня м.Києва</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>01994095</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>31100</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:13:41.320524+00:00</t>
         </is>
       </c>
     </row>
@@ -14960,7 +16505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16543,6 +18088,164 @@
       </c>
       <c r="E60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-17T04:04:06+00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>{"bytes": 46524}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-18T04:14:24+00:00</t>
+          <t>2026-01-19T04:20:46+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282499.303665.1.02997663a538d93c316c3093058128e8",
-  "updated_at": "2026-01-18T04:14:24.070183+00:00",
-  "pages_done": 175,
-  "tenders_scanned": 17500,
-  "tenders_fetched": 17500,
-  "milk_tenders": 135,
-  "milk_items": 140
+  "offset": "1478282636.857645.1.6987178195d5990c571295b5a5a3d24b",
+  "updated_at": "2026-01-19T04:20:46.260258+00:00",
+  "pages_done": 200,
+  "tenders_scanned": 20000,
+  "tenders_fetched": 20000,
+  "milk_tenders": 140,
+  "milk_items": 145
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9268,6 +9268,305 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>091d0a9abfab4f68925992e32cf548a6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>d4e63d992d30474182f0689125f09f81</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Молоко пастерізоване жирністю до 2,5% включно. Місце поставкі - м.Київ,вул.Волинська,21. Надання всіх установчих документів від "Постачальника", сертифікатів качества на продукцію. Наявність холодільного устаткування для перевезення продуктів харчування. Склад "Постачальника" повинен бути розташованим в м.Києві.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>462</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2015-10-19T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:02:40.522454+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>3640730854ec420183c5014e36c06536</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>9841368e8ec34f1fad13cdaff4fce90c</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>1. Виготовлення листівки для школи, формат: А2, офсетний тип друку; кольоровість: Pantone Black + Pantone 802; рекомендований матеріал: папір munken print cream 150 г/м2 (альтернативою може буті матовий папір з кремовим відтінком, не нижче 150 г/м2) з розробкою брендового дзайну макету - 2000 шт. 2. Виготовлення календаря-будиночка, перекидний лист 13 штук, розмір 210х115 мм, двосторонній картон 230 гр, Друк 4 + 4, підкладка картон 300 гр, Розмір 340х210 мм, 4 + 0, захисний лак, палітурка - пружина з розробкою брендового дизайну макету - 2000 шт.
+Кандидати, які приймають участь у даному аукціоні, повинні мати види діяльності для виготовлення поліграфічної продукції, та окремо на розробку дизайн макету!!!!! Учасник повинен прікріпити усі необхідні документи у період подачи пропозиції, до аукціону!!!! Якщо ви перемогли, не лякайтесь та відповідайте на електронну адресу чи по телефону.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>22300000-3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>2</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2015-10-25T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2015-10-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:01.452788+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2501f2fa861349b6a07e5f105b3a9f81</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>c8388c112b654b5c94368a9cd6894815</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Код ДК 016-2010: 10.51.1- «Молоко та вершки, рідинні, оброблені», документація додається</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2015-10-18T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:11.591572+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>f7b855d747d44a91b67fba0189e36ec1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>351688dfda3d4abcaa9cdd41589cd0d3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Молоко довгострокового використання 2,6% тетрапак</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>140</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2015-10-12T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2015-10-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>м.Нікополь</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:29.562763+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ce21da0bf81e4d09b3fc172d56225a81</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>3bd0fc5600df4554b95a1d47175f450f</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Молоко коровяче питне пастеризоване 2,5% жиру. ТУ У 25027034-008-98 Склад: молоко коровяче незбиране, молоко коровяче нежирне. Поживна (харчова) цінність 100 г молока,г: жири- 2,5%, білки- 3,0, вуглеводи- 4,5. Без ГМО. Калорійність 100 г молока, ккал - 57. Маса нетто,г: 1000. Строк придатності не менше 5 діб.
+Доставка згідно телефонної заявки харчоблока.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:45.240689+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9279,7 +9578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16491,6 +16790,271 @@
       <c r="K136" t="inlineStr">
         <is>
           <t>2026-01-18T04:13:41.320524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>091d0a9abfab4f68925992e32cf548a6</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UA-2015-09-30-000251</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:02:40.522454+02:00</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 3 Солом"янського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>01993747</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:09.315743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3640730854ec420183c5014e36c06536</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UA-2015-10-02-000151</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:01.452788+02:00</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Київський зоологічний парк загальнодержавного значення</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>02221171</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:09.315743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2501f2fa861349b6a07e5f105b3a9f81</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UA-2015-10-05-000084</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:11.591572+02:00</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ДП "Одеський морський торговельний порт"</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>01125666</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:09.315743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>f7b855d747d44a91b67fba0189e36ec1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UA-2015-10-06-000069</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:29.562763+02:00</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ДП "Державний професійно-технічний навчальний заклад "Нікопольський центр професійної освіти""</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>02541705</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>22797.5</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:09.315743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ce21da0bf81e4d09b3fc172d56225a81</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UA-2015-10-07-000102</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:03:45.240689+02:00</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:09.315743+00:00</t>
         </is>
       </c>
     </row>
@@ -16505,7 +17069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18246,6 +18810,164 @@
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-18T04:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>{"bytes": 50958}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-19T04:20:46+00:00</t>
+          <t>2026-01-20T04:15:27+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282636.857645.1.6987178195d5990c571295b5a5a3d24b",
-  "updated_at": "2026-01-19T04:20:46.260258+00:00",
-  "pages_done": 200,
-  "tenders_scanned": 20000,
-  "tenders_fetched": 20000,
-  "milk_tenders": 140,
-  "milk_items": 145
+  "offset": "1478282782.373001.1.944e0b6f52d7cd059c6a7cf44de9b330",
+  "updated_at": "2026-01-20T04:15:27.121666+00:00",
+  "pages_done": 225,
+  "tenders_scanned": 22500,
+  "tenders_fetched": 22500,
+  "milk_tenders": 152,
+  "milk_items": 158
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9567,6 +9567,827 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>5f647e4792954740877799c97a477841</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>25408090bb4840dd8c131ddbb5b9a3e9</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Молоко фасоване 1 л п/е 2.5% 
+Скорочена процедура. В зв`язку з нагальною потребою для забезпезпечення безперебійного лікувального процесу в лікарні.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2015-10-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:14.811378+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>096cf02d4caf4544818091cbedc910fa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3a0e806f1f6c48c7a6b298f2b4892c08</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Молоко довгострокове</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>450</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2015-10-21T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2015-10-27T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:24.747776+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>096cf02d4caf4544818091cbedc910fa</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>60c3f534db4843cc8c9e1c08c0181823</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>133</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2015-10-21T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2015-10-27T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:24.747776+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1469105c7b8748e69ade33bef8d01113</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>d157f820ba0e40d487102f4cf9f0e192</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>1. Молоко «На здоров’я»  3,2% Дитяче 0,5 л. - 1378 шт.
+2. Сік ТМ «Чудо Чадо» 0,2 л. в асортименті - 1048 шт.
+3. Суміш "Малиш" молочна 350 г. з вівсяним борошном - 45 шт.
+4. Суміш "Малиш" молочна 350 г. з рисовим борошном - 10 шт.
+5. Суміш "Малиш" молочна 350 г. з гречаним борошном - 50 шт.
+Детально див. в додатковій Специфікації.
+Доставка за рахунок продавця.
+Надати документи:
+1. Виписка з Єдиного державного реєстру юридичних осіб та фізичних осіб-підприємців
+2. Довідка з Єдиного державного реєстру підприємств та організацій України (ЄДРПОУ)
+3. Реквізити
+4. Типовий договір
+5. Засвідчені належним чином копії відповідних сертифікатів якості/відповідності товару</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>2531</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2015-10-20T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2015-10-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:28.688932+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>8c1f6e1414524cb8be6b3b4cb32b38a5</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>a11728b1074144c6b08647abfccf8da3</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>1.Кури морожені - 250 кг.,   2.Масло вершкове 72,7 % жиру - 80,0 кг.,   3.Молоко 2,5% - 1000л., 4.Сметана 21% жиру- 30 шт. по 0,450гр в пакетах ,  5.Цукор-250 кг., 6.Повидло-15кг., 7  .Дріжджі-2 кг., 8. Томатна паста - 48 бан.,скло 0,5 гр. вага 0,485 гр.,   9.Зелений горошок - 24,0 бан. скло 0,510 гр.,  10.Цибуля – 80 кг.,  11.Морква – 120 кг.,  12.Картопля – 1000 кг.,  13.Буряк – 70 кг.,14.  Сухофрукти – 70 кг,  15. Кавовий напій – 3 кг.,16. Олія – 10 бут./1л.,17. Згущене молоко – 60 бан. металева  0,370 грн.,18.   Крупа гречана – 50 кг.,  19.Манна крупа – 50 кг.,  20. Крупа ячнева – 75 кг.,  21.Рис – 75 кг,  22.Пшоно – 75 кг.,  23.Макарони – 150 кг.,  24.Пластівці вівсяні «Геркулес» - 75 кг.,  25. Чай – 9,6 кг.,  26. Хліб Український столичний подовий 0,950 кг.- 450 од.,  27. Батони нарізні Київські,в/с 0,5 кг – 25 од.,  28.Хліб пшеничний традиційний подовий ,1с.,0,650 кг. 100,0 од.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>4095</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2015-10-27T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2015-10-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:29.640251+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>e7a1a12491be4e2ba83c3e5e107fb460</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>b6715bb53c5a4e9e872329355534e6a3</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Молоко питне пастеризоване  2,6%</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2015-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>смт.Миколаївка</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:59.418168+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>6c3f90f4770e469fa73d41bf4bd73848</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2685b4254fb74cb3811d79f350a83efa</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Молоко та вершки,рідини оброблені 10.51.1
+Молоко пастеризоване 2,5% - 520 л.
+1.Вимоги до продукції, що поставляється
+1.1. Загальні вимоги
+1.2. Товари, що постачаються повинні мати необхідні копії сертифікатів якості виробника, реєстраційне посвідчення та висновок державної санітарно-епідеміологічної експертизи,  або іншій подібний документ , що підтверджує відповідність товару вимогам, встановленим до нього загальнообов’язковими на території України нормами і правилами, повинен бути оформлений відповідно до вимог законодавства України.
+ 1.3. Термін постачання товарів: партіями по заявках Замовника з моменту укладання Договорю про закупівлю товарів за державні кошти до 31 грудня 2015 року.
+1.3. Умови постачання:
+1.3.1. доставка і розвантаження товару здійснюється спецтранспортом і силами за рахунок Учасника по заявці замовника за адресою: пр-т Комарова, 3, м. Київ, 03680, склад харчових продуктів.
+Наявність санітарного паспорту на транспортний засіб і санітарної книжки водія - експедитора обов’язково при постачанні товару.
+2. Вимоги до тавару
+2.1. Найменування товару і його технічні, якісні та кількісні характеристики
+Молоко та вершки,рідини оброблені 10.51.1 - 520 л.	Молоко пастеризоване , жирністю 2,5 % ,фасоване по 1 л в плівку, термін реалізації 5 діб .
+. Вимоги до кваліфікації учасників:
+-	Копія свідоцтва про державну реєстрацію(для юридичних осіб та суб’єктів підприємницької діяльності) (у разі наявності) або Виписка з Єдиного державного реєстру юридичної та фізичних осіб – підприємств із зазначенням відповідних відомостей.
+-	Копія довідки ЄДРПОУ (для юридичних осіб)
+-	Копія довідки про присвоєння ідентифікаційного коду(для фізичних осіб)
+-	Копія довідки про взяття на облік платника податків. 
+-	
+Інша інформація:
+Документи, що підтверджують відповідність вимогам до кваліфікації учасників та копія статуту (іншого установчого документу, а також іншого документу (за наявності), що підтверджують правомочність на укладення договору про закупівлю), в паперовому вигляді, завірені підписом та печаткою учасника, надаються замовнику переможцем під час укладання договору про закупівлю за вимогою замовника .</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>520</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2015-11-04T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:01.339392+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>b6ae955e78ad4dcbb9f007167c628ab2</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>15a63f1d03a347848eb7272cd58c0b00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2015-12-22T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>с.Стара Прилука</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:10.507374+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ef042b3e4def4b5cb965a46b11613b3f</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>967e04a4a0f24072952beb8c427a53b7</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Молоко коровяче питне пастеризоване 2,5% жиру. ТУ У 25027034-008-98 Склад: молоко коровяче незбиране, молоко коровяче нежирне. Поживна (харчова) цінність 100 г молока,г: жири- 2,5%, білки- 3,0, вуглеводи- 4,5. Без ГМО. Калорійність 100 г молока, ккал - 57. Маса нетто,г: 1000. Строк придатності не менше 5 діб. Доставка згідно телефонної заявки харчоблока. Контактна особа: 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:17.447236+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>22e90065611948368ebfc7e59a21a6b5</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>f452bac0d2264ecfb46585a835d2ff26</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Сметана 15% жирності. Склад: вершки пастерізовані, молочнокислі бактерії. ТУ У 25027034-009-99</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>400</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:18.915658+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>469fae136cd24b4181e1aa9eb0668618</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>966a0891cd444470a55961350d4b6df3</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>молоко сухе знежирене</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>15511300-6</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>200</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2015-11-12T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:41.034308+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>a36deb514d124e448b6a39977a3b215f</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>40fa66ec4ca2407ea81e2efd2bdb123e</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже </t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2015-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>м.Котовськ</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:10.496653+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>bd69cee6f0ad4904ab11f9ef5a4e1969</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>288b468d19ea46b8816f0351302f516d</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Молоко згущене фасоване ж/б 370 грам</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2015-11-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>м.Київ</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:12.642763+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9578,7 +10399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17055,6 +17876,642 @@
       <c r="K141" t="inlineStr">
         <is>
           <t>2026-01-19T04:20:09.315743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>5f647e4792954740877799c97a477841</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>UA-2015-10-09-000003</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:14.811378+02:00</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №6 Шевченківського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>26387019</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>9975</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>096cf02d4caf4544818091cbedc910fa</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>UA-2015-10-09-000277</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:24.747776+02:00</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>КУ "Першотравенська загальноосвітня спеціальна школа-інтернат"</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20250549</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>12624.8</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1469105c7b8748e69ade33bef8d01113</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UA-2015-10-12-000108</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:28.688932+02:00</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Центр первинної медико - санітарної допомоги № 3 Дарницького району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>30300749</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>27012</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>8c1f6e1414524cb8be6b3b4cb32b38a5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UA-2015-10-12-000141</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:29.640251+02:00</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Київський міський пологовий будинок № 1</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>01993859</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>51500</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>e7a1a12491be4e2ba83c3e5e107fb460</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UA-2015-10-15-000130</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:04:59.418168+02:00</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>КУ "Миколаївська спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>22509425</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>6c3f90f4770e469fa73d41bf4bd73848</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UA-2015-10-15-000185</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:01.339392+02:00</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №6</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>25680355</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>b6ae955e78ad4dcbb9f007167c628ab2</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>UA-2015-10-16-000019</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:10.507374+02:00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Староприлуцька спеціальна загальноосвітня школа - інтернат</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>24902380</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ef042b3e4def4b5cb965a46b11613b3f</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>UA-2015-10-16-000216</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:17.447236+02:00</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>16800</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>22e90065611948368ebfc7e59a21a6b5</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>UA-2015-10-16-000254</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:18.915658+02:00</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>11200</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>469fae136cd24b4181e1aa9eb0668618</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>UA-2015-10-19-000326</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:05:41.034308+02:00</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>відокремлений підрозділ „Рівненська АЕС” державного підприємства   „Національна атомна енергогенеруюча компанія “Енергоатом”</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>05425046</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>a36deb514d124e448b6a39977a3b215f</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UA-2015-10-21-000229</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:10.496653+02:00</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>КУ "Котовська загальноосвітня школа-інтернат I-II ступенів для дітей-сиріт і дітей, позбавлених батьківського піклування"</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20987480</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>bd69cee6f0ad4904ab11f9ef5a4e1969</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UA-2015-10-21-000290</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:12.642763+02:00</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна лікарня № 2</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>05415941</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:14:46.200920+00:00</t>
         </is>
       </c>
     </row>
@@ -17069,7 +18526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18968,6 +20425,164 @@
       </c>
       <c r="E72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:46+00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>{"bytes": 52781}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-20T04:15:27+00:00</t>
+          <t>2026-01-21T04:15:00+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282782.373001.1.944e0b6f52d7cd059c6a7cf44de9b330",
-  "updated_at": "2026-01-20T04:15:27.121666+00:00",
-  "pages_done": 225,
-  "tenders_scanned": 22500,
-  "tenders_fetched": 22500,
-  "milk_tenders": 152,
-  "milk_items": 158
+  "offset": "1478282934.105662.1.da436a5a634ba5d396a000ea7df2fbec",
+  "updated_at": "2026-01-21T04:15:00.194359+00:00",
+  "pages_done": 250,
+  "tenders_scanned": 25000,
+  "tenders_fetched": 25000,
+  "milk_tenders": 162,
+  "milk_items": 168
 }</t>
         </is>
       </c>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10388,6 +10388,585 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>b9d699a2d9c24885b8219c2d11f0eeda</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1e7be7c3ad4c43ddafad8b12b22260a3</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Сир  кисломолочний 9,5% жиру.Склад:молоко коров'яче  незбиране,молоко знежирене,закваска.Поживна(харчова)цінність в 100 г продукту:білків 16,7 г ; вуглеводів-2,0 г;жирів-9,5 г.Енергетична цінність(калорійність) 100 г продукту: 670 кДж (160 ккал).Строк придатночті -не більше ніж 7 діб. Контактна особа: 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>15542100-0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>350</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:22.653806+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>13d3e040487144a0b01f70f8500f5773</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>becc89cab4e54403ad249df82bae42be</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Кефір-Склад:молоко коров'яче незбиране,молоко знежирене,концентрат грибкрвої кефірної закваски.Кількусть життєздатних молочнокислих бактерій,КУО в 1см куб.,не менше,ніж 1*10 у сьомій степені.Повна (харчова)цінність 100г продукту (в  г): білки-2,90,жири-2,5,вуглеводи-3,90,Енергетична цінність (калорійність) 100 г продукту:208 кДж (50 ккал).Строк придатності не більше 5 діб.
+контактна особа 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>990</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:22.701902+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>facb61daaa4e47bfa05183f2486b8ca7</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>d2032d17149a4bcf93cb61dc9b99834b</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване питне 2,6-3,2% </t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2015-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2015-11-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>м. Ананьїв</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:23.127497+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>b8f76725b89e4baba4eca38be6356800</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4544bc9d7a2c470898f328a99a35c5b2</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>молоко згущене</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>200</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2015-11-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2015-11-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>м.Ананьїв</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:27.095083+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>f62509bcdf2d45cdb646ceedc55afac1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>bd3860cf51a348af93dc9021c1e24506</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>молоко згущене 8,5% жирності, код ДК 016-2010 – 10.51.5 вимоги-продукція повинна мати сертифікат якості. фасовкою 1кг</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>100</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2015-11-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2015-11-16T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:33.707854+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9e4f81cf6ca34e51b9413c57f8079a3c</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>36bdc0de2be34b679931818a5466accd</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>«Молоко та вершки, рідинні, обробленні» (молоко коров’яче, пастеризоване, рідке, 2,5% жирність, фасоване 0,5 літра, упаковано поліетилен), код 10.51.1 за ДК 016-2010</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>71450</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:21.569948+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>a42bd6bd1243441bbb9b09999459ef9c</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>71b35df3505b4f8fa1c1b07305e0534f</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>1.Кури морожені - 250 кг., 2.Масло вершкове 72,7 % жиру - 80,0 кг., 3.Молоко 2,5% - 1000л., 4.Сметана 21% жиру- 30 шт. по 0,450гр в пакетах , 5.Цукор-250 кг., 6.Повидло-15кг., 7 .Дріжджі-2 кг., 8. Томатна паста - 48 бан.,скло 0,5 гр. вага 0,485 гр., 9.Зелений горошок - 24,0 бан. скло 0,510 гр., 10.Цибуля – 80 кг., 11.Морква – 120 кг., 12.Картопля – 1000 кг., 13.Буряк – 70 кг.,14. Сухофрукти – 70 кг, 15. Кавовий напій – 3 кг.,16. Олія – 10 бут./1л.,17. Згущене молоко – 60 бан. металева 0,370 грн.,18. Крупа гречана – 50 кг., 19.Манна крупа – 50 кг., 20. Крупа ячнева – 75 кг., 21.Рис – 75 кг, 22.Пшоно – 75 кг., 23.Макарони – 150 кг., 24.Пластівці вівсяні «Геркулес» - 75 кг., 25. Чай – 9,6 кг.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>3577</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2015-10-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2015-10-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:29.968201+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>e45c3fd827054b48ae14185389e76725</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ac53db2e73284402a8e871b2e3e99e21</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>1.Молоко сгущене з цукром, жирність 8,5%, фасоване у ж/б,1/370 г.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>216</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2015-11-26T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2015-12-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:34.734179+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>6ece36ff64ca426ca46b786bc4b3c2ed</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4966aba34a644668ab94751781095cef</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Молочні продукти</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>1461</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>П'ятихатский р-н</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:08:10.294052+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7a838369aa3946c2ba4db17b0046d2f6</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>fcbb780f91014e45a5b9e0c175eedc1b</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване фасоване по 1 л</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>160</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:08:22.475924+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10399,7 +10978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18512,6 +19091,536 @@
       <c r="K153" t="inlineStr">
         <is>
           <t>2026-01-20T04:14:46.200920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>b9d699a2d9c24885b8219c2d11f0eeda</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UA-2015-10-21-000396</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:22.653806+02:00</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>22344</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>13d3e040487144a0b01f70f8500f5773</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UA-2015-10-21-000401</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:22.701902+02:00</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>12870</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>facb61daaa4e47bfa05183f2486b8ca7</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UA-2015-10-22-000004</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:23.127497+02:00</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>КУ "Комунальний заклад "Ананьївська загальноосвітня школа-інтернат І-ІІІ ступенів""</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20994698</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>21684</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>b8f76725b89e4baba4eca38be6356800</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>UA-2015-10-22-000098</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:27.095083+02:00</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>КУ "Комунальний заклад "Ананьївська загальноосвітня школа-інтернат І-ІІІ ступенів""</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20994698</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>24509.5</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>f62509bcdf2d45cdb646ceedc55afac1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>UA-2015-10-22-000247</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:06:33.707854+02:00</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Київська міська туберкульозна лікарня №1 з диспансерним відділенням</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>01993960</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9e4f81cf6ca34e51b9413c57f8079a3c</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>UA-2015-10-27-000065</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:21.569948+02:00</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>КП "Киевский Метрополитен"</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>03328913</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>332242.5</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>a42bd6bd1243441bbb9b09999459ef9c</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>UA-2015-10-27-000252</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:29.968201+02:00</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Київський міський пологовий будинок № 1</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>01993859</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>47700</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>e45c3fd827054b48ae14185389e76725</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>UA-2015-10-27-000361</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:07:34.734179+02:00</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Одеська філія Державного підприємства  «Адміністрація морських портів України» (адміністрація Одеського морського порту)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>38728457</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>2491.2</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>6ece36ff64ca426ca46b786bc4b3c2ed</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>UA-2015-10-29-000324</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:08:10.294052+02:00</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Державний професійно-технічний навчальний заклад "Західно-Дніпровський центр професійно-технічної освіти"</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>02541846</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>24328.9</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>7a838369aa3946c2ba4db17b0046d2f6</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>UA-2015-10-30-000225</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:08:22.475924+02:00</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Київська міська наркологічна клінічна лікарня "Соціотерапія"</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>05496862</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1760</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:14:19.426611+00:00</t>
         </is>
       </c>
     </row>
@@ -18526,7 +19635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20583,6 +21692,164 @@
       </c>
       <c r="E78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:15:27+00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>{"bytes": 58192}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,12 +420,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -451,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-21T04:15:00+00:00</t>
+          <t>2026-01-22T04:18:04+00:00</t>
         </is>
       </c>
     </row>
@@ -500,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478282934.105662.1.da436a5a634ba5d396a000ea7df2fbec",
-  "updated_at": "2026-01-21T04:15:00.194359+00:00",
-  "pages_done": 250,
-  "tenders_scanned": 25000,
-  "tenders_fetched": 25000,
-  "milk_tenders": 162,
-  "milk_items": 168
+  "offset": "1478283082.839698.1.5867ee034abb8587ebfe38e8868a431b",
+  "updated_at": "2026-01-22T04:18:04.359162+00:00",
+  "pages_done": 275,
+  "tenders_scanned": 27500,
+  "tenders_fetched": 27500,
+  "milk_tenders": 179,
+  "milk_items": 185
 }</t>
         </is>
       </c>
@@ -522,71 +510,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tender_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>item_key</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>classification_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>classification_scheme</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>unit_name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unit_code</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>delivery_start</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>delivery_end</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>locality</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>dateModified</t>
         </is>
@@ -10967,6 +10955,980 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>6cd373f98d524705912c92adeb1b663f</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>55ee3ba6da384a3a90c734af75a95139</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Кефір-Склад:молоко коров'яче незбиране,молоко знежирене,концентрат грибкрвої кефірної закваски.Кількусть життєздатних молочнокислих бактерій,КУО в 1см куб.,не менше,ніж 1*10 у сьомій степені.Повна (харчова)цінність 100г продукту (в г): білки-2,90,жири-2,5,вуглеводи-3,90,Енергетична цінність (калорійність) 100 г продукту:208 кДж (50 ккал).Строк придатності не більше 5 діб. контактна особа 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.118211+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>b3ccbb0baf144e8da1ac7b41732e3174</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>a5ec270c1fd741039851d2fa1aed14b7</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Молоко коровяче питне пастеризоване 2,5% жиру. ТУ У 25027034-008-98 Склад: молоко коровяче незбиране, молоко коровяче нежирне. Поживна (харчова) цінність 100 г молока,г: жири- 2,5%, білки- 3,0, вуглеводи- 4,5. Без ГМО. Калорійність 100 г молока, ккал - 57. Маса нетто,г: 1000. Строк придатності не менше 5 діб. Доставка згідно телефонної заявки харчоблока. Контактна особа: 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.322265+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>56ecb00e992d495ebf3a8d669043ef36</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>c15df02fe31146019e7b22b4e4c15f84</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Сир кисломолочний 9,5% жиру.Склад:молоко коров'яче незбиране,молоко знежирене,закваска.Поживна(харчова)цінність в 100 г продукту:білків 16,7 г ; вуглеводів-2,0 г;жирів-9,5 г.Енергетична цінність(калорійність) 100 г продукту: 670 кДж (160 ккал).Строк придатночті -не більше ніж 7 діб. Контактна особа: 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>15542100-0</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>760</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.413992+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ed1a860939f44996bc8ea47e2697853a</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>00890f7b051846bea531b96273bbfd25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Сметана 15% жирності. Склад: вершки пастерізовані, молочнокислі бактерії. ТУ У 25027034-009-99</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>580</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.421679+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>89811135ab98445090b905c38aec1a77</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>22803f2aa4c94fa0a1ba142c80102c53</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Цукерки в коробці «Пташине молоко» 200гр. ТМ «Рошен»</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>15842000-2</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>150</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2015-11-04T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2015-11-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:12.771841+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>5a1775b171d746ad862a621e8f42dcb0</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>703e3f8e61db4507b543d9b3f36c1ed6</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Борошно-50кг, крупа гречана-30кг,макаронні вироби-30кг, цукор-50кг, олія-50бут, молоко згущене-19бан, печиво-30кг, томатна паста-20бан.(детально-в документації)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>15610000-7</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>190</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2015-11-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2015-11-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Житомир</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:41.439540+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>a7426e4926934108ab043e4aece53161</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4846d0732bf848df81a8fb4f6b717da9</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Сметана 15% жирності. Склад: вершки пастерізовані, молочнокислі бактерії. ТУ У 25027034-009-99
+Всі  питання 067-225-15-25</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>560</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:44.950357+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>bdd3772058e944cca122964f2d0edd41</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>60f92bcc98d440cb9ec740b5c9949ad8</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>молоко 2,6 % жиру пет/пл. 900 г</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>492</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:49.359827+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>e48a6ec00b6a40b8b275396fb454ef94</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>9d7c3a55a3cc46b5a2eb8d1feaf663a0</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>10.51.5 Продукти молочні, інші (10.51.51-08.00 спецхарчування)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1190</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:17.099558+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>62126080d2a343f98299680d0f918c93</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>e56170a6db5349eea6dda4f26ef320c3</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Сир кисломолочний 18 % жиру. ДСТУ 4554-2006 Склад продукту :молоко нормалізоване, закваска, кальцій хлористий, сичужний фермент тваринного походження .Поживна(харчова)цінність в 100 г продукту:білків 14.0 г ; вуглеводів-1.3 г;жирів-18.0 г. Енергетична цінність(калорійність) 100 г продукту: 226 ккал.Строк придатночті -не більше ніж 7 діб. Контактна особа: 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>15542100-0</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>760</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:25.900440+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>c95f70ed22ed4b04956a8aadee03424a</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>069de3e4126f4f2db1d86d9b93b9461a</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Засіб для чищення з відбілюючим ефектом,фасований 0,500л., торгова марка «Cif Creame»</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>39800000-0</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>9</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2015-11-24T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2015-11-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:34.014298+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>6a82d097752c4223ba7c2efccde132f9</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>bd69efb270c3419ab0525f42e09af786</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Продукти готові для дитячого та дієтичного харчування</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>200</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2015-11-20T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2015-11-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>днепропетровск</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:36.535052+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>75a066ae6b19458a9ca26a4cd126bae3</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>8d040f7342f9458b95e92a35f2481e71</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Продукти готові для дитячого та дієтичного харчування</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>160</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2015-11-20T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2015-11-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>днепропетровск</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:37.044601+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>148ee8241c53400dab0a77ca6197d453</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>842306becc384d83971113efe797494f</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Піпетка Пастера поліетиленова (стерильна) 160 мм; 3,0 мл градуйована з поділками 0,5 мл. Для взяття крові з пальця у донора</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>38437000-7</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2015-11-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2015-12-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:54.708994+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>44dc84dd176443ee9a6b4aa3cfa4a60f</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>c48dd3482f7e4a608b70db4fa82c3a68</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Молоко коровяче питне пастеризоване 2,5% жиру. Маса нетто,г: 1000л. та 0,500л.Упаковка полиетилен.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2015-11-20T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2015-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:55.858865+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>14af3ca67bf844b2ad4fe5122f716f5f</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>f9964312795f407388af0ab881382f76</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Крупи: гречана-24 кг, рисова-17 кг, пшенична-18 кг, ячна-13 кг; макарони-18 кг; олія соняшникова-12 л; масло вершкове-22 кг; кава-2 кг; хліб-208 кг, булочки-12 кг, печиво-8 кг; борошно-8 кг; молоко-108 л, сир кисломолочний-8 кг, сир твердий-7 кг, сир плавлений-9 кг, йогурт-41 л, кефір-50 л, сметана-3 л; м’ясо св.-23 кг, м’ясо ял.-4 кг,м’ясо курки-79 кг, філе курине-25 кг; риба с/м-22 кг; ковбаса варена-5 кг, сосиски- 12 кг; сік фруктовий-31 л, кисіль фруктовий-2 кг</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>28</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2015-11-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2015-12-25T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>смт. Софіївка</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:17.299589+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2dd7eb10496846ada77b0c2538698dc1</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>a0d077754c3d4d41ac187f0e7b007ed5</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>молоко згущене цільне жб банка 370-380грам</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>800</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2015-11-18T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:18.005468+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10978,61 +11940,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tender_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tenderID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dateModified</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>procurementMethodType</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>procuringEntity_name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>procuringEntity_id</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>value_amount</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>value_currency</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>value_vatIncluded</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>fetched_at</t>
         </is>
@@ -19621,6 +20583,907 @@
       <c r="K163" t="inlineStr">
         <is>
           <t>2026-01-21T04:14:19.426611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>6cd373f98d524705912c92adeb1b663f</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>UA-2015-11-03-000488</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.118211+02:00</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>14598</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>b3ccbb0baf144e8da1ac7b41732e3174</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>UA-2015-11-03-000494</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.322265+02:00</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>28233</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>56ecb00e992d495ebf3a8d669043ef36</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>UA-2015-11-04-000003</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.413992+02:00</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>32746</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ed1a860939f44996bc8ea47e2697853a</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>UA-2015-11-04-000004</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:11.421679+02:00</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>14598</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>89811135ab98445090b905c38aec1a77</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>UA-2015-11-04-000051</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:12.771841+02:00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Центр соціально-психологічної реабілітації дітей та молоді з функціональними обмеженнями в Оболонському районі міста Києва</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>38511264</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>5a1775b171d746ad862a621e8f42dcb0</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>UA-2015-11-05-000174</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:41.439540+02:00</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Державний професійно-технічний навчальний заклад "Житомирське вище професійне училище сервісу і дизайну"</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>02543408</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>a7426e4926934108ab043e4aece53161</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>UA-2015-11-05-000229</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:44.950357+02:00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>14096</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>bdd3772058e944cca122964f2d0edd41</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>UA-2015-11-05-000335</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:09:49.359827+02:00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Київмедспецтранс</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>01993807</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>4750</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>e48a6ec00b6a40b8b275396fb454ef94</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UA-2015-11-09-000036-a</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:17.099558+02:00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ  "Південна електроенергетична система" державного підприємства "Національна енергетична компанія "Укренерго"</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>23208938</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>20792.5</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>62126080d2a343f98299680d0f918c93</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>UA-2015-11-09-000058-a</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:25.900440+02:00</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>32746</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>c95f70ed22ed4b04956a8aadee03424a</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>UA-2015-11-09-000135</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:34.014298+02:00</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти Навчально-реабілітаційний центр Горлиця ДОР</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>24238640</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>4483</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6a82d097752c4223ba7c2efccde132f9</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>UA-2015-11-09-000156</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:36.535052+02:00</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>КУ "ДНІПРОПЕТРОВСЬКА ДИТЯЧА МІСЬКА КЛІНІЧНА ЛІКАРНЯ № 6 ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>01985127</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>75a066ae6b19458a9ca26a4cd126bae3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>UA-2015-11-09-000161</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:37.044601+02:00</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>КУ "ДНІПРОПЕТРОВСЬКА ДИТЯЧА МІСЬКА КЛІНІЧНА ЛІКАРНЯ № 6 ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>01985127</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>148ee8241c53400dab0a77ca6197d453</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>UA-2015-11-10-000130-a</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:54.708994+02:00</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>44dc84dd176443ee9a6b4aa3cfa4a60f</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>UA-2015-11-10-000152</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:10:55.858865+02:00</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>КУ " Днепропетровская шестая городская клиническая больница Днепропетровского обласного совета"</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>01984441</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>28300</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>14af3ca67bf844b2ad4fe5122f716f5f</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>UA-2015-11-11-000103</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:17.299589+02:00</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ДПТНЗ СОФІЇВСЬКИЙ ПРОФЕСІЙНИЙ ЛІЦЕЙ</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>21902126</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>22900</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2dd7eb10496846ada77b0c2538698dc1</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>UA-2015-11-11-000108-a</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:18.005468+02:00</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №12</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>25680639</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>14900</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:17:26.946376+00:00</t>
         </is>
       </c>
     </row>
@@ -19635,31 +21498,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ts</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>details</t>
         </is>
@@ -21849,6 +23712,164 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>{"bytes": 61242}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:04+00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:04+00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:05+00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:05+00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:05+00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-22T04:18:04+00:00</t>
+          <t>2026-01-23T04:13:09+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283082.839698.1.5867ee034abb8587ebfe38e8868a431b",
-  "updated_at": "2026-01-22T04:18:04.359162+00:00",
-  "pages_done": 275,
-  "tenders_scanned": 27500,
-  "tenders_fetched": 27500,
-  "milk_tenders": 179,
-  "milk_items": 185
+  "offset": "1478283235.865606.1.1df811d9ceaa002689688b6883b115d4",
+  "updated_at": "2026-01-23T04:13:09.631553+00:00",
+  "pages_done": 300,
+  "tenders_scanned": 30000,
+  "tenders_fetched": 30000,
+  "milk_tenders": 193,
+  "milk_items": 199
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11929,6 +11929,878 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>63cad8f7fc6c47d6a0898b0126794194</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>eb6ae3fdf6c6428188ae17a838504f6a</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>молоко -1000л;сметана-50 кг;сир кисломолочний-50 кг;</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>03142000-8</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2015-12-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Николаевка</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:28.792013+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>546b6ee61ba84367a8021c2f0f3c62a7</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>455d75bfe3374b5ba574e66fe359396a</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Молоко та вершки,рідини оброблені 10.51.1
+Кількість товарів: Молоко пастеризоване 2,5% - 800 л.
+Технічні вимоги до товару: Молоко та вершки,рідини оброблені 10.51.1
+1.Вимоги до продукції, що поставляється
+1.1. Загальні вимоги
+1.2. Товари, що постачаються повинні мати необхідні копії сертифікатів якості виробника, або іншій подібний документ , що підтверджує відповідність товару вимогам, встановленим до нього загальнообов’язковими на території України нормами і правилами, повинен бути оформлений відповідно до вимог законодавства України.
+ 1.3. Термін постачання товарів: партіями по заявках Замовника з моменту укладання Договорю про закупівлю товарів за державні кошти до 31 грудня 2015 року.
+1.3. Умови постачання:
+1.3.1. доставка і розвантаження товару здійснюється спецтранспортом і силами за рахунок Учасника по заявці замовника за адресою: пр-т Комарова, 3, м. Київ, 03680, склад харчових продуктів.
+Наявність санітарного паспорту на транспортний засіб і санітарної книжки водія - експедитора обов’язково при постачанні товару.
+2. Вимоги до товару
+2.1. Найменування товару і його технічні, якісні та кількісні характеристики
+Молоко та вершки,рідини оброблені 10.51.1- 800 л.Молоко пастеризоване , жирністю 2,5 % ,фасоване по 1 л в плівку, термін реалізації 5 діб 
+Вимоги до кваліфікації учасників:
+-	 Цінова пропозиція.
+-	Копія свідоцтва про державну реєстрацію(для юридичних осіб та суб’єктів підприємницької діяльності) (у разі наявності) або Виписка з Єдиного державного реєстру юридичної та фізичних осіб – підприємств із зазначенням відповідних відомостей.
+-	Копія довідки ЄДРПОУ (для юридичних осіб)
+-	Копія довідки про присвоєння ідентифікаційного коду(для фізичних осіб)
+-	Копія довідки про взяття на облік платника податків. 
+Інша інформація:
+Документи, що підтверджують відповідність вимогам до кваліфікації учасників та копія статуту (іншого установчого документу, а також іншого документу (за наявності), що підтверджують правомочність на укладення договору про закупівлю), в паперовому вигляді, завірені підписом та печаткою учасника, надаються замовнику переможцем під час укладання договору про закупівлю за вимогою замовника .</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>800</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2015-12-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:36.496822+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2d80972d148340e0ac6a6e6ee94e9872</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>e9fc41c97f2f4651969b8284ea3bc685</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Молоко ультрапастеризоване вище 2,5% жирністю упаковка 1,5л тетрапак, без сухого молока</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2015-12-03T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2015-12-24T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:47.585393+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>96964c692ef342cebd10001c8c01f94a</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>d5caec5d76ab447ea73ff60f1d527f05</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>молоко 2,6 % жиру пет/пл. 900 г</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>492</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2015-12-03T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:57.002829+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>499ac16eeb2f43328945b83683c1cda2</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>fb285d2c459e4ef580295589d1ca2bd1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10.51.5 «Продукти молочні, інші (10.51.51-04.00 молоко згущене на І квартал 2016 року)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>2070</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:57.920659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>0667812d87ed4c1cb619fa09b9271d30</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>c1d14bb898614a6a8aee1bed06331bfa</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>10.51.1 "Молоко та вершки, рідинні, оброблені”</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>100</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:04.311191+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>6af43219678047aeabeab189b88c1dcb</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>91d2571406ec48f981bd62401a820e48</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Запропонований учасником товар за своїми властивостями повинен відповідати наступним вимогам:
+Склад: борошно пшеничне, цукор, жир кулінарний, яйця курячі, молоко сухе незбиране
+Поживна харчова цінність не менше 100гр.: білки- 7,9 г, жири-10,5 г., вуглеводи- 71,2 г
+Енергетична цінність (калорії) не менше: 411 ккал/1720 кДж
+Печиво у своєму складі не повинно мати генетично модифікованих організмів (ГМО).
+Вимоги до температури подальшого зберігання: зберігання за температури: (18±5°С), вологість повітря не більше 75%.
+Термін зберігання: не менше 9 місяців (на момент поставки термін придатності повинен становити не менше 80% від дати виготовлення)
+Дата виготовлення і пакування вказана на упакованих пачках. ДСТУ 3781
+Фасовка в картонних коробках не більше 4,5 кг
+Вага 1 пачки печива 50 г</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>15821200-1</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>315</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2015-11-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2015-12-20T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:11.570650+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>af24f90b5b6d44f88d7b99a7f99c4e0e</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>79c630b84f6f47a1afec478a90630dc7</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Молоко сгущене – 700 кг; 8,5% жирності , фасоване у залізні банки. (повинні надходити в бляшаних банках не менше 0,380 кг. Не допускаються банки пробиті, сильно деформовані, з іржею, з неприємним запахом та іншими недоліками.)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>700</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2015-11-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:25.944800+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>a21a71d90f31411e84addaefd3558cdb</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>a03684f5b7bb48a7aba7557db723a699</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Згущене молоко незбиране з цукром, неварене, 8,5% у банках по 0,370 кг
+Доставка здійснюється одноразовою партією, її вартість та вартість розвантажувальних робіт на території Замовника включена в вартість товару.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>95</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2015-11-26T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:55.198642+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>a077af968ec248abaa4ad1e5c0ea234c</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1fb4759fc9924893857e98adf94d4931</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Фенилкетанурия питание (Ф-АМ -2 500 г.)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>4</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:55.220879+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>f5a565e1bc244355a4ce5308bde6fe38</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>d637160af114462a94b888f3b8dfff90</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване по 1 л</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>160</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:01.480875+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>558b5042dcbd4b1dbabd8e268c262057</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>404a2afdf7534b87a99077be23eafc29</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Масло вершкове, молоко цільне, сир кисломолочний, сир твердий, сметана, ряженка</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>2046</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2016-01-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2016-01-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:01.890836+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>48e168c20948455fb55097f53328d821</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>afb892042c274211aa68c091c546ae6b</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жир., фасування по 1 кг  - 1600 кг. Скорочена закупівля в зв"язку з нагальною потребою для безперебійного лікувального процесу в лікарні</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2015-11-25T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2015-12-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:45.039442+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1bc3b6049d97484e854d7021a21bf0be</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>70bbad0a9bdd40fd998a86f6820b4fb2</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Сметана фасована по 0,45 - 0,500 кг , масова частка жиру - 15% - 160,0 кг. Скорочена закупівля в зв"язку з нагальною потребою для безперебійного лікувального процесу в лікарні</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>160</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2015-11-25T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2015-12-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:47.931990+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11940,7 +12812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21484,6 +22356,748 @@
       <c r="K180" t="inlineStr">
         <is>
           <t>2026-01-22T04:17:26.946376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>63cad8f7fc6c47d6a0898b0126794194</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>UA-2015-11-12-000011</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:28.792013+02:00</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>КУ "Миколаївська спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>22509425</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>15400</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>546b6ee61ba84367a8021c2f0f3c62a7</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>UA-2015-11-12-000075-a</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:36.496822+02:00</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №6</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>25680355</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>9800</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2d80972d148340e0ac6a6e6ee94e9872</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>UA-2015-11-12-000176</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:47.585393+02:00</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровський навчально-реабілітаційний центр № 1 Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20199883</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>96964c692ef342cebd10001c8c01f94a</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>UA-2015-11-13-000012</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:57.002829+02:00</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Київмедспецтранс</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>01993807</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>4750</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>499ac16eeb2f43328945b83683c1cda2</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>UA-2015-11-13-000020-b</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:11:57.920659+02:00</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ "Південно - Західна електроенергетична система" державного підприємства «Національна енергетична компанія «УКРЕНЕРГО» "</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>21725012</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>26532</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>0667812d87ed4c1cb619fa09b9271d30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>UA-2015-11-13-000066-b</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:04.311191+02:00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>КП "Киевский Метрополитен"</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>03328913</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>123.24</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>6af43219678047aeabeab189b88c1dcb</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>UA-2015-11-13-000122-b</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:11.570650+02:00</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>12366</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>af24f90b5b6d44f88d7b99a7f99c4e0e</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>UA-2015-11-16-000069-a</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:25.944800+02:00</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Управління освіти Подільської районної в м.Києві державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>37393777</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>30800</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>a21a71d90f31411e84addaefd3558cdb</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>UA-2015-11-17-000090-b</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:55.198642+02:00</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №7 Печерського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>01993842</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>1710</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>a077af968ec248abaa4ad1e5c0ea234c</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>UA-2015-11-17-000091</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:12:55.220879+02:00</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>КЗ "Дніпропетровський центр первинної медико-санітарної допомоги №2"</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>37899741</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>f5a565e1bc244355a4ce5308bde6fe38</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UA-2015-11-17-000141</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:01.480875+02:00</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Київська міська наркологічна клінічна лікарня "Соціотерапія"</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>05496862</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>558b5042dcbd4b1dbabd8e268c262057</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UA-2015-11-17-000144</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:01.890836+02:00</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Навчально-реабілітаційний центр № 12" ДОР"</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>20199239</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>67573.64999999999</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>48e168c20948455fb55097f53328d821</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>UA-2015-11-19-000024-a</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:45.039442+02:00</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №18</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>01993776</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>20880</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1bc3b6049d97484e854d7021a21bf0be</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>UA-2015-11-19-000042-b</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:13:47.931990+02:00</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №18</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>01993776</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>5644</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:12:33.615612+00:00</t>
         </is>
       </c>
     </row>
@@ -21498,7 +23112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23871,6 +25485,164 @@
       </c>
       <c r="E90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-01-22T04:18:05+00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>{"bytes": 66233}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:09+00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:09+00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-23T04:13:09+00:00</t>
+          <t>2026-01-24T04:06:52+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283235.865606.1.1df811d9ceaa002689688b6883b115d4",
-  "updated_at": "2026-01-23T04:13:09.631553+00:00",
-  "pages_done": 300,
-  "tenders_scanned": 30000,
-  "tenders_fetched": 30000,
-  "milk_tenders": 193,
-  "milk_items": 199
+  "offset": "1478283381.780455.1.c9915bd5cb221959b52ad251823478a9",
+  "updated_at": "2026-01-24T04:06:52.088446+00:00",
+  "pages_done": 325,
+  "tenders_scanned": 32500,
+  "tenders_fetched": 32500,
+  "milk_tenders": 212,
+  "milk_items": 223
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12801,6 +12801,1525 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2eb943ea6b1940f29a8ca8a1cf6b28d2</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>780040b13c1b457195d496f6708ff068</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>1.Кури морожені(10.12.2) –479,00кг;  
+2.Масло вершкове (10.51.3) 72,7%--110,00 кг.; 
+3. Олія рослинна (10.41.5) фас.920,00г.(1л.)—15 б.; 
+4. Молоко 2,5 %(10.51.1)--900,00л.; 
+5.Сметана21% жиру по 0,450 гр.в пакетах (10.51.5)40,00пак; 
+6.Борошно (10.61.2)--- 70,00кг;
+7.Крупа гречана (10.61.3)---100,00кг;
+8.Крупа манна(10.61.3)---50,00кг; 
+9.Крупа ячнева (10.61.3)---75,00кг;
+10.Рис(10.61.3)---100,00кг;
+11.Пшоно(10.61.3)---100,00кг;
+12.Пластівці вівсяні «Геркулес»(10.61.3)---100,00кг;
+13.Вермішель(10.73.1)---200,00кг;
+14.Цукор(10.81.1)---300,00кг; 
+15.Сухофрукти(10.39.2)---100,00кг;
+16.Повидло (10.39.2)---30,00кг; 
+17.Чай(10.83.1)-14,00кг;
+18.Картопля(01.13.5)---1800,00кг;
+19.Цибуля(01.13.4)---100,00кг;
+20. Морква(01.13.4)---100,00кг;
+21.Згущене молоко 0,370 грн(10.51.5)---90,00бан,
+22.Буряк(01.13.7)---50,00кг,
+23. Дріжджі  (10.89.1)---1,0 кг,
+24. Зелений горошок (скло -0,510 гр.)(10.39.1)---12 бан.,
+25. Томатна паста (скло-0,485гр.)(10.39.1)---36 бан.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2015-11-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:08.802151+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>65ed114b15e84df0966c27322329e65f</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>3cc0c63e9c2c4b79a5c34662ac0b1d80</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2.Піпетка Пастера 280мм (скло)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>33793000-5</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>8</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2015-12-02T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:11.684884+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>5d12429019354e1bb2316135588e4961</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>367203a14435416986913bcf90fce800</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Сметана фасована по 0,450-0,500 кг, масова частка жиру становить 20%	 35 кг
+Кефір, фасований по 0,9 кг в пакеті, масова частка жиру-2,5%	 100 кг</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>135</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2015-11-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:12.414794+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>cd4886c76a8b4b4a8ea162a7d128e95e</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>fd37f255971149c19bd8cc6cb570d1e0</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Молоко фасоване 1 л п/е 2.5% 	320 л</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>320</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2015-11-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:13.319052+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6375b2c711dc406b838b4658159d6986</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>418fe3e178a6489d8c2b30c8e5d0c872</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Сметана фасована по 0,450- масова частка жиру становить 20%. - 24 уп., вітчизняного виробництва</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>24</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2015-12-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:24.149113+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>de39e8a7aae54f19a2f74f3d713e6295</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>29fb0a04e05c496aa1ff013d7200feb3</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Молоко згущене незбиране з цукром (8,5%, 380-400 гр., ж/б)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2015-11-26T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:35.046994+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>3a530355613743539c8b3b3eae79b29e</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>e4327e37e7a54065b4333843fd3fed12</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Молоко 2,6% п/е</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>15544000-3</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:42.784555+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>3a530355613743539c8b3b3eae79b29e</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>bc61b13522134ca78c7fc14fcf700f80</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Молоко згущене 7,5% 7,8 кг</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>15544000-3</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>100</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:42.784555+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>3d989d0c73994eedb14940f19d4ec01a</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>720725055ec346d7be1187ae0ddf1c65</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>код ДК 016:2010 – 10.20.2 «Риба, оброблена чи законсервована іншим способом; ікра осетрових та замінники ікри» (консерва рибна Сардина); 
+код ДК 016:2010 – 10.51.5 «Продукти молочні, інші» (молоко згущене); 
+код ДК 016:2010 – 10.39.2 «Плоди й горіхи, оброблені та законсервовані» (родзинки, чорнослив, курага);
+код ДК 016:2010 – 10.72.1 «Вироби хлібобулочні, зниженої вологості, та кондитерські, борошняні, тривалого зберігання» (печиво-сендвіч);
+код ДК 016:2010 – 10.82.1 «Какао терте, какао-масло, жири й олія, какао-порошок» (какао);
+код ДК 016:2010 – 10.83.1 «Чай і кава, оброблені» (чай, кава, напій кавовий).</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>560</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2015-12-20T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Енергодар</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:43.610472+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>dd50de479060499394de5a3104f1f0b3</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>51a88eedd0c74867a43e8d0df08a2938</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Молоко, 10.51.1, молоко з умістом жиру , неконцентроване</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2015-12-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2015-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:47.183391+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>921f36e10f23449aa198d39feff37523</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ded60d36e5b047f5be10a4b7c1ea0756</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха "Малютка" від народження без варки по 350грам.</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>27</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2015-12-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2015-12-15T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:48.216879+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>921f36e10f23449aa198d39feff37523</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>62e6297b5e844efd88557b18673c3d82</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха "Малиш" без варки з 3місяців по 350грам.</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>173</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2015-12-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2015-12-15T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:48.216879+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>fa2bf99da44d4eca9c799a55bbb8a2d5</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>aea5f78d2c43496aa9ab6aaf0536c28c</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Молоко коров´яче, фасоване в плівку, жирн. 2,5%, пастеризоване, 1л</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>750</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2015-12-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:50.071206+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>99586a9eb8534577972bfa978ab0ce7b</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>78e8bf144d6c401194847b98c86b4b5a</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Маргарин ваговий Майонез  2,9 кг Сир «Фета» Сир»Бринза» Вершки порційні 10%</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>15332410-1</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.016391+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>208f39450a14411c80c25ae55ff66714</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>01d95bf35c364e29b984ad9b1cda1f4a</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малютка» З цукром 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>30</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2015-12-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.059455+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>208f39450a14411c80c25ae55ff66714</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>9543e5e29bd249a784e5532d1eb25bc6</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малиш» швидкого приготування З гречаним борошном 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>250</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2015-12-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.059455+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>208f39450a14411c80c25ae55ff66714</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>8a2063c406ef4be0937551545197d788</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малиш» швидкого приготування З вівсяним борошном 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>250</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>2015-12-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.059455+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>208f39450a14411c80c25ae55ff66714</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>0b691a34485d4bc0bc4fd68d8e6b4b5d</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Каша молочна «Малишка» Суміш рису, кукурудзи, вівса, гречки 250 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>300</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2015-12-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.059455+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>00edabe673384c229527cfc7a47956fc</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>4826ac59f3aa4bc182d97356bc8b8677</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>піпетка Пастеровська</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>33790000-4</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>500</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2015-11-30T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2015-12-04T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:04.625797+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>788199b378d243179a62ccdad458fcd4</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>6c678c19e8e64d029cc769693aad9e2e</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Запропонований учасником товар за своїми властивостями повинен відповідати наступним вимогам:
+Склад: борошно пшеничне, цукор, жир кулінарний, яйця курячі, молоко сухе незбиране
+Поживна харчова цінність не менше 100гр.: білки- 7,9 г, жири-10,5 г., вуглеводи- 71,2 г
+Енергетична цінність (калорії) не менше: 411 ккал/1720 кДж
+Печиво у своєму складі не повинно мати генетично модифікованих організмів (ГМО).
+Вимоги до температури подальшого зберігання: зберігання за температури: (18±5°С), вологість повітря не більше 75%.
+Термін зберігання: не менше 9 місяців (на момент поставки термін придатності повинен становити не менше 80% від дати виготовлення)
+Дата виготовлення і пакування вказана на упакованих пачках. ДСТУ 3781
+Фасовка в картонних коробках не більше 4,5 кг
+Вага 1 пачки печива 50 г</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>15821200-1</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>315</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2015-12-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2015-12-17T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:19.955023+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>6de85358a8834abc98e4a043590ef3a2</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>290c60e09b974d1a90d85a147435a85e</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Згущене молоко незбиране з цукром, неварене, 8,5% у банках по 0,370 кг Доставка здійснюється одноразовою партією, її вартість та вартість розвантажувальних робіт на території Замовника включена в вартість товару.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>150</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2015-12-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:32.857337+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2e12cd7834db449f9883d36af2f9c037</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>7058168feea846a39ff50954d518508e</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Картопля 
+Капуста
+Буряк
+Цибуля
+Морква
+Птиця (окорок)
+Молоко 2,5% жирності
+Творог 5%
+Сметана 20%
+Крупа гречана (січка)
+Крупа манна
+Крупа ячнева
+Макаронні вироби
+Рис
+Пшоно
+Горох, ваговий
+Вівсяні пластівці Геркулес
+Цукор
+Сухофрукти (яблука, груші)
+Чай чорний фас. 400г.
+Масло вершкове, моноліт
+Масло рослинне (1л=920г)
+Яйца
+Паста томатна
+Сіль</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2015-12-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:05.338231+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>22dd1b9b56ae451b91343f2181ba1c9a</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>fec8d521cac54f8c9bd37e7b981c3fbb</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - плівка по 1 л.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>680</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:16.139215+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2178e273bfd4400087266f73bb00256d</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>9a0307b59c9449b392aa53f66c50c45e</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха «Малютка»</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>150</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:16.158231+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12812,7 +14331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23098,6 +24617,1013 @@
       <c r="K194" t="inlineStr">
         <is>
           <t>2026-01-23T04:12:33.615612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2eb943ea6b1940f29a8ca8a1cf6b28d2</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>UA-2015-11-20-000013-b</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:08.802151+02:00</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Київський міський пологовий будинок № 1</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>01993859</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>66900</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>65ed114b15e84df0966c27322329e65f</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>UA-2015-11-20-000031</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:11.684884+02:00</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ТМО "ДЕРМАТОВЕНЕРОЛОГІЯ" у місті Києві</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>05416248</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>63508.68</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>5d12429019354e1bb2316135588e4961</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>UA-2015-11-20-000036-b</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:12.414794+02:00</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №6 Шевченківського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>26387019</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>2625</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>cd4886c76a8b4b4a8ea162a7d128e95e</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>UA-2015-11-20-000045-a</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:13.319052+02:00</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №6 Шевченківського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>26387019</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>3520</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>6375b2c711dc406b838b4658159d6986</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>UA-2015-11-20-000087-a</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:24.149113+02:00</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 5 Святошинського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>00185011</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>353</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>de39e8a7aae54f19a2f74f3d713e6295</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>UA-2015-11-22-000005-b</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:35.046994+02:00</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Загальноосвітній навчальний заклад "Київський спортивний ліцей-інтернат"</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>23516367</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>3a530355613743539c8b3b3eae79b29e</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000061-a</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:42.784555+02:00</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Державне підприємство Дарницький вагоноремонтний завод</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>14294471</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>79987.2</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>3d989d0c73994eedb14940f19d4ec01a</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000068-b</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:43.610472+02:00</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ВП Запорізька АЕС ДП НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>19355964</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>24965</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>dd50de479060499394de5a3104f1f0b3</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000098</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:47.183391+02:00</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Чорнянська спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>20989125</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>64409.5</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>921f36e10f23449aa198d39feff37523</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000104</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:48.216879+02:00</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ДНІПРОПЕТРОВСЬКИЙ ЦЕНТР ПЕРВИННОЇ МЕДИКО-САНІТАРНОЇ ДОПОМОГИ №4 </t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>37899673</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>10508</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fa2bf99da44d4eca9c799a55bbb8a2d5</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000122</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:50.071206+02:00</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №9 Подільського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>05492290</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>99586a9eb8534577972bfa978ab0ce7b</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000145-a</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.016391+02:00</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Державне підприємство Дарницький вагоноремонтний завод</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>14294471</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>1623526.8</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>208f39450a14411c80c25ae55ff66714</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>UA-2015-11-23-000146</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:14:54.059455+02:00</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровський центр первинної медико-санітарної допомоги № 9"</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>37899715</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>27551</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>00edabe673384c229527cfc7a47956fc</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>UA-2015-11-24-000048</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:04.625797+02:00</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>КУ "Міжобласний центр медичної генетики і пренатальної діагностики"</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>25843751</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>4810</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>788199b378d243179a62ccdad458fcd4</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>UA-2015-11-24-000118-a</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:19.955023+02:00</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>12366</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>6de85358a8834abc98e4a043590ef3a2</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>UA-2015-11-25-000035-a</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:15:32.857337+02:00</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №7 Печерського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>01993842</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2e12cd7834db449f9883d36af2f9c037</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>UA-2015-11-26-000074-b</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:05.338231+02:00</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Київський міський центр репродуктивної та перинатальної медицини</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>02124976</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>103090</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>22dd1b9b56ae451b91343f2181ba1c9a</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>UA-2015-11-26-000168-b</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:16.139215+02:00</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>8561.200000000001</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2178e273bfd4400087266f73bb00256d</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>UA-2015-11-26-000169</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:16.158231+02:00</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>"Одеська обласна клінічна лікарня"</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>01998526</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:14.341405+00:00</t>
         </is>
       </c>
     </row>
@@ -23112,7 +25638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25643,6 +28169,164 @@
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-01-23T04:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>{"bytes": 71797}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-24T04:06:52+00:00</t>
+          <t>2026-01-25T04:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283381.780455.1.c9915bd5cb221959b52ad251823478a9",
-  "updated_at": "2026-01-24T04:06:52.088446+00:00",
-  "pages_done": 325,
-  "tenders_scanned": 32500,
-  "tenders_fetched": 32500,
-  "milk_tenders": 212,
-  "milk_items": 223
+  "offset": "1478283527.660165.1.36d57537ebf0afb46d6bffb03a86fb2e",
+  "updated_at": "2026-01-25T04:31:45.013020+00:00",
+  "pages_done": 350,
+  "tenders_scanned": 35000,
+  "tenders_fetched": 35000,
+  "milk_tenders": 230,
+  "milk_items": 243
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14320,6 +14320,1293 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>28f413a405b943d192223232a88cb9be</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>5d5b396a0303418794e9cf0c03dbcfe4</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>молоко жирність 2,6% плівка по 1л</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2015-12-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2015-12-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.183799+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>422c88e9893a44b999000862626be611</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>a91cdfd507424a70a3dfe7d72dfacb90</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>285</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.338985+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ad3beb487db64e58bbbea741ada300e6</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>f4079b30df0644c6ad8f3e13e34d2cdd</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Молоко цільне згущене  з цукром, жирнісь -8,5%,
+Кількість - 934кг., фасовка-жестяна банка, згідно з ДСТУ 4274:2003,
+зовнішній вигляд - колір біло-кремовий, рівномірний;
+консистенція - однорідна, помірно вязка, без осаду;
+смак -солодкий,з легким присмаком топленого молока.
+Термін / умови зберігання - 12 місяців /при температурі 0...10°С і вологості не вище 85%.</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>934</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2015-12-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2015-12-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.602873+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>b1f6447834b94203b0841a5cc9f5892b</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ab374eaaed2d4314845abde311d958ee</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>10.51.5 «Продукти молочні, інші (10.51.51-04.00 молоко згущене на І квартал 2016 року)»</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>1965</v>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:37.421742+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>fe9b6c874ad6424190897d3163d1e729</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>eabbbfd040ec4449ad20ba91bf8faaa5</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром, 8,5% жир., фасоване в металевих банках (нетто 370г) ДСТУ 4274:2003, виготовлене не раніше вересня 2015р. – 400 банок.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>400</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2015-12-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2015-12-20T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:42.394795+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>36ebc5516cdf4ba3943a06c967aa9d24</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>b704f1310ad046d68e6e7aa8d00b62ae</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Молоко згущене   ДСТУ 8,5 % з/б (виготовлення жовтень-листопад 2015 року)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>350</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2015-12-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:55.128545+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2108721d95f04baf877b6fcc9f751ae7</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>78514f92d9d144268e7e550ac347d30c</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Сир сичужний та кисломолочний сир (сир твердий)
+Яйця у шкаралупі, свіжі (яйце куряче)
+Олії рафіновані (олія соняшникова)
+Продукти молочні інші (молоко згущене)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>4</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2015-12-10T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2015-12-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:13.437556+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>6e89068a4def45a4ad35004435d07108</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>92522d519b6546e79c2b157dfab16a83</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Молоко згущене з цукром та какао, жб банка 370-380грам, 1000 шт.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>2015-12-07T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:21.686850+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>97af6dfc9a2c4112bb1007f806f0629e</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>656328148be947c3a13bf18537178f18</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>2015-12-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:23.659527+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>8bb3efecba12430a861d75f42805d93f</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>c4154859d28c43bf9fa2d5eeeef0a992</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Пипеткa Пастера пластиковая одноразовая на 3 мл</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>33141620-2</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2015-12-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>2015-12-18T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:27.998802+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>4a7fc5900fe544608325c0d37c5d9dfb</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>56e89fd93c41410eb210c5ab579005f4</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>101</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>2015-12-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2015-12-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:45.123768+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>b963f898bf844a11b765bc98a39df474</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>9a2ddd821f194ae0bc8c10345aaa5f13</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Молоко коров’яче 2,5% (фас.) 1л. - 3000 шт;
+Молоко коров’яче 2,6% (фас.) 1л. - 1000 шт;
+Молоко коров’яче 3,2% (фас.) 1л. - 500 шт;
+Молоко коров’яче 1% (фас.) 1л. - 1000 шт; 
+Вершки коров’ячі 10% (фас.) 10г - 14964 шт;
+Вершки коров’ячі 10% (фас.) 20г - 2075 шт;
+Вершки коров’ячі 10% (фас.) 0,5л - 221 шт</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>21760</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Южне</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:51.193383+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>33cf9b5e5c3e41f291561889c795a391</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>e7540c1479eb47bfa2bf3b32c5db525a</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>огірки мариновані слабокислі пастерезовані ГОСТ1633-73,3000г</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>03221270-9</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2015-12-18T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2015-12-24T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Костополь</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:54.207528+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>670aea6e5d084eb3b1003f898a3ea171</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>fa695aef8b8d4501a1633c917b8a3461</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>молоко згущене з цукром</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>170</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>2015-12-17T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2015-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:00.791680+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>5d2c8558647a48288a6393b396b186ff</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ea0adee1af394e1e99ce3d95952fc456</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>1. Продукти молочні, інші, код ДКПП 10.51.5. 2. Постачальник зобов'язується передати до кінця 2015 року у власність Покупця товар, а Покупець зобов'язується прийняти цей товар та оплатити його. Поставка товару за договором здійснюється частинами відповідно до письмових заявок Покупця. Заявка Покупця має містити інформацію щодо кількості, місця та терміну поставки товару. 3. Ціни на послуги встановлюються в національній валюті України. В ціну товару входить доставка та навантажувально-розвантажувальні роботи. 4. Розрахунки за наданий товар здійснюються на поточний розрахунковий рахунок Постачальника протягом 10 банківських днів з дати підписання накладних. 5. У разі затримки цільового бюджетного фінансування розрахунок за поставлений товар здійснюється протягом 5 банківських днів з дати отримання Замовником цільового бюджетного фінансування на свій реєстраційний рахунок. 6. У випадку порушення строків поставки, порушення обсягів поставки Постачальник пеню у розмірі 1% від суми договору за кожен день прострочки. У разі порушення вимог щодо якості товару Постачальник сплачує одноразовий штраф у розмірі 1% від суми договору за кожний випадок. 7. Сплата пені не звільняє Сторону від виконання прийнятих на себе зобов'язань по Договору поставки. 8. Обсяги товару можуть бути зменшені в залежності від реального фінансування. 9. Права та обов'язки сторін : Покупець зобов’язаний: - своєчасно та в повному обсязі (при наявності бюджетного фінансування) сплачувати за поставлений товар; - приймати поставлений товар згідно з актом приймання передачі товару. Покупець має право: - у разі невиконання зобов’язань Постачальника покупець має право достроково розірвати договір, повідомивши про це Постачальника. - контролювати поставку товарів у строки, встановлені договором. - повернути видаткову накладну постачальнику без здійснення оплати в разі неналежного оформлення документів; - У випадку наявності претензій до кількості, комплектності, якості, Товару відмовляється від приймання Товару Постачальник зобов’язаний: - забезпечити поставку товару у строки, встановлені договором; Постачальник має право: - своєчасно та в повному обсязі отримати плату за поставлений товар. 10. У випадках, не передбачених цим Договором, Сторони несуть відповідальність, передбачену чинним законодавством України. 11. Зміни у цей Договір набирають чинності з моменту належного оформлення Сторонами відповідної додаткової угоди до цього Договору, якщо інше не встановлено у самій додатковій угоді, цьому Договорі або у чинному в Україні законодавстві. 12. Договір набирає чинності з дня його підписання і діє до 31.12.2015 року.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2015-12-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:00.893243+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>fd7028fb4ee1495da3a27f659fc15157</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>72d4eeaa3aab4b0b83c82d7420727155</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>молоко 2,5% фасоване тривалого зберіганні, 1,0 л.</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>60</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2015-12-20T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>м. Нікополь</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:17.633082+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>fd7028fb4ee1495da3a27f659fc15157</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>e266e6ec10004f788299befee66560e4</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>молоко згущене 805%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>20</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2015-12-20T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>м. Нікополь</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:17.633082+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>fd7028fb4ee1495da3a27f659fc15157</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>3ed7132c838745fc8b7b382558924df1</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>сметана 20%</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>8</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2015-12-20T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>м. Нікополь</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:17.633082+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>3d7f393f74e54275a496f3f3bf1093f7</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>541dba62f29e4b2bb6d7c6135ca5c8f0</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Запропонований учасником товар за своїми властивостями повинен відповідати наступним вимогам:
+Склад: борошно пшеничне, цукор, жир кулінарний, яйця курячі, молоко сухе незбиране
+Поживна харчова цінність не менше 100гр.: білки- 7,9 г, жири-10,5 г., вуглеводи- 71,2 г
+Енергетична цінність (калорії) не менше: 411 ккал/1720 кДж
+Печиво у своєму складі не повинно мати генетично модифікованих організмів (ГМО).
+Вимоги до температури подальшого зберігання: зберігання за температури: (18±5°С), вологість повітря не більше 75%.
+Термін зберігання: не менше 9 місяців (на момент поставки термін придатності повинен становити не менше 80% від дати виготовлення)
+Дата виготовлення і пакування вказана на упакованих пачках. ДСТУ 3781
+Фасовка в картонних коробках не більше 4,5 кг
+Вага 1 пачки печива 50 г</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>15821200-1</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>315</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2015-12-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2015-12-18T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:36.868007+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>605315b4dce24bd6a68633ff196e7b1e</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>0969b66a662f453c838023cbef3cfee3</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Печиво - 80 кг, вафлі - 60 кг, курячі чверті - 250 кг, молоко згущене (0,5) - 60 банок, оцет 9% (1л) - 10 бут, повидло - 40 кг</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>430</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>2015-12-08T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2015-12-09T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>м.Острог</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:42.168049+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14331,7 +15618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25624,6 +26911,960 @@
       <c r="K213" t="inlineStr">
         <is>
           <t>2026-01-24T04:06:14.341405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>28f413a405b943d192223232a88cb9be</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>UA-2015-11-27-000055-b</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.183799+02:00</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>25180</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>422c88e9893a44b999000862626be611</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>UA-2015-11-27-000058</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.338985+02:00</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>"Одеська обласна клінічна лікарня"</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>01998526</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>11970</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ad3beb487db64e58bbbea741ada300e6</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>UA-2015-11-27-000061-a</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:26.602873+02:00</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №8</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>05497146</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>39775</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>b1f6447834b94203b0841a5cc9f5892b</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>UA-2015-11-27-000144-a</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:37.421742+02:00</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ "Південно - Західна електроенергетична система" державного підприємства «Національна енергетична компанія «УКРЕНЕРГО» "</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>21725012</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>22110</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>fe9b6c874ad6424190897d3163d1e729</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>UA-2015-11-27-000195-a</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:42.394795+02:00</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Київський геріатричний пансіонат</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>21462905</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>36ebc5516cdf4ba3943a06c967aa9d24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>UA-2015-11-30-000012-a</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:16:55.128545+02:00</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Святошинський дитячий будинок - інтернат</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>03188760</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2108721d95f04baf877b6fcc9f751ae7</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>UA-2015-11-30-000162-a</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:13.437556+02:00</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №3</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>05415958</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>75743</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>6e89068a4def45a4ad35004435d07108</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>UA-2015-11-30-000212-a</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:21.686850+02:00</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №12</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>25680639</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>23800</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>97af6dfc9a2c4112bb1007f806f0629e</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>UA-2015-12-01-000007-b</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:23.659527+02:00</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Ново-Білицький психоневрологічний інтернат для чоловіків</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>26267255</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>8bb3efecba12430a861d75f42805d93f</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>UA-2015-12-01-000046</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:27.998802+02:00</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровський центр первинної медико-санітарної допомоги №8"</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>37899778</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4a7fc5900fe544608325c0d37c5d9dfb</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>UA-2015-12-01-000144-a</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:45.123768+02:00</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Ново-Білицький психоневрологічний інтернат для чоловіків</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>26267255</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>5800</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>b963f898bf844a11b765bc98a39df474</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>UA-2015-12-01-000187-a</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:51.193383+02:00</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Южненська філія державного підприємства "Адміністрація морських портів України" (адміністрація морського порту "Южний")</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>38728549</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>420000</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>33cf9b5e5c3e41f291561889c795a391</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>UA-2015-12-01-000217</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:17:54.207528+02:00</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>КП ""КОСТОПІЛЬСЬКИЙ ОБЛАСНИЙ ЛІЦЕЙ-ІНТЕРНАТ ІІ-ІІІ СТУПЕНІВ ФІЗИЧНОЇ КУЛЬТУРИ І СПОРТУ ""</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>26009837</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>22560</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>670aea6e5d084eb3b1003f898a3ea171</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>UA-2015-12-02-000014</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:00.791680+02:00</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>КУ " Днепропетровская шестая городская клиническая больница Днепропетровского обласного совета"</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>01984441</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>10720</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>5d2c8558647a48288a6393b396b186ff</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>UA-2015-12-02-000015-b</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:00.893243+02:00</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Управління освіти Шевченківської районної в місті Києві державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>37470086</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>fd7028fb4ee1495da3a27f659fc15157</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>UA-2015-12-02-000134</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:17.633082+02:00</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Нікопольский територіальний центр соціального обслуговування (надання соціальних послуг)</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>21909039</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>3030</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>3d7f393f74e54275a496f3f3bf1093f7</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>UA-2015-12-03-000035-b</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:36.868007+02:00</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>12367</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>605315b4dce24bd6a68633ff196e7b1e</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>UA-2015-12-03-000074</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:42.168049+02:00</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Острозький психоневрологічний інтернат" Рівненської обласної ради</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>03189280</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>16330</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:07.173800+00:00</t>
         </is>
       </c>
     </row>
@@ -25638,7 +27879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28327,6 +30568,164 @@
       </c>
       <c r="E102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-01-24T04:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>{"bytes": 78524}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-25T04:31:45+00:00</t>
+          <t>2026-01-26T04:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283527.660165.1.36d57537ebf0afb46d6bffb03a86fb2e",
-  "updated_at": "2026-01-25T04:31:45.013020+00:00",
-  "pages_done": 350,
-  "tenders_scanned": 35000,
-  "tenders_fetched": 35000,
-  "milk_tenders": 230,
-  "milk_items": 243
+  "offset": "1478283672.676864.1.599a051af5668ac55b9a226772a6f836",
+  "updated_at": "2026-01-26T04:34:35.446652+00:00",
+  "pages_done": 375,
+  "tenders_scanned": 37500,
+  "tenders_fetched": 37500,
+  "milk_tenders": 244,
+  "milk_items": 260
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M244"/>
+  <dimension ref="A1:M261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15607,6 +15607,1082 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>fa8e35e2aea5445e96e6fd76eb5647da</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>e982cdff7a6743e5b573b5bfa974cb89</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Молоко сухе, контактна особа 067 225 15 25</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>500</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:50.196009+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>7d0d4158e6724640ac7840b47546d17e</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>446a67174f594a7980a3ce9feec8be6f</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малютка» З цукром 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>30</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2015-12-22T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:12.752726+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>7d0d4158e6724640ac7840b47546d17e</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>fdeac23e8d48413aaf1b09cad2ae6e25</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малиш» швидкого приготування З гречаним борошном 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>125</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2015-12-22T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:12.752726+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>7d0d4158e6724640ac7840b47546d17e</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>7ab7c3c62fb149c9934ba47d8e9c4f93</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха для дітей грудного віку «Малиш» швидкого приготування З вівсяним борошном 350 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>126</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>2015-12-22T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:12.752726+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>7d0d4158e6724640ac7840b47546d17e</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2317fe204a654ff783927273e8e35834</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Каша молочна «Малишка» Суміш рису, кукурудзи, вівса, гречки 250 г. виробник Хорольский молоко консервний комбінат дитячих продуктів  Україна м. Хорол</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>190</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2015-12-22T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:12.752726+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>6abedce1a84f42029b48b0a0c0768167</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>674dd0eb2ae2454999d1550068fcf6c6</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирн. пак. 1л пастерізоване</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>днепропетровск</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:38.430498+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>b4f4dfabc6a642498ac3f379fa09ea0e</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>524e375323e54d1db8aeed04a1aa61a5</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Молоко згущене цільне,  жб банка 370-380грам - 500 шт.
+Молоко згущене з цукром та какао жб банка 370-380грам - 1000 шт.</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2015-12-09T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2015-12-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:43.013131+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>cf4b168c61e948d8bb15c19cef72c588</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>fa559d4ea85f4112971959c0960b0b35</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - плівка по 1 л.</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>300</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2015-12-10T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>2015-12-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:01.307130+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>c479ad0ded3a41df87984450066677fb</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>19aaad70c2574015989e4b867a1c7e5e</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Сухе Молоко Вагове 150кг. Досавка адресна. Доставка по замовленню</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>150</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2015-12-16T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:21.642056+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>f619d872cb1d46ee8778915e21ab3e29</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>c53447b5b1aa46848a5e705a672f028a</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Молоко згущене фасоване ж/б</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>500</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2015-12-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>2015-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:27.003060+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ebd4d8730cdc4ddfbeb6caf8dc044a96</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>fb0f0e46307f41b28a33398ce3aed83c</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Запропонований учасником товар за своїми властивостями повинен відповідати наступним вимогам:
+Склад: борошно пшеничне, цукор, жир кулінарний, яйця курячі, молоко сухе незбиране
+Поживна харчова цінність не менше 100гр.: білки- 7,9 г, жири-10,5 г., вуглеводи- 71,2 г
+Енергетична цінність (калорії) не менше: 411 ккал/1720 кДж
+Печиво у своєму складі не повинно мати генетично модифікованих організмів (ГМО).
+Вимоги до температури подальшого зберігання: зберігання за температури: (18±5°С), вологість повітря не більше 75%.
+Термін зберігання: не менше 9 місяців (на момент поставки термін придатності повинен становити не менше 80% від дати виготовлення)
+Дата виготовлення і пакування вказана на упакованих пачках. ДСТУ 3781
+Фасовка в картонних коробках не більше 4,5 кг
+Вага 1 пачки печива 50 г</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>15821200-1</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>315</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2015-12-17T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2015-12-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:36.949747+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>5ea9298b37a7471f8ad648db1f7d4857</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>971b5fd85858426f801a435e6546cb9f</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Піпетка Пастера поліетиленова (стерильна) на 3,0 мл, градуювання 7,8 х150мм. В індивідуальній упаковці.  Для взяття крові з пальця у донора</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>38437000-7</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2015-12-17T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>2015-12-23T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:39.571803+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>dd09d3390436441d9fe6e0b87b20cff8</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>94b169da743947cdbd26b326080b3e7c</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Дитяча молочна суміш з варкою</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>62</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2015-12-18T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2015-12-25T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Днепродзержинськ</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:40.956802+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ef2611e83c214eaa8007618873c7a482</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>8b2a38d2c73446c2840023abc701e330</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Чай-40шт.; печиво (пач)-40 шт.; лимон-12 кг; олія (0,9 л)-40 пляшок; цукор-40 кг; гречка-40 кг; сардина (з/б 240г)-40 шт; згущене молоко (380г)- 40 шт; сік (1 л)-40 шт;мед (0,5 кг)-40 шт; цукерки "Південна ніч"  (фасовані 300 г)-40 шт; пакет-40 шт.
+Продукція повинна мати сертифікати якості. Постачальник повинен мати документи Державної реєстрації, ліцензії, дозволи, зареєстровані рахунки в банках. Оплата після надходження товару - безготівкова. Доставка -безкоштовна.</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>15894200-3</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>40</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:42.542965+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>9e03c6643cc846f1bcdcb36f9b6fbf3b</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>990056be802148149f31a129fd2e8fa0</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5% жир.(пакет 0,5л.)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>960</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Николаев</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:51.928318+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>d8dc3b6b5f9c4190b54757ec54a3564a</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>670ce594846a4178acb9ec8338a9ff78</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Молоко повинне відповідати  ДСТУ. Однорідна в міру щільна консистенція, з чистим присмаком пастеризованого молока, кольор від від молочно-білого до світло-кремового. Жирність 2,6 %.</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Помічна</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:07.798680+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>793ff641303a45ff8009063c19c0c5b8</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>c58218ab638c43e48f3610091b016c47</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>370</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2016-01-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:08.241132+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15618,7 +16694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27865,6 +28941,748 @@
       <c r="K231" t="inlineStr">
         <is>
           <t>2026-01-25T04:31:07.173800+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>fa8e35e2aea5445e96e6fd76eb5647da</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UA-2015-12-03-000135-a</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:18:50.196009+02:00</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №1</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>01981738</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>27500</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>7d0d4158e6724640ac7840b47546d17e</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>UA-2015-12-04-000128</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:12.752726+02:00</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровський центр первинної медико-санітарної допомоги № 9"</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>37899715</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>15393.22</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>6abedce1a84f42029b48b0a0c0768167</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>UA-2015-12-07-000065</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:38.430498+02:00</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКИЙ ОБЛАСНИЙ КЛІНІЧНИЙ ЦЕНТР КАРДІОЛОГІЇ ТА КАРДІОХІРУРГІЇ" </t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>01985370</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>36300</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>b4f4dfabc6a642498ac3f379fa09ea0e</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>UA-2015-12-07-000102-b</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:19:43.013131+02:00</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №12</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>25680639</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>32300</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>cf4b168c61e948d8bb15c19cef72c588</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>UA-2015-12-08-000028-b</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:01.307130+02:00</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>3777</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>c479ad0ded3a41df87984450066677fb</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>UA-2015-12-08-000144-b</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:21.642056+02:00</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Пуща-Водицький психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>03188795</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>1</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>f619d872cb1d46ee8778915e21ab3e29</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>UA-2015-12-08-000182</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:27.003060+02:00</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна лікарня № 2</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>05415941</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ebd4d8730cdc4ddfbeb6caf8dc044a96</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>UA-2015-12-09-000049-a</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:36.949747+02:00</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>12366</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>5ea9298b37a7471f8ad648db1f7d4857</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>UA-2015-12-09-000061-b</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:39.571803+02:00</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>14850</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>dd09d3390436441d9fe6e0b87b20cff8</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>UA-2015-12-09-000079</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:40.956802+02:00</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>1</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ef2611e83c214eaa8007618873c7a482</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>UA-2015-12-09-000093-a</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:42.542965+02:00</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування (надання соціальних послуг) Печерського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>22870397</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>9e03c6643cc846f1bcdcb36f9b6fbf3b</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>UA-2015-12-09-000158</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:20:51.928318+02:00</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ДП "АМПУ"/Філія "Октябрьск" ДП "АМПУ" (адміністрація СМП "Октябрьск")</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>38728512</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>11520</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>d8dc3b6b5f9c4190b54757ec54a3564a</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>UA-2015-12-10-000049-a</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:07.798680+02:00</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Добровеличківська спеціалізована загальноосвітня школа-інтернат І-ІІІ ступенів Кіровоградської обласної ради</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>23228183</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>34510</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>793ff641303a45ff8009063c19c0c5b8</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UA-2015-12-10-000051</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:08.241132+02:00</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>КУ "ДНІПРОДЗЕРЖИНСЬКИЙ ДИТЯЧИЙ ПРОТИТУБЕРКУЛЬОЗНИЙ САНАТОРІЙ ДОР"</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>26048926</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:33:46.393490+00:00</t>
         </is>
       </c>
     </row>
@@ -27879,7 +29697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30726,6 +32544,164 @@
       </c>
       <c r="E108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-01-25T04:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>{"bytes": 85361}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:35+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:35+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:36+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:36+00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:36+00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-26T04:34:35+00:00</t>
+          <t>2026-01-27T04:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283672.676864.1.599a051af5668ac55b9a226772a6f836",
-  "updated_at": "2026-01-26T04:34:35.446652+00:00",
-  "pages_done": 375,
-  "tenders_scanned": 37500,
-  "tenders_fetched": 37500,
-  "milk_tenders": 244,
-  "milk_items": 260
+  "offset": "1478283808.810887.1.e73d078235118181530390347b99b77e",
+  "updated_at": "2026-01-27T04:16:50.218898+00:00",
+  "pages_done": 400,
+  "tenders_scanned": 40000,
+  "tenders_fetched": 40000,
+  "milk_tenders": 271,
+  "milk_items": 288
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16683,6 +16683,1805 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ccaaa3aa139c448c9cccffac3e1b91ab</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>d797996519474118af01c0bd2b02e5ab</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Молоко згущене повинне
+ відповідати  ДСТУ. Має бути солодкий, чистий, без сторонніх присмаків і запахів смак пастеризованого молока. Колір – білий з кремовим відтінком, рівномірний. Консистенція – однорідна, без наявності відчутних органолептичних кристалів молочного цукру. Допускається незначна мучниста консистенція і осад лактози на дні банки. Масовою часткою жиру не менше 8,5%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>320</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Помічна</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:13.074114+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ccaaa3aa139c448c9cccffac3e1b91ab</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>77d6afa5448449668959f1513b0d7566</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Сметана повинна відповідати ДСТУ. Однорідна маса з 
+глянсуватою поверхнею, густа, незначна крупинчатість, з присмаком і ароматом властивим пастеризованому продукту, без сторонніх присмаків і запахів. Колір білий з кремовим відтінком, рівномірний за всією масою. Жирність не менше ніж 21%.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>250</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Помічна</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:13.074114+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ec60da2a4da744fea9d2b723b3c9f2d9</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>e593f464b7d84891838e8dc13fa62a39</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Молоко, жирність 3,2%, фасоване по 1 л</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:44.161129+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>69a06a1dc91441a8aea767f8c2418983</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>22628b86c2a44f8b8accc684da3f2a28</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>398</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:46.911565+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2b6a53eb86b4435a9c8776177a3793db</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>cfdcf58e52f44b319542025c6613360d</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване по 1 л</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>100</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2015-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:06.748818+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>3d4f6be7c5b04a7295328713ff654adf</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ab181f0574b647888dee05a9760443ea</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Харчування дитяче. 
+Молоко «На здоров’я»  3,2% Дитяче 0,5 л. (510 шт.), 2. Сік  «Чудо Чадо» 0,2 л. в асортименті (423 шт.), Суміш Малиш молочна 350 г. в асортименті (20 шт.)
+Вимоги щодо якості товару:
+1. Товар повинен мати реєстраційне посвідчення
+2. Якісно поставленим товаром вважається такий товар, який відповідає 
+вимогам, що звичайно ставляться до товару відповідного характеру.
+3. Товар повинен мати санітарно-гігієнічний висновок.
+4. Товар повинен мати сертифікат якості.
+5. Товар повинен бути новим, таким що не був у вжитку.
+6.  На момент постачання  залишок терміну зберігання продукції повинен 
+бути не менш 80% загального терміну зберігання.
+Надати документи:
+1. Виписка з Єдиного державного реєстру юридичних осіб та фізичних 
+осіб-підприємців
+2. Довідка з Єдиного державного реєстру підприємств та організацій 
+України (ЄДРПОУ)
+Постачання і транспортування продукції на склад Замовника здійс-
+нюється  транспортом  постачальника і за рахунок постачальника.
+Вимоги до якості товару і кваліфікації учасників - в Додатках 
+до Закупівлі.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>953</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:08.098981+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>8268f3d3a17e4b719381e0661cf7089b</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>4775d752431741f5a4576005e155bcb9</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Молоко цільне згущене з сахаром 8,5% , вага 0,370кг. кількість 1081баночок або 400кг. Дата виготовлення повинна бути не менша ніж вересень-жовтень 2015р</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>400</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2015-12-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2015-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:09.867668+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>0166c626c384429ca69341e9e254dcc7</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>cf0f7100936f41abae47fbd5f1f3a5a3</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Молоко рідке 2,5%-3,2% жирністю пастеризоване фасоване в поліетиленових пакетах 1000г</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2015-12-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2016-02-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Гостомель</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:10.290199+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>b91ba43d2f5d4931bffca3e4649f6589</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>bfee9a8cfa204af0920f8893ee55e1d6</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване  п/е,2,5%-3,2%  жиру (1000г)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2016-01-03T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:11.640383+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>7d406bfc05c84355b91e5efa3885caa6</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>3a3dd76fa6924cef863b3541b31ba30c</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Молоко цільне коров'яче, пастеризоване, вітчизняного виробника, жирність 3,2%, фасоване 1 л</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>330</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2016-01-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2016-01-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:30.756740+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>400efa6eb19d4c9c97a3237663cec16e</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>f26c28fb882b48c3a47d81405d04f56e</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Дитяча молочна суміш з варкою</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>62</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2015-12-18T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2015-12-25T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Днепродзержинськ</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:31.406311+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>06331f0ff91f417f8be34bb8f31812cb</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>78d7df902e4e47bc80a24bb9dfd2fe75</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване в п/е 0,5 л; жирністю 2,5%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Днепропетровская обл.</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.084745+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>83524531612141aca316d6d3b94789a4</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>0146c30a855141a3b4fbb305b8c90a44</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>10.51.1 «Молоко та вершки, рідинні, оброблені»</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>м. Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.461917+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>66cf424b49974a1d83f64fce2880ef6f</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>31973883e73e4e37be3de901e9ad293b</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2016-01-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.825225+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1c9fbf23e9f34c698ead3cf4ec470f9a</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>13d01b57e60a4d4f82d42229e4ed4705</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче,пастеризоване, питне,жирністю 3,2%, фасоване по 0,5л в плівку</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>29700</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2016-01-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ, м.Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:50.765721+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>e747848a30914a0fa6f0c30905521dc9</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>4678f25b6eee49bd837cdf18eca57e7b</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Молоко договір, специфікація, технічні вимоги та детальний опис  предмету закупівлі додається.</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:53.333975+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2aac8a56577e4e5fafb9086b6805a559</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>f6b1ae797298449dbb3883e335535306</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Молоко 3,2 % ж.</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:54.964331+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2fd9d99bdc03475bad42885fb41c6df5</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>400bc0f222614ec18dad37f139c98419</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Кефір 2.5 % ж., ряжанка 4 % ж., сметана 15% ж., молоко згущене 8,5 % ж.</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:55.270964+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>fdf839687a5b463eb1913ed657fe4ec4</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>0acfb17b0310458cace3894efcaa6f30</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Продукти харчування (код за ДК 016-2010   10.51.1; 10.51.5; 10.51.4; 10.51.3) Молоко; Кефір; Йогурт питний з плодово-ягідними наповнювачами; Сметана; Сир кисломолочний; Масло солодковершкове</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2016-01-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:59.057510+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>a023b031c70a4244b9f3d7feeef97cfa</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>0098f9196ab842e1b763b6ffb50c92d1</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Молоко повинне відповідати ДСТУ. Однорідна в міру щільна консистенція, з чистим присмаком пастеризованого молока, кольор від молочно-білого до світло-кремового. жирність  2,5%.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2015-12-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Краматорськ</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:01.683096+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>0704da48e1a24a169eb49845eaa722a9</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>9d996bf503ed48fe8ec13dea3e05df5e</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене 8.5%; Масло вершкове ТМ "Глобіно" 73 %</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>2</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2016-01-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:16.583593+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1dfb7d5f914d43579f73bd43284b007f</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>506ea75be624499a97ca840546fae092</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване свіже 2.7% </t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>800</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2015-12-28T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2015-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:17.131601+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>26e5ce30005741519519d99531f2a2cf</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>03383cb20d7f48b8800501e17c1583ae</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:19.163516+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>122e362ff9084ccdae1a8b307de180b8</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>47fb9f28efb7439c92313b0724739615</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Вапняне молоко</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>24210000-9</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>290</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>тонны</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Ивано-Франковская область</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>м. Калуш</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:22.827382+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>bdb43b9f1f374ae0a6d2f574cbfa87ef</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>e7fc8cd7afc34d50a177a26b8d518e41</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване, жирн. 2,5-2,6%</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>440</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>смт.Роздори Синельниківський р-н</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:25.734292+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>0ed93759a2ac417b890d2bbe1b2b53ea</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ee612097460d44bda17c570710fc7e5d</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко, пастер..,3,2%,1л.,
+Масло вершкове, 72% фасоване,
+Творог 9%, фасований 0,200,
+Сир твердий рос. 50% жир.,
+Сметана, 20% фасована 0,300 кг у пластиковому стакані.,
+Йогурт 2,5%,0,300 кг.
+</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>371</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>кг.</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>2016-01-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.532095+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>4cc0b38388624f9082b41dcd7a44623e</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1dfd310a56f646c9a933b82fcf81ce3a</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче питне пастеризоване жирність 2,5%</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>747</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>смт. Софіївка</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.611604+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>c82a6f991f7f44ed95b9954a3d5595c3</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>a2f41e6d2fef41089c50a034b5bca7a2</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені (молоко рідке)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2016-01-02T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>м. Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.760658+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16694,7 +18493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K245"/>
+  <dimension ref="A1:K272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29683,6 +31482,1437 @@
       <c r="K245" t="inlineStr">
         <is>
           <t>2026-01-26T04:33:46.393490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ccaaa3aa139c448c9cccffac3e1b91ab</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UA-2015-12-10-000078-b</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:13.074114+02:00</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Добровеличківська спеціалізована загальноосвітня школа-інтернат І-ІІІ ступенів Кіровоградської обласної ради</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>23228183</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>29060</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ec60da2a4da744fea9d2b723b3c9f2d9</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>UA-2015-12-11-000116</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:44.161129+02:00</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>КУ "КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКИЙ СПЕЦІАЛІЗОВАНИЙ БУДИНОК ДИТИНИ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ""</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>25726293</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>96804</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>1</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>69a06a1dc91441a8aea767f8c2418983</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>UA-2015-12-11-000128</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:21:46.911565+02:00</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>КИЇВСЬКА МІСЬКА КЛІНІЧНА ЛІКАРНЯ №4</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>30212155</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>19900</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2b6a53eb86b4435a9c8776177a3793db</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>UA-2015-12-14-000076</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:06.748818+02:00</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Київська міська наркологічна клінічна лікарня "Соціотерапія"</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>05496862</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>1</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>3d4f6be7c5b04a7295328713ff654adf</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>UA-2015-12-14-000089-a</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:08.098981+02:00</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Центр первинної медико - санітарної допомоги № 3 Дарницького району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>30300749</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>9996</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>8268f3d3a17e4b719381e0661cf7089b</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>UA-2015-12-14-000094-a</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:09.867668+02:00</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Пуща-Водицький психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>03188795</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>0166c626c384429ca69341e9e254dcc7</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>UA-2015-12-14-000097-a</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:10.290199+02:00</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Київська міська туберкульозна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>01994043</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>b91ba43d2f5d4931bffca3e4649f6589</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>UA-2015-12-14-000111-a</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:11.640383+02:00</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Тернопільводоканал"</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>03353845</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>46800</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>7d406bfc05c84355b91e5efa3885caa6</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>UA-2015-12-15-000083</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:30.756740+02:00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Навчально-реабілітаційний Центр "Веселка" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>21908293</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>29319.42</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>400efa6eb19d4c9c97a3237663cec16e</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>UA-2015-12-15-000087</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:31.406311+02:00</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>06331f0ff91f417f8be34bb8f31812cb</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000028</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.084745+02:00</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>КП ""ДНІПРОВОДОКАНАЛ" ДНІПРОПЕТРОВСЬКОЇ МІСЬКОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>03341305</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>83524531612141aca316d6d3b94789a4</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000034</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.461917+02:00</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>КЗ "Криворізька станція переливання крові" ДОР"</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>01986606</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>66cf424b49974a1d83f64fce2880ef6f</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000038</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:49.825225+02:00</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Навчально-реабілітаційний центр №6" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>24238634</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>107840</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1c9fbf23e9f34c698ead3cf4ec470f9a</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000049</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:50.765721+02:00</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровська обласна станція переливання крові"</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>01985434</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>142560</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>e747848a30914a0fa6f0c30905521dc9</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000062-a</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:53.333975+02:00</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Центр соціально-психологічної реабілітації дітей №1 Служби у справах дітей виконавчого органу Київської міської ради (Київської міської державної адміністрації)</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>20076991</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>23543.3</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2aac8a56577e4e5fafb9086b6805a559</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000075</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:54.964331+02:00</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Дніпропетровський дитячий будинок інтернат Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>03188272</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>80700</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2fd9d99bdc03475bad42885fb41c6df5</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000077</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:55.270964+02:00</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Дніпропетровський дитячий будинок інтернат Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>03188272</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>77905</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>fdf839687a5b463eb1913ed657fe4ec4</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000105</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:22:59.057510+02:00</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Криворізький дитячий будинок-інтернат" Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>03188292</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>32912.5</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>a023b031c70a4244b9f3d7feeef97cfa</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>UA-2015-12-16-000125-b</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:01.683096+02:00</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Комунальна лікувально-профілактична установа "Міський протитуберкульозний диспансер м.Краматорська"</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>01990766</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>1</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>0704da48e1a24a169eb49845eaa722a9</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>UA-2015-12-17-000070</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:16.583593+02:00</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Навчально-реабілітаційний центр №6" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>24238634</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>112450</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1dfb7d5f914d43579f73bd43284b007f</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>UA-2015-12-17-000075</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:17.131601+02:00</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Криворізький центр підготовки та перепідготовки робітничих кадрів будівельної галузі</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>02541602</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>78000</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>26e5ce30005741519519d99531f2a2cf</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>UA-2015-12-17-000083</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:19.163516+02:00</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Одеський морський торговельний порт"</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>0112566</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>122e362ff9084ccdae1a8b307de180b8</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>UA-2015-12-18-000003</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:22.827382+02:00</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ДП "Виробнича філія Державного підприємства зовнішньоекономічної діяльності «Укрінтеренерго» Калуська ТЕЦ"</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>36335452</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>219000</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>bdb43b9f1f374ae0a6d2f574cbfa87ef</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>UA-2015-12-18-000020</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:25.734292+02:00</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Обласний госпіталь для ветеранів війни" (Дніпропетровська обл., Синельниківський р-н)</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>33826456</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>25805</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>0ed93759a2ac417b890d2bbe1b2b53ea</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>UA-2015-12-18-000028-b</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.532095+02:00</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>КЗСЗ ЦС-ПР дітей "Барвінок" ДМР</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>0025799174</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>4cc0b38388624f9082b41dcd7a44623e</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>UA-2015-12-18-000030</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.611604+02:00</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ДПТНЗ СОФІЇВСЬКИЙ ПРОФЕСІЙНИЙ ЛІЦЕЙ</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>21902126</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>32541.5</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>c82a6f991f7f44ed95b9954a3d5595c3</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>UA-2015-12-18-000031</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:23:26.760658+02:00</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Криворізький спеціальний багатопрофільний навчально-реабілітаційний центр № 1"Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>23927366</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>50499</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:09.361760+00:00</t>
         </is>
       </c>
     </row>
@@ -29697,7 +32927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32702,6 +35932,164 @@
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-01-26T04:34:36+00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>{"bytes": 90062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-01-27T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-28T04:14:58+00:00</t>
+          <t>2026-01-29T04:49:01+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478283993.784926.1.b44262967a78dc4df9ffb4802d897ae3",
-  "updated_at": "2026-01-28T04:14:57.976073+00:00",
-  "pages_done": 425,
-  "tenders_scanned": 42500,
-  "tenders_fetched": 42500,
-  "milk_tenders": 358,
-  "milk_items": 387
+  "offset": "1478284176.741446.1.72e4b63a143d438090d9d783685873f1",
+  "updated_at": "2026-01-29T04:49:00.690299+00:00",
+  "pages_done": 450,
+  "tenders_scanned": 45000,
+  "tenders_fetched": 45000,
+  "milk_tenders": 418,
+  "milk_items": 450
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M388"/>
+  <dimension ref="A1:M451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24790,6 +24790,3954 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>52a6d62fe8a5451d9e728f8ab4640e9a</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>3e899759f56845c28114f47ede0b5f72</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром 8,5% жиру (банка 0,370кг)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>117</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>2016-01-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>2016-01-27T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:43.343313+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>609e38a1d1be4254ba0fbfc864d02e76</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>fbd87232131244f8bde169d5e591f8f6</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Жирність 2,5-2,6% Продукція повинна мати необхідні посвідчення, висновки, сертифікати відповідності, які передбачені чинним законодавством України.</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>2016-01-25T08:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>2016-03-31T07:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:47.939983+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>c6e8ded5f40b43ffa6308d591dad2308</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>1071c88d-9181-4f95-9d03-bb1ee75aff9b</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко, пастер..,3,2%,1л.,
+Масло вершкове, 72% фасоване,
+Творог 9%, фасований 0,200,
+Сир твердий рос. 50% жир.,
+Сметана, 20% фасована 0,300 кг у пластиковому стакані.,
+Йогурт 2,5%,0,300 кг.
+</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>840</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	кг.	</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>2016-03-31T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:48.625597+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>bd20fec8200249719074268249624244</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>8c028b0be2c54a0c9da84c67e4e6f94e</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Молоко незбиране в порошку (з умістом жиру 25 мас.%)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>55</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:49.525729+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>e3a595acae604f25a22efe96a2044dca</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>3f857c2e233241ec92d95535b72c5c45</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване плівка 2/5%</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>400</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>м. Гірник</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:53.022489+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>bb8853f3947349bbb167f552185e709b</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>faebb64a3fdd4abd82c3da3d0e522306</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Сметана 15%</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>38</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>2016-01-18T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Миколаїв</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:55.063145+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>0334ea0dfd4f4458ab7a28e7cd31c6d8</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>6fe99218bd0a4e89807305c5dbaf25e8</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Молоко повинно бути пастеризоване, ультрапастеризоване,  стерилізоване. Упаковка у тетрапак, тетрафіноасептік, в пляшках та т.ін.  ємкістю від 0,900 л. до 1,5 л. з відсотком жирності від 2,5 % до 3,5 %. Молоко повинно бути таких торгових марок: «Бурьонка», «На здоров’я»,  «Селянське», «Простоквашино», «Веселий молочник» та т.ін.   
+     Продукт повинні виготовляти у відповідності з вимогами діючих стандартів по технологічних інструкціях, які затверджені в установчому порядку.</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>70</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>2016-01-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>2016-01-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Малокозирщина</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:01.182680+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>46ffd3e391524b18ae8991b4a676d989</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>b35182be6ddd4cf48b2eb09c015df164</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване фасоване по по 1 л</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>600</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>2016-01-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:03.805313+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>7bfd3d85d22b46f29a3f4fd1967ff1a6</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>dd18ef69878a4d1088150c4828f6f5ce</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Молоко рідке, 3,2%</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:06.941853+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>fa3af5bcab73407a8f2ed55f6f34bb80</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>345242f375a5454aa65379032388c215</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Молоко рідке</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:07.045734+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>7cf0d57f7a94468cb461ca6d06b1a1f4</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>cf226bfbbcc147cfb6b1f9c541a71821</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>800</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:09.091186+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>9101449a42ee42fa863e6248ba482560</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>73650ad6f6c44df99193b79e2c6bcfee</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване, жирністю 2,5 %, фасоване по 0,93 кг в п\е пакети, термін реалізації 5 діб. </t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>1720</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>2016-05-20T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Тернопольская область</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Струсів</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:10.917723+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>268e65307d4046629a4f502ca22e81ad</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>fe0612ca10944bfb8440e3b6d4a6577f</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Згідно додатку. ДОДАТОК 1 повинен бути підписаний та зпечаткою підкріплений в системі.
+Очікувана сума закупівлі на рік</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2016-02-01T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>2016-02-28T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:17.212159+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>960ecb925d684392aeb55e33a50b716f</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>887a3f790e2d45979623788b07ac2e68</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>250</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2016-01-16T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>2016-01-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>смт. Магдалинівка</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:17.960922+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>f055b57f50f24adab679ba36028b3beb</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>f8aec07fe202484da924f16b15e61a72</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>молоко сгущенное</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>180</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>2016-01-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Авдеевка</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:20.965969+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>c832a8ebff444a418077f9c5eb780781</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>9600005bf6bb437c995bc45f1bbc7c1f</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Молоко свіже</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>600</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Кировоградская область</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Добровеличківка</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:22.313654+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>b1a9a8315a8f46c3a13fe065c1db7939</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>10c9fa80a44a487a8fe72236799296ce</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>сметана</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>420</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>2016-01-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Авдеевка</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:22.865029+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>537f7de0dd08458fba3a6512f13b474c</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>item_1</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>печиво, печінка теляча, ковбаса варена, сарделі вищ/готунку, молоко 2,5% фасоване. риба морожена типу хек, цукор,</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>4371</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>місто</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.003270+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1c63e47b750e492a949de6c681b12201</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>3208</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Тернопільська область</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Теребовля</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.053072+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>c0933f1892e341709f2ea87b35afb7c9</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>62763</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>10.51.1 "Молоко та вершки, рідинні, оброблені”, 10.89.1 "Супи, яйця, дріжджі та інші харчові продукти; екстракти та соки з м'яса, риби й водяних безхребетних”, 10.39.2 "Плоди й горіхи, оброблені та за</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>265</v>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.983186+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>7a55dad43183458299ff1cdcfc1f6b8c</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>d7f90103a1184b1797277ac3e681f9b7</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>2016-12-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>м. Чернігів</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:27.065505+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>da4d80240e064b3288d1d55c0156637f</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>03cd2cf7176d4b08ba1162aaae644e99</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване – 279,5 л, Соки фруктові (яблучний, персиковий) з м’якотю - 64,5 л  </t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>344</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:32.117131+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>da441b45c5394faba774dd3f23257078</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>63174456013c4ff6a8b78ca18b1c4313</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>молоко сухе</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>25</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>2016-01-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:41.074554+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>e03cf3f694f24e5cb99f04097d2681d1</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>660ea000ffaf4679af60593df9ba90fa</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Молоко свіже 2,5% жирн. 0,5л пакети</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:42.188390+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>44bc25b81b0348bd92036ff4c4b97d68</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>8d4a9e8389dc400883d4de89e6fd5534</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>молоко згущене  іриска 0,5</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>3</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>2016-01-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>м.Нікополь</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:42.399635+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>c215c85cb180459a8ab24541e65a0468</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>037536c4e50644b6b161a7b0fdcfa840</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Ковбаса варена – 130 кг; Ікра кабачкова, с/б, 0,510 л – 216 банок; Горошок зелений консервований з мозкових сортів, с/б, 0,510 л – 24 банки; Молоко згущене незбиране з цукром, ж/б 0,370 кг  – 60 банок; Огірки консервовані, с/б, 3л – 36 банок; Томатна паста, с/б, 0,530 л – 48 банок; Сік томатний 0,95 – 1л – 48 тетрапаків; Сік фруктово-ягідний в асортименті 0,95 – 1л – 60 тетрапаків; Сік яблучний освітлений, с/б, 3л – 100 банок.</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>722</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>2016-01-26T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>м. Новомосковськ</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:43.216569+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>d327577b97564c90b8590db621cf074a</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>10d4b35c810b48078a9c502463f01334</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>молоко 2,5%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>330</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>2016-01-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>м.нікополь</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:46.080463+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>cc028f980e8346a0b1c535be465bbf47</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>9d47bee2a7914c9797e0e22eaa6f3be6</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирності  пакетоване по1л</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>8850</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Острог</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:46.576440+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>3a9bb74d1ca14f9f9aec8a13948d6360</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>63192</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:50.569030+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>4143eea9f7164ec9be0a3dd346d37d68</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>5a1f9b158b4c4f5199c097d4caf3ec49</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>сметана 15% 0,450 гр. поліет.пакет</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>15</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Павлоград</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:55.954076+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>4143eea9f7164ec9be0a3dd346d37d68</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>d3fa168315fe43d6853c4ecc66605f77</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>молоко 2,5%політілен. пакети 1,0л.</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>120</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Павлоград</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:55.954076+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>d0d9fddf96324f4388bbf3a247d6891e</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>63386</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>10.51.2 Молоко у твердих формах (сухе молоко)  ДК 021:2015- 15511000-3 Молоко</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>190</v>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:56.270279+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>f731708d91784463b23a949eee95e142</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ad9e431dbf0743169ffbcc24f3a3778f</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Молоко, кефір, йогурт, масло вершкове, сметана, сир кисломолочний</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>7305</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:56.688373+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>8cd261be4f3f4bb9986aac91ebe66e2e</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>17639e442bc64963b4db7b2533ac3bf9</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Молоко незбиране в порошку (з умістом жиру 25 мас.%)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>55</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:04.726046+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>bfc05aec3b564b2cbd480c86d4b6af17</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>63401</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>10.51.5 Продукти молочні, інші (молоко сгущене)ДК 021:2015- 15511000-3 Молоко</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>500</v>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:05.018588+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>ed678ef868f44d2d9b1e71d16697e33e</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>d31cc987b1ed490e8704d79e5bbd88aa</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене із цукром 8,5% жирності по 370 гр.</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>120</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>2016-01-25T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>2016-03-23T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>с. Чудель</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:06.496536+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16b3f8934e2448589310d87d9df86ad9</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ebbcf511e09646269dd3ab946a5e67fd</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5 % жирності</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>500</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>м.Перещепине</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:06.637792+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>06c389876bd444eab6b31f15e3c1c68f</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Молоко фасоване п/е 3,2 % 900 г</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>2016-06-01T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:20.051614+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>ba8c5ec2a7fc46e7a462becf6964da41</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>0821ecaddcf1440fb26393c2b0d44d61</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Масло вершк.-70 кг; молоко-900 л;сир кисломол.-85 кг; сир тверд.-12 кг; сметана – 34 кг; яйця курячі - 1200 шт</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>2301</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:28.030295+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>b8bd052f29be49c1ae9614c7cfcfc78a</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>3ae1d9d68ebb4be3988b137d33bac120</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирності, фасоване у поліетиленові пакети по 1,0 кг</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:28.604688+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>b8bd052f29be49c1ae9614c7cfcfc78a</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>233a1a3e88bc4b518c3ed39065076840</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Молоко згущене фасоване по 0,380 кг</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>210</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:28.604688+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>06354c8c7b874844aa045ea7310b0b34</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>7142fedd1bc844d7baa2cfedad47d8d4</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Молоко довготривалого зберігання жирністю 2,5% фасоване по 1л в упаковки по системі "Тетра Пак" на основі картону</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:29.529147+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>06354c8c7b874844aa045ea7310b0b34</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>3de224cb4bc74010b11c79186efc0542</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% фасоване по 1л.</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>6930</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:29.529147+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>5f10fccbc802498d94267c6dbd9b7d32</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>fce777afdb804ec7941f3b9a653d0153</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>молоко2,5%-1600л; сметана 20%-100кг; сир кисло-молочний 9%-100кг;ряженка 2,5%-150л; кефір 2,5%-150л;сир твердий-40кг;</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>2140</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>смт.Миколаївка</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:35.906386+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>3121f255ca614c5db04374aa53f61028</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>45d0f8b06e7a440eb786c8ea1d9ba7cf</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Жирність 2,5-2,6% Продукція повинна мати необхідні посвідчення, висновки, сертифікати відповідності, які передбачені чинним законодавством України.</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>2016-01-25T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>2016-01-27T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:37.409271+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>0d00f164832046aca21844e854ed3149</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>84538159fc744a439e05a158c7e94552</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%  пастеризоване</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>400</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:38.628299+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>37c9479e811b43f0aed2f4cd2b1e5284</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>205997dbdd494c6eb78e321640135b2a</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване 2,5% жирності по 1 л. в поліетиленових пакетах (графік поставок понеділок )</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>2016-01-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:52.897938+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>64e924bc01954ce2a5c204ae22a3073c</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>977337edef6b44efbe4e42fdcf285e26</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>600</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:53.104766+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>21f78de78e8b494dbb15c793b8798918</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>пастеризоване молоко жир.2,5%</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:53.841927+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>82e30cea2faa45619d444e2aa015a0a2</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>b3fdf0e9ac194292859f71a80a1ed90f</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Молоко та вершки рідинні, обробленні</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>25500</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2015-12-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:58.951941+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>95eb07cf53ce424cad19058b6a17955f</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>5e6498a04c954816920717f4b94ea27d</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Молоко згущене з цільного молока, 8,5%, фасоване в жестяних банках</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>місто Жовті Води</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:00.572045+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ace5c5d0efaf47b9b4043f97f13b9448</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>0c969629ea6446cd98986bdedb9034da</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Сметана 15% жирності</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>500</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Луганская область</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Северодонецк</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:02.786160+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>dc0c3cac639d425683564afd89e9873d</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>68ab3b375bde4856adc98b3bb223e6e9</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>молоко 3,2%</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>540</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:13.807097+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>c1c89aa57ccf4a21ac4d974a3ec6eafa</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>d8b65951a6394be5b380517ec8ba11a6</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>згідно додатку</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>2016-02-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Ірпінь</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:14.374654+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>7e7fd8c1da8e400ab9a4d9ad116ce167</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>10066d98f43e46d9aec4a5926cee20f3</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>3640</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>2016-01-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:22.402952+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>15944d0c23b54de591bddfe7e2ef5d60</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>00292710946846e9b93d3893d0ac0e88</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Молоко(пастеризоване молоко) з підвищенним вмістом жиру(плівка)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>2016-01-21T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Маріуполь</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:22.964948+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>4c2d568ec30b4b7cb6a855aa0fc10ab3</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ebf909e61bf142f3a426b53fe158636f</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Молоко сгущене,в ж/банках,фірми "Сміляна",сЛана.Полтавської обл.</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>60</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>2016-01-27T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>2016-02-01T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:24.614937+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1a35d7d809424a87abc65eca79ba724f</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>3450c6a23a8c47a2b8fc3382ff9bce6c</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>1. Молоко 2,5 % жирності, фасоване у п/е по 1,0 кг (280кг х 13,09=3665,20);
+2. Кефір 2,5% жирності, фасоване у п/е по 0,5 кг (378кг х 16,84=6365,52);
+3. Сматана 15% жирності, фасоване у п/е по 0,5 кг (928кг х 31,55=883,40);
+4. Сир кисломолочний 9% жирності фасований у п/е по 0,250 кг (91кг х 62,46=5683,86);
+5. Масло вершкове 73% жирності, вагове (160кг х 103,65=16584,00);
+6. Сир твердий "Російський" 50% жирності, ваговий (20кг х 118,00=2360,00).</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>937</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>2016-02-10T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:24.764286+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>12337bdc30814032a14925c464b305d5</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>689cecd5d06245a29c02a4730f3f14be</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Дитяча молочна суміш з варкою</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>90</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Днепродзержинськ</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:28.420855+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>09b47fb12c4948808df75d6463567b98</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>57f7b2f50ec24166ad4d23c68190aca3</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко та вершки рідинні оброблені </t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>750</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:28.991340+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>009e6d78cba2411599e4a32c3dfab07c</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>02fd7e857742463fa7e3c335c67e380c</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>2016-02-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Ірпінь</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:30.305789+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>17bc80f765ab4a4996d91bd9293d5688</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>65399</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>793</v>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:31.006510+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>60a768e8db544491ad4b6e915a562e21</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>a9c46e5635a447e0be2c8dc359a2f872</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>молоко 2,5% фас 1л</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>20900</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>2016-07-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:35.392362+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24801,7 +28749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K359"/>
+  <dimension ref="A1:K419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43832,6 +47780,3186 @@
       <c r="K359" t="inlineStr">
         <is>
           <t>2026-01-28T04:14:17.500900+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>52a6d62fe8a5451d9e728f8ab4640e9a</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000024-a</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:43.343313+02:00</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна інфекційна лікарня</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>01993664</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>4515</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J360" t="n">
+        <v>1</v>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>609e38a1d1be4254ba0fbfc864d02e76</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000063-b</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:47.939983+02:00</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>25637595</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J361" t="n">
+        <v>1</v>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>c6e8ded5f40b43ffa6308d591dad2308</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000070-a</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:48.625597+02:00</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>КЗСЗ ЦС-ПР дітей "Барвінок" ДМР</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>0025799174</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>20800</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J362" t="n">
+        <v>1</v>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>bd20fec8200249719074268249624244</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000085-a</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:49.525729+02:00</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>КП "Дніпродзержинська міська лікарня №1 Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>01985794</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>3740</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J363" t="n">
+        <v>1</v>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>e3a595acae604f25a22efe96a2044dca</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000108-a</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:53.022489+02:00</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування ( надання соціальних послуг)м.Селидове Донецької області</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>34766528</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>17355</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J364" t="n">
+        <v>1</v>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>bb8853f3947349bbb167f552185e709b</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>UA-2016-01-14-000150-a</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:26:55.063145+02:00</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Миколаївський обласний шкірно-венерологічний диспансер Миколаївської обласної ради</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>05483301</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>13998</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J365" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>0334ea0dfd4f4458ab7a28e7cd31c6d8</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000024-a</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:01.182680+02:00</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Перещепинський НВК "Родина""Загальноосвітний навчальний заклад-дошкільний навчальний заклад І-ІІ ступенів з інтернатним відділенням для дітей -сиріт, дітей, позбавлених батьківського піклування, для дітей з кризових сімей" Новомосковської Районної Ради Дніпропетровської обл.</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>21928485</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>1043</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J366" t="n">
+        <v>1</v>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>46ffd3e391524b18ae8991b4a676d989</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000052-a</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:03.805313+02:00</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Київська міська наркологічна клінічна лікарня "Соціотерапія"</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>05496862</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>6300</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J367" t="n">
+        <v>1</v>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>7bfd3d85d22b46f29a3f4fd1967ff1a6</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000098-a</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:06.941853+02:00</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровське обласне бюро судово-медичної експертизи ДОР"</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>01985239</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J368" t="n">
+        <v>1</v>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>fa3af5bcab73407a8f2ed55f6f34bb80</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000102-a</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:07.045734+02:00</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровське обласне бюро судово-медичної експертизи ДОР"</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>01985239</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>28500</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J369" t="n">
+        <v>1</v>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>7cf0d57f7a94468cb461ca6d06b1a1f4</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000106-a</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:09.091186+02:00</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровське обласне бюро судово-медичної експертизи ДОР"</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>01985239</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>54400</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J370" t="n">
+        <v>1</v>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>9101449a42ee42fa863e6248ba482560</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>UA-2016-01-15-000151-a</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:10.917723+02:00</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Струсівська санаторна загальноосвітня школа-інтернат I-III ступенів Тернопільської обласної ради</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>04590990</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J371" t="n">
+        <v>1</v>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>268e65307d4046629a4f502ca22e81ad</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>UA-2016-01-16-000027-a</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:17.212159+02:00</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Консультативно-діагностичний центр №2 Дарницького району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>26064374</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J372" t="n">
+        <v>1</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>960ecb925d684392aeb55e33a50b716f</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>UA-2016-01-16-000034-a</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:17.960922+02:00</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КЗО "МАГДАЛИНІВСЬКИЙНАВЧАЛЬНО-РЕАБІЛІТАЦІЙНИЙ ЦЕНТР"ДОР" </t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>21910858</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>32539</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>f055b57f50f24adab679ba36028b3beb</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>UA-2016-01-16-000084-a</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:20.965969+02:00</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Відділ освіти Авдіївської міської ради</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>24803577</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J374" t="n">
+        <v>1</v>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>c832a8ebff444a418077f9c5eb780781</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>UA-2016-01-16-000118-a</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:22.313654+02:00</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Добровеличківська селищна рада</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>04365922</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>11015</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>b1a9a8315a8f46c3a13fe065c1db7939</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>UA-2016-01-17-000009-a</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:22.865029+02:00</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Відділ освіти Авдіївської міської ради</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>24803577</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>17760</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J376" t="n">
+        <v>1</v>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>537f7de0dd08458fba3a6512f13b474c</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000005</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.003270+02:00</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Дніпропетровський багатопрофільний  навчально-реабілітаційний центр № 9" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>20216742</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>186051</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J377" t="n">
+        <v>1</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1c63e47b750e492a949de6c681b12201</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000006</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.053072+02:00</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Теребовлянський навчально-реабілітаційний центр</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>04590984</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J378" t="n">
+        <v>1</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>c0933f1892e341709f2ea87b35afb7c9</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000013-a</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:26.983186+02:00</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>КП "Киевский Метрополитен"</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>03328913</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>15902.4</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J379" t="n">
+        <v>1</v>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>7a55dad43183458299ff1cdcfc1f6b8c</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000015-a</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:27.065505+02:00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНЕ ПІДПРИЄМСТВО "СПЕЦІАЛІЗОВАНИЙ КОМБІНАТ КОМУНАЛЬНО-ПОБУТОВОГО ОБСЛУГОВУВАННЯ" ЧЕРНІГІВСЬКОЇ МІСЬКОЇ РАДИ</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>03357636</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>10980</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J380" t="n">
+        <v>1</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>da4d80240e064b3288d1d55c0156637f</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000054-a</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:32.117131+02:00</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>КЗ ДНІПРОПЕТРОВСЬКА МІСЬКА СТУДЕНТСЬКА ПОЛІКЛІНІКА ДОР</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>01984398</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>3570</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>da441b45c5394faba774dd3f23257078</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000078-a</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:41.074554+02:00</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>КЗ "Дніпропетровська міська багатопрофільна клінічна лікарня №4"ДОР"</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>01280527</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J382" t="n">
+        <v>1</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>e03cf3f694f24e5cb99f04097d2681d1</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000096-a</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:42.188390+02:00</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровська міська клінічна лікарня №16 ДОР"</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>01984624</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>21014</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>44bc25b81b0348bd92036ff4c4b97d68</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000102-a</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:42.399635+02:00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Нікопольський професійний ліцей</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>02541728</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>192</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>c215c85cb180459a8ab24541e65a0468</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000125-a</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:43.216569+02:00</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>КУ "НОВОМОСКОВСЬКА ЦЕНТРАЛЬНА РАЙОННА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>26137707</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>17401.6</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J385" t="n">
+        <v>1</v>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>d327577b97564c90b8590db621cf074a</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000147-a</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:46.080463+02:00</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Нікопольський професійний ліцей</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>02541728</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>23070</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>cc028f980e8346a0b1c535be465bbf47</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>UA-2016-01-18-000159-a</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:46.576440+02:00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>КУ "Острозька спеціальна загальноосвітня школа-інтернат І-ІІІ ст. Рівненської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>21084314</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>316132</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J387" t="n">
+        <v>1</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>3a9bb74d1ca14f9f9aec8a13948d6360</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000001-b</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:50.569030+02:00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Автобаза управління справами Апарату Верховної Ради України</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>05907124</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>19700</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J388" t="n">
+        <v>1</v>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>4143eea9f7164ec9be0a3dd346d37d68</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000030-a</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:55.954076+02:00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>КУ "ПАВЛОГРАДСЬКА ЦЕНТРАЛЬНА РАЙОННА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>01988746</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>3246</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J389" t="n">
+        <v>1</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>d0d9fddf96324f4388bbf3a247d6891e</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000033-b</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:56.270279+02:00</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Комунальний заклад охорони здоров'я Обласна дитяча клінічна лікарня</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>02003600</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>10678</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J390" t="n">
+        <v>1</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>f731708d91784463b23a949eee95e142</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000036-a</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:27:56.688373+02:00</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Криворізький дитячий будинок-інтернат" Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>03188292</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>149267</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>8cd261be4f3f4bb9986aac91ebe66e2e</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000118-a</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:04.726046+02:00</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>КП "Дніпродзержинська міська лікарня №1 Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>01985794</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>5583</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J392" t="n">
+        <v>1</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>bfc05aec3b564b2cbd480c86d4b6af17</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000127-a</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:05.018588+02:00</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Комунальний заклад охорони здоров'я Обласна дитяча клінічна лікарня</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>02003600</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J393" t="n">
+        <v>1</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ed678ef868f44d2d9b1e71d16697e33e</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000155-a</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:06.496536+02:00</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>комунальний заклад "Чудельська спеціальна загальноосвітня школа-інтернат №1 І-ІІ ступенів" Рівненської обласної ради</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>22558895</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J394" t="n">
+        <v>1</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>16b3f8934e2448589310d87d9df86ad9</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>UA-2016-01-19-000161-a</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:06.637792+02:00</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Перещепинська районна ліканя №2" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>01988700</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J395" t="n">
+        <v>1</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>06c389876bd444eab6b31f15e3c1c68f</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000021</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:20.051614+02:00</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Київський міський будинок дитини "Берізка"</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>23390630</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>61875</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J396" t="n">
+        <v>1</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ba8c5ec2a7fc46e7a462becf6964da41</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000062-a</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:28.030295+02:00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Навчально-реабілітаційний Центр "Веселка" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>21908293</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>80951.32000000001</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J397" t="n">
+        <v>1</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>b8bd052f29be49c1ae9614c7cfcfc78a</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000067-b</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:28.604688+02:00</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Дитячий спеціалізований санаторій "Ялинка" Територіального медичного об'єднання "САНАТОРНОГО ЛІКУВАННЯ" у місті Києві</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>05415970</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>108170</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J398" t="n">
+        <v>1</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>06354c8c7b874844aa045ea7310b0b34</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000077-a</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:29.529147+02:00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дніпропетровський навчально-реабілітаційний центр №10 </t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>21929243</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>763095.15</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J399" t="n">
+        <v>1</v>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>5f10fccbc802498d94267c6dbd9b7d32</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000128-a</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:35.906386+02:00</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>КУ "Миколаївська спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>22509425</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>38820</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J400" t="n">
+        <v>1</v>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>3121f255ca614c5db04374aa53f61028</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000159-a</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:37.409271+02:00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>25637595</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>10100</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J401" t="n">
+        <v>1</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>0d00f164832046aca21844e854ed3149</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>UA-2016-01-20-000185-a</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:38.628299+02:00</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>КУ "ДНІПРОПЕТРОВСЬКА ДИТЯЧА МІСЬКА КЛІНІЧНА ЛІКАРНЯ № 5" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>01985475</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J402" t="n">
+        <v>1</v>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>37c9479e811b43f0aed2f4cd2b1e5284</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000023-b</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:52.897938+02:00</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Відокремлений підрозділ Оболонський міжрайонний відділ(філія) лабораторних досліджень Державної установи"Київський міський лабораторний центр Держсанепідслужби України"</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>38568965</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>23300</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J403" t="n">
+        <v>1</v>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>64e924bc01954ce2a5c204ae22a3073c</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000025-a</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:53.104766+02:00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>КУ "ДНІПРОДЗЕРЖИНСЬКИЙ ДИТЯЧИЙ ПРОТИТУБЕРКУЛЬОЗНИЙ САНАТОРІЙ ДОР"</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>26048926</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>38250</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J404" t="n">
+        <v>1</v>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>21f78de78e8b494dbb15c793b8798918</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000031</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:53.841927+02:00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>КУ "Одеський обласний медичний центр психічного здоров*я"</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>38644773</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>26400</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J405" t="n">
+        <v>1</v>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>82e30cea2faa45619d444e2aa015a0a2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000059-a</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:28:58.951941+02:00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>ДП "КЗОЗ ДОНЕЦЬКЕ ОБЛАСНЕ БЮРО СУДОВО-МЕДИЧНОЇ ЕКСПЕРТИЗИ"</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>01990080</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>165000</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>95eb07cf53ce424cad19058b6a17955f</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000075-a</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:00.572045+02:00</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Відділ освіти виконкому Жовтоводської міської ради</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>02142371</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>63402.5</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J407" t="n">
+        <v>1</v>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ace5c5d0efaf47b9b4043f97f13b9448</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000106-a</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:02.786160+02:00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Відділ освіти Сєвєродонецької міської ради</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>02141973</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J408" t="n">
+        <v>1</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>dc0c3cac639d425683564afd89e9873d</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000250-a</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:13.807097+02:00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>КЗО Дніпропетровський навчально-реабілітаційний центр "Колосок" ДОР</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>25533312</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>30034.95</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J409" t="n">
+        <v>1</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>c1c89aa57ccf4a21ac4d974a3ec6eafa</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>UA-2016-01-21-000262-a</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:14.374654+02:00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Дитячий спеціалізований санаторій "Орлятко" Територіальногго медичного обєднання "САНАТОРНОГО ЛІКУВАННЯ" у місті Києві</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>19426807</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>19635</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J410" t="n">
+        <v>1</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>7e7fd8c1da8e400ab9a4d9ad116ce167</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000014-b</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:22.402952+02:00</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Ново-Білицький психоневрологічний інтернат для чоловіків</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>26267255</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>51000</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J411" t="n">
+        <v>1</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>15944d0c23b54de591bddfe7e2ef5d60</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000018-a</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:22.964948+02:00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Маріупольський пансіонат для ветеранів війни та праці № 1</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>03190159</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>70632</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J412" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>4c2d568ec30b4b7cb6a855aa0fc10ab3</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000034-a</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:24.614937+02:00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровський професійний залізничний ліцей "</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>05536107</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>35500</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J413" t="n">
+        <v>1</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1a35d7d809424a87abc65eca79ba724f</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000037-a</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:24.764286+02:00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Дитячий спеціалізований санаторій "Лісова поляна"</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>05415817</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>35542</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>12337bdc30814032a14925c464b305d5</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000056-a</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:28.420855+02:00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>3680</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J415" t="n">
+        <v>1</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>09b47fb12c4948808df75d6463567b98</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000061-a</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:28.991340+02:00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>8797.799999999999</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J416" t="n">
+        <v>1</v>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>009e6d78cba2411599e4a32c3dfab07c</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000079-b</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:30.305789+02:00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Дитячий спеціалізований санаторій "Орлятко" Територіальногго медичного обєднання "САНАТОРНОГО ЛІКУВАННЯ" у місті Києві</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>19426807</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J417" t="n">
+        <v>1</v>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>17bc80f765ab4a4996d91bd9293d5688</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000090-a</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:31.006510+02:00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД ОСВІТИ "ДНІПРОПЕТРОВСЬКА ВАЛЬДОРФСЬКА СЕРЕДНЯ ЗАГАЛЬНООСВІТНЯ ШКОЛА" ДНІПРОПЕТРОВСЬКОЇ МІСЬКОЇ РАДИ</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>23928928</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>10832</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J418" t="n">
+        <v>1</v>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>60a768e8db544491ad4b6e915a562e21</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000120-a</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:35.392362+02:00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Клінічний онкологічний диспансер" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>02007265</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>248850</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J419" t="n">
+        <v>1</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:48:19.604388+00:00</t>
         </is>
       </c>
     </row>
@@ -43846,7 +50974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47167,6 +54295,164 @@
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-01-28T04:14:58+00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>{"bytes": 124071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-29T04:49:01+00:00</t>
+          <t>2026-01-30T04:51:49+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478284176.741446.1.72e4b63a143d438090d9d783685873f1",
-  "updated_at": "2026-01-29T04:49:00.690299+00:00",
-  "pages_done": 450,
-  "tenders_scanned": 45000,
-  "tenders_fetched": 45000,
-  "milk_tenders": 418,
-  "milk_items": 450
+  "offset": "1478284368.973916.1.9eb3210fb26d70e7ab546128c65e86fc",
+  "updated_at": "2026-01-30T04:51:48.733653+00:00",
+  "pages_done": 475,
+  "tenders_scanned": 47500,
+  "tenders_fetched": 47500,
+  "milk_tenders": 470,
+  "milk_items": 507
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M451"/>
+  <dimension ref="A1:M508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28738,6 +28738,3688 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>411579c452e3476094518799f1e57c15</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>64e1e9668c4f4065a95616bdf1849542</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Молоко питне коров'яче пастеризоване, жирність 2,5 %, фасоване</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>2016-01-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:39.483281+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>af90aefaca8842aeae6e6b05450b0a90</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>e874dbb6464948b2b1fc2d87de296e3b</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Апельсини,мандарини,макаронні вир.,томатна паста,сухофрукти,родзинки,повидло,капуста,цибуля ріп.,морква,буряк,картопля,сік томатний,сік ф-яг.,банани,яблука,окорока курячі,печінка ялов.,ковбаса напівкоп. та варена,риба с/м,рис,олія рафінована,борошно,пшоно,оселедць,сир твердий,йогурт,яйця кур.,дріжджі,цукерки шок.,кавовий напій,какао-порошок,печиво,вафлі,лимони,квасоля,сирок плав./сол./глазур.,молоко згущ.,крупа гречана/ячна/перлова/манна,сухарі панір.,карамель,чай чорний,сода,свинина,сало,сіль,кисіль.</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>11945</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>с. Котовка</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:53.122869+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>8e804023c3bd4d97933132742046fe5e</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>62aba79ac56a405fb66f77eaf04053ad</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Картопля- 800 кг,
+Морква- 250 кг,
+Цибуля- 100 кг,
+Капуста- 150 кг,
+Буряки цукрові- 300 кг,
+Паста та пюре томатні, концентровані- 24 банки,
+Плоди, засушені (крім бананів, фініків, інжиру, ананасів, авокадо, гуаяви, манго, мангостанів, цитрусових плодів і винограду); суміші горіхів або сушених плодів- 50 кг,
+Олія соняшникова та її фракції, рафінована, хімічно незмодифікована- 15 бут,
+Масло вершкове з умістом жиру не більше ніж 85 мас.%- 50 кг,
+Молоко та вершки, згущені, підсолоджені- 525 банок,
+Крупи та крупка із звичайної пшениці та спельти (манка)- 50 кг,
+Крупи та крупка з ячменю (перлова)- 50кг,
+Крупи та крупка з зерна інших зернових культур, н.в.і.у.(гречка)- 50 кг,
+Крупи та крупка з зерна інших зернових культур, н.в.і.у.(пшоно)- 25 кг,
+Вироби макаронні, неварені, з умістом яєць (крім виробів з начинкою чи приготованих іншим способом)- 100 кг,
+Чай-5кг
+Також звертайте увагу на додатки
+Поставка протягом лютого, періодичність поставки -  1 раз на 2 тижня.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>16</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>2016-01-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>2016-02-28T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:58.571342+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>c327dd0ce14347b58b72bddaf5ce3f14</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Молоко, 2,6%, пет/пл, 0,900 кг</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>660</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>2016-02-17T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:00.053301+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>be612404b4154d8abfb4cca243300ed9</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>66f78d33179b44d9849fdfc0221b9032</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Молоко, 2,5% (1л) з терміном придатності 72 години (ДСТУ 2661:2010)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>462</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>2016-01-28T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>2016-03-30T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:00.453533+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>cd7bfcdeab0a4150bb12a2074c92d63e</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>42807c592c844a9987e4d8d1a08b18e8</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Молоко 2,6% жирності, фасований в пакет 1 літр</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>2016-01-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:08.262567+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>96250228c704463ebbb188ee7f63ee97</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>fe08bf8f91e04f0babd7dacbf6d4f553</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Йогурт	шт	12500	115 грм. 
+1,5% жирності
+Кефір	пак	1250	500грм. 
+2,5% жирнисті
+Молоко сгущене	бан	250	бан 270гр 
+8,5% жирності 
+Ряжанка	пак	850	пак 500грм 
+2,5% жирності
+Сироватка	літр	125	пакет 1літр 
+0% жирності
+Сметана	пач	1600	450грм 
+20% жирності</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>16575</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2016-01-31T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:08.445197+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>150010606c54494bb0f867541bbc29b2</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>142e84dee9d3484fb9421aefed7b1673</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сметана 20%,фас 0,400 </t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>700</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>2015-07-08T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Днепропетровськ</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:09.262125+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>abf8a93c18bc4b6d86cc164b46941997</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>9b449fe15ae24f9c814e966a0e9f8d68</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Вимоги до кваліфікації учасників. Учасник повинен надати в електронному (сканованому форматі) установчі документи: 1. Статут або інший установчий документ. 2. Виписку з Єдиного державного реєстру юридичних та фізичних осіб – підприємців. 3. Витяг з Єдиного державного реєстру підприємств та організацій України (ЄДРПОУ) 4. Довідку про присвоєння ідентифікаційного коду (для фізичних осіб). 5. Паспорт (для фізичних осіб). 6. Свідоцтво про реєстрацію платника податку на додану вартість або єдиного податку. 7. Довідку про взяття на облік платника податків або виписку. 8. Відповідні ліцензії. 9.Кваліфікація учасників буде визначатися з врахуванням, в т.ч., досвіду роботи не менше 5 років та підписанням аналогічних договорів.КОНСУЛЬТАЦІЇ НАДАЮТЬСЯ ЗА ТЕЛЕФОНОМ:095-420-35-25; 068-389-11-72, ЛЮДМИЛА.</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>2016-02-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>2016-02-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:12.075388+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>4bac50d196b948739569eb34f0dd214f</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>9b94164869a442efa43b83853ae289ab</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Сосиски з молоком 1гат.(вага сосиски приблизно 48-49гр)</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>15131120-2</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>69</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:14.005803+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>b62caf7ccd734b9aa6f55f649d528cc2</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>50439d41d901446cad07202ceb358ac9</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>270</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:15.206372+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>011619a3fc2b4114a802b0bbea408b39</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>42c9488a7f95471783ef8528169be069</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирності</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>350</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>2016-02-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:21.779456+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>ab33812aff3d4c24950577830325ba23</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>молоко згущене</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>50</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>2016-02-08T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Татарбунари</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:29.518846+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>ae0b10a461e24025a357b0f15ecb8d2f</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 %</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>12712</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:33.059233+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>50ff44b41b7343289851888d1bbfb89c</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>42d2cd0a00b94ee3be82c1f82d0134c5</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, 2,5%	 - 1200 л.. Пропозицію надавати відповідно до документації.</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>2016-02-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:37.991165+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>7b8c7bb51b6f4eb686d254a345c95b34</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>b387735ced574e85bb61f405f36247fc</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> молоко сухе</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>750</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>м.Кілія</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:41.028020+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>47ae1cafa7944a6cad17682695b450b0</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>6ded17c4c65a4a3683e014468dcecf6e</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Молоко фас 1 літр п/е, 2.5% </t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>2016-02-08T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:41.390441+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>85005f8620fa47d687e27c9239616e85</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>b8d734cbcaa24e5f8f077172e1798e47</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Молоко пастерізоване 2,5% фас-1л</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>390</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:44.491577+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>47ca45b2f6734dbbbf6f4e77165be0d6</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>9a65a062a16f444ab94fc995c166ef68</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Молоко Масло Сир кисломолочний Сир твердий Кефір Ряженка Сметана</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>м.Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:45.190933+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>520a898c742d47eab90993431835d372</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>a3b200b0e984442b8f6881168f70da7a</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване питне 2,6-3,2% </t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>м. Ананьїв</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:56.102791+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>9c34ad8ca1de41f8a8196c03448886fe</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>a93f419b2e4d431ab2380a3b6b95a868</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Молоко сгущене незбиране з цукром</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>6</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:59.356573+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>dd40baf1e863435aa664d4cffcc53c07</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>554802d1b59e4290aeffca01e399a4e5</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>200</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>2016-02-02T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Запорожская область</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:59.788842+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>7c9e62ecf0a5445ea860fd71831d31de</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>1.	Олія раф. Соняшникова (24,55 кг х 34,52) = 847,47 2.	Сіль кам’яна (12,125 кг х 3,13) = 37,95 3.	Картопля (515,50 кг х 6,58) = 3391,99 4.	Вироби кондитерські (49,69 кг х 47,20) = 2345,25 5.	Мед (8,563 кг х 82,68) = 707,95 6.	Сухофрукти (13,375  кг х 102) = 1364,25 7.	Кавовий напій (4,45 кг х 120) = 534 8.	Цукор-пісок (87,19 кг х 18,52) = 1614,71 9.	Чай (0,61 кг х 289,20) = 175,33 10.	Яблука (141,06 кг х 13,12) = 1850,74 11.	Апельсини (117,5 кг х 27,83) = 3270,03 12.	Банани (117 кг х 41,47) = 4851,99 13.	Борошно пшеничне (420,12 кг х 10,26) = 4310,48 14.	Риба с/м (124,625 кг х 67,27) = 8383,52 15.	Сосиски, в/г (45,31 х 83,80) = 3797,19 16.	Ковбаса Сервелат «Столичний» (17,81 кг х 90,72) = 1615,95 17.	Соки фруктові, 1л (245,50 х 15,72) = 3859,26 18.	Крупа гречана (27,62 кг х 29,67) = 819,63 19.	Рис (23,5 кг х 23,84)= 560,24 20.	Крупа ячнєва (23,50 кг. х 7,63) = 179,31 21.	Макаронні вироби (25,0 кг х 6,29) = 407,25 22.	Паста томатна (5,0 кг. х 38,64) = 193,20 23.	Яйця (1820  х 2,76) = 5019,56 24.	М`ясо яловичини (106,35 х 95,99) = 10208,65 25.	Окорочка курячі (98,0 х 39,99) = 3919,02 26.	Молоко згущене (88,0 х 52,56) = 4625,28 27.	Кефір (24 х 12,60) = 302,40 28.	Дріжджі сухі (2,725 х 61,68) = 168,08 29.	Сир твердий (24,93 х 107,88) = 2688,91 30.	Сир кисломолочний (87,5 х 65,75) = 5753,13 31.	Масло вершкове (62,31 х 106,47) = 6634,41 32.	Сметана (31,125 х 45,21) = 1407,16 33.	Капуста б/к (192,25 х 11,25) = 2162,81 34.	Буряк столовий (161,25 х 8,09) = 1304,51 35.	Морква столова (117,50 х 12,16) = 1428,80 36.	Цибуля ріпчаста (117,50 кг х 10,72) = 1259,60</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>4983</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>м. Новомосковськ,</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:07.415728+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>31ce3104f8a74e819b2d9732082c73ea</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>4a09c470d7644545addeffb39ced0946</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>2016-02-05T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>смт. Христофорівка</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:09.760462+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>cd556b8a6e14432d85534da1a686ede1</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>85a6b9e6dc424db4ba87046bddaad078</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>молоко  незбиране згущене з цукром ПМКК 370г ж/б ДСТ 8,5% жиру</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>230</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>м.Ананьїв</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:20.958275+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>00eff389707d4f888ef13caec0a3ab85</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>6f3e1325b08e491d9ec9c29026637910</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>2016-12-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>м. Чернігів</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:26.442732+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>1cdc8470c40a4271809f5270c5957aae</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>53dca86771414a8f913bcc20305d01f7</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Молоко рідинне жирністю 2,5%</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>15511200-5</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>сел. Камишівка</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:26.567082+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>f30e61f64a284c95b705cd27665a0c66</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>item_2</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>300</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>2016-03-15T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Нікополь</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:35.546962+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>c51fe554e4ed4998aa6a581a5250926c</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>e5877a66b59847acbb8c7fc85f6d3dea</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Молоко фасоване 1л 3,2% п/ст пленка.</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>200</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>смт Магдалинівка</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:38.224516+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>b16aaa22f1ea4329b58c60763e167d9b</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>0472da3b65d44df0be53a53520a017a5</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко та вершки,рідини оброблені 10.51.1 </t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>5869</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:40.264357+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>61eef11a71624e15a142cc72ea8c630c</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>3d79ca054b984f299bea2d1e7fac5567</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>1284</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:53.813308+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>05ef9042fb4d4c5ca21489f1a2e5f70a</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>e73bb3b9eee04c3aa0ce558467dea104</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>сметана</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>15512200-2</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>120</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>2016-02-08T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>2016-02-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>с.Урвенна</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:05.742484+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>05ef9042fb4d4c5ca21489f1a2e5f70a</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>fd65b0252223485f981f7a52fa32aa23</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>400</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>2016-02-08T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>2016-02-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Ровенская область</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>с.Урвенна</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:05.742484+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1c14835b4c8f4df48ac67b762817b341</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>14a28bbb3c6d44f3b4c13acb8e496399</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Молоко пастериалізоване</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:06.378164+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>3b1e375a7e194999be263aaaedd43d3f</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>item_17</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Васильківка</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:08.714766+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>3b24baa442a34908913372cab2eccfe0</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>e25e167eea194ebc8aac28bdf4094eaa</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Молоко ультрапастеризоване, 1,5% жиру, ТМ «Селянське «Особливе», 1000 мл.</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>10482</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>2016-02-09T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Ізмаїл</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:09.726100+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>6a133b8ed3d34f348ecdac879bb790a0</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>098baca713c34e4f88d68112b370af7b</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, стерилізоване в пляшках та т.ін.  ємкістю від 0,900 л. до 1,5 л. з відсотком жирності від 2,5 % до 3,5 %. Смак та запах – характерні для молока, без сторонніх присмаків і запахів, з легким присмаком кип’ятіння. Колір – білий, рівномірний по всій масі, для стерилізованого – з кремовим 
+відтінком</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>750</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>2016-02-09T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Малокозирщина</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:16.308050+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>6a133b8ed3d34f348ecdac879bb790a0</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>f06e184d64344aeaa97a580e40ccbe54</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Сир кисломолочний 9,5% жиру
+Фасування по 1-5кг без рослинних жирівСклад:молоко коров'яче незбиране,молоко знежирене,закваска.Поживна(харчова)цінність в 100 г продукту:білків 16,7 г ; вуглеводів-2,0 г;жирів-9,5 г.Енергетична цінність(калорійність) 100 г продукту: 670 кДж (160 ккал).Строк придатночті -не більше ніж 7 діб.</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F489" t="n">
+        <v>150</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>2016-02-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Малокозирщина</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:16.308050+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>5a8ae136730e4090ad11f43aae7a17af</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>69fb49e4285f4fddb8a19d51a4a0ef42</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко та вершки рідинні оброблені </t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>40</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>2016-02-03T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Днепродзержинськ</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:17.843270+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>a6854bf55471498db87733ff98702a76</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>4a2934d9acdb43e2a1d15a7c45fc034b</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>детальна інформація в документації</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:20.794617+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>a6854bf55471498db87733ff98702a76</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>31f64100d12c4be89ef72ad485d94507</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>детальна інформація в документації</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F492" t="n">
+        <v>78</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:20.794617+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>de35c4ad9d5d4cd38c9d50f70720cd79</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>d483259718dd4c63a0a666f9c9acea69</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>«Молоко та вершки, рідинні, оброблені» код 10.51.1 за ДК 016:2010 («Молоко» код 15511 за ДК 021:2015) - молоко рідке жирністю не менше 2,5 %. Детальний опис закупівлі: див. файл ТУ</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F493" t="n">
+        <v>42108</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>2016-02-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:22.249572+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>c8b1d8597ad64d2b837bce46c246e275</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>d21eef4888744f768eba4c871e90775b</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>відповідно до ДКТ</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F494" t="n">
+        <v>900</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>2016-02-11T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>2016-04-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:23.446148+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>58670e0cf5ac494eaf6d144867e82199</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>193abf4b607b4b589dc5a377f4346025</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Молоко згущене незбиране із цукром 8,5% жирності.  Фасоване по 380г в жестяній тарі. Продавець повинен передати (поставити) Покупцеві товар (товари), якість яких відповідає діючим ДСТУ (ТУ),  санітарним нормам та підтверджується документом, який підтверджує якість продукту харчування (копія висновку державної санітарно-епідеміологічної експертизи або якісне посвідчення тощо). 
+	Замовлення «Замовник» направляє «Постачальнику» за 2 дні до  моменту поставки по телефону.
+Доставка продуктів здійснюється спеціалізованим транспортом «Постачальника» на адресу «Замовника», за рахунок «Постачальника» два рази на місяць. 
+           Сторони зобов'язуються своєчасно повідомляти одне одного про факт відправки та прибуття товару до Покупця.
+             Залишок терміну зберігання з моменту поставки:
+-	молока згущеного повинен бути не менше 70% від загального терміну зберігання, встановленого виробником продукції. Оплата окремо за кожну партію товару після доставки, згідно накладної.</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F495" t="n">
+        <v>300</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>2016-02-10T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:24.161868+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>58670e0cf5ac494eaf6d144867e82199</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>fb74eceb57ef4e1eb6025aeb70d8bf9e</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Сметана жирністю 22%. Фасована в політиленові пакети по 400 г. Продавець повинен передати (поставити) Покупцеві товар (товари), якість яких відповідає діючим ДСТУ (ТУ),  санітарним нормам та підтверджується документом, який підтверджує якість продукту харчування (копія висновку державної санітарно-епідеміологічної експертизи або якісне посвідчення тощо). 
+	Замовлення на швидкопсуючі продукти «Замовник» направляє «Постачальнику» за 2 дні до  моменту поставки по телефону.
+Доставка продуктів здійснюється спеціалізованим транспортом «Постачальника» на адресу «Замовника», за рахунок «Постачальника» два рази на тиждень.  
+           Сторони зобов'язуються своєчасно повідомляти одне одного про факт відправки та прибуття товару до Покупця.
+             Залишок терміну зберігання з моменту поставки:
+-	сметани повинен бути не менше 50% від загального терміну зберігання, встановленого виробником продукції;
+ Оплата окремо за кожну партію товару після доставки, згідно накладної.</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>100</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>2016-02-10T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:24.161868+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>c900042b7430431cbba90478b70b20d5</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>4d12ff3287d94398a33b83c21d06ca52</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>сметана 20%,фас. по 400 гр.</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>700</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:25.505225+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>c900042b7430431cbba90478b70b20d5</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ce8ac91306164654868002dc261abd89</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>кефир 2,5%,фас,1 л</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>2015-12-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:25.505225+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1967cee574be42e7b5dc35e97b839afb</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>427a3058beb14bfe9bfb8655255cc33d</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>831</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Харьковская область</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Шевченківський р-н</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:26.061066+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>e6ce7adccedc428f8164605958731971</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>8c964a05a36249328ae18cbd90baaa2e</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>молоко 2,5%,фас 1л</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F500" t="n">
+        <v>18480</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:28.065838+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>6f165732fba14a7aa19e44e36b3569c3</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3f83782b94064951a20fcdd5347297bd</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене </t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F501" t="n">
+        <v>37</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>2016-02-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:28.576677+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>9897aeaaf5cb4e26beef8ed635b7ee40</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>609ae028464240f5876d94f2b72d58c3</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>молоко згущене іриска 0,5</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F502" t="n">
+        <v>3</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>м.Нікополь</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:29.906584+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>0192adfbe40b49ecbf5e7939bb8c11f1</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>e7c1809293a74167940a9b7c56372c5d</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром 8,5% жиру (банка 0,380кг) Молоко незбиране згущене з цукром 8,5% жиру (банка 0,380кг. Смак солодкий,чистий, без сторонніх присмаків та запахів, з вираженим смаком Пастеризованного молока. Колір рівномірний білий з кремовим відтінком. Консистенція – однорідна, без наявності органоліптичних кристалів молочного цукру Вимоги до якості та безпеки згущеного молока регламентуються національними стандартами України:</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F503" t="n">
+        <v>200</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>2016-02-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>2016-02-15T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:32.102298+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>a479c26dc3274d94a81b119c9b154b10</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>d6fb604d85654a068580dab45881362d</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Йогурт питний фасований по 0,115кг, Молоко згущене 8,5%</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F504" t="n">
+        <v>705</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>2016-12-28T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>с. Котовка</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:33.094723+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>c40f8cd961084c5bac9a6f862aa01611</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>спецхарчування (молоко)</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>80</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>2016-02-25T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>м. Киів</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:39.221146+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>40901b559efa44edb319cc09f7f9916d</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>2016-07-29T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>м.Вінниця</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:44.935755+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ac111f34185148d185af5e522814247e</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>item_2</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>931</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>с. Васильківка</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:46.007858+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ce3fa27672ac4dd9a52d4ea8be7281da</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>d0b410b05722463796b3f532b79bc9db</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>молоко2,5%-1600л; сметана 20%-100кг; сир кисло-молочний 9%-100кг;ряженка 2,5%-150л; кефір 2,5%-150л;сир твердий-40кг;</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>2140</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>2016-02-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>смт.Миколаївка</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:46.589761+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28749,7 +32431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K419"/>
+  <dimension ref="A1:K471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50960,6 +54642,2762 @@
       <c r="K419" t="inlineStr">
         <is>
           <t>2026-01-29T04:48:19.604388+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>411579c452e3476094518799f1e57c15</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>UA-2016-01-22-000187-a</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:39.483281+02:00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Дошкільний заклад освіти №628 Державного управління справами</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>22864155</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>af90aefaca8842aeae6e6b05450b0a90</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>UA-2016-01-24-000009-a</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:53.122869+02:00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД ОСВІТИ "КОТОВСЬКИЙ НАВЧАЛЬНО-РЕАБІЛІТАЦІЙНИЙ ЦЕНТР" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>23078513</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>1315620</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J421" t="n">
+        <v>1</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>8e804023c3bd4d97933132742046fe5e</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000029-b</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:29:58.571342+02:00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Перинатальний центр м.Києва</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>22964365</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>32000</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J422" t="n">
+        <v>1</v>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>c327dd0ce14347b58b72bddaf5ce3f14</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000042</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:00.053301+02:00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Київмедспецтранс</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>01993807</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>7010</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J423" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>be612404b4154d8abfb4cca243300ed9</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000043-b</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:00.453533+02:00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування Святошинського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>37674964</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>17892</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J424" t="n">
+        <v>1</v>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>cd7bfcdeab0a4150bb12a2074c92d63e</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000093-a</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:08.262567+02:00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Олімпійський навчально-спортивний центр "КОНЧА-ЗАСПА"</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>38217021</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>58823</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J425" t="n">
+        <v>1</v>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>96250228c704463ebbb188ee7f63ee97</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000098-a</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:08.445197+02:00</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Олімпійський навчально-спортивний центр "КОНЧА-ЗАСПА"</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>38217021</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>91913</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J426" t="n">
+        <v>1</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>150010606c54494bb0f867541bbc29b2</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000106-a</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:09.262125+02:00</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Клінічний онкологічний диспансер" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>02007265</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>50300</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J427" t="n">
+        <v>1</v>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>abf8a93c18bc4b6d86cc164b46941997</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000120-b</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:12.075388+02:00</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Київська міська психоневрологічна лікарня №2</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>01993992</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>46300</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J428" t="n">
+        <v>1</v>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4bac50d196b948739569eb34f0dd214f</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000137-a</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:14.005803+02:00</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня швидкої медичної допомоги"ДОР</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>01985854</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>10157</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>b62caf7ccd734b9aa6f55f649d528cc2</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000148-a</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:15.206372+02:00</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня швидкої медичної допомоги"ДОР</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>01985854</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>9184</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J430" t="n">
+        <v>1</v>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>011619a3fc2b4114a802b0bbea408b39</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>UA-2016-01-25-000244-a</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:21.779456+02:00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська поліклініка №1"</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>30311923</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J431" t="n">
+        <v>1</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ab33812aff3d4c24950577830325ba23</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000028</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:29.518846+02:00</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Державний навчальний заклад" Татарбунарське професійно-технічне аграрне училище"</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>20949806</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J432" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>ae0b10a461e24025a357b0f15ecb8d2f</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000055</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:33.059233+02:00</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Консультативно-діагностичний центр" Святошинського р-ну м. Києва</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>26199401</t>
+        </is>
+      </c>
+      <c r="H433" t="n">
+        <v>141000</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J433" t="n">
+        <v>1</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>50ff44b41b7343289851888d1bbfb89c</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000084-a</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:37.991165+02:00</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 5 Святошинського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>00185011</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>14400</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J434" t="n">
+        <v>1</v>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>7b8c7bb51b6f4eb686d254a345c95b34</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000120-a</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:41.028020+02:00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Комунальний заклад " Кілійська спеціальна  загальноосвітня школа-інтернат 1-11 ступенів"</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>20991955</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J435" t="n">
+        <v>1</v>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>47ae1cafa7944a6cad17682695b450b0</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000124-a</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:41.390441+02:00</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна лікарня № 2</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>05415941</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J436" t="n">
+        <v>1</v>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>85005f8620fa47d687e27c9239616e85</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000140-a</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:44.491577+02:00</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>КЗ "Дитяча лікарня м.Дніпродзержинська"ДОР"</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>01985848</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>7660</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J437" t="n">
+        <v>1</v>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>47ca45b2f6734dbbbf6f4e77165be0d6</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000154-a</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:45.190933+02:00</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>КЗ"Навчально-виховний комплекс "Загальноосвітній навчальний заклад-дошкільний навчальний заклад" №3  м.Дніпродзержинська</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>23371360</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>77560</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>520a898c742d47eab90993431835d372</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000245-a</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:56.102791+02:00</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>КУ "Комунальний заклад "Ананьївська загальноосвітня школа-інтернат І-ІІІ ступенів""</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>20994698</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>15015</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J439" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>9c34ad8ca1de41f8a8196c03448886fe</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000265-a</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:59.356573+02:00</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>КЗО "НРЦ розвитку дитини дошкільного віку"ДОР"</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>26371642</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>6984.92</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>dd40baf1e863435aa664d4cffcc53c07</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>UA-2016-01-26-000272-a</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:30:59.788842+02:00</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Запорізька державна інженерна академія</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>05402565</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J441" t="n">
+        <v>1</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>7c9e62ecf0a5445ea860fd71831d31de</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>UA-2016-01-27-000033</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:07.415728+02:00</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Професійно-технічне училище № 48 м. Новомосковська</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>02541763</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>92000</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>31ce3104f8a74e819b2d9732082c73ea</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>UA-2016-01-27-000049-b</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:09.760462+02:00</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "ХРИСТОФОРІВСЬКИЙ ПРОТИТУБЕРКУЛЬОЗНИЙ САНАТОРІЙ ДЛЯ ДОРОСЛИХ"</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>01988189</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>52494</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J443" t="n">
+        <v>1</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>cd556b8a6e14432d85534da1a686ede1</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>UA-2016-01-27-000163-b</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:20.958275+02:00</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>КУ "Комунальний заклад "Ананьївська загальноосвітня школа-інтернат І-ІІІ ступенів""</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>20994698</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>12123.9</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>00eff389707d4f888ef13caec0a3ab85</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>UA-2016-01-27-000239-b</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:26.442732+02:00</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНЕ ПІДПРИЄМСТВО "СПЕЦІАЛІЗОВАНИЙ КОМБІНАТ КОМУНАЛЬНО-ПОБУТОВОГО ОБСЛУГОВУВАННЯ" ЧЕРНІГІВСЬКОЇ МІСЬКОЇ РАДИ</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>03357636</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>10980</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J445" t="n">
+        <v>1</v>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1cdc8470c40a4271809f5270c5957aae</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>UA-2016-01-27-000243-b</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:26.567082+02:00</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Камишівський психоневрологічний інтернат  </t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>03190254</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>27500</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J446" t="n">
+        <v>1</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>f30e61f64a284c95b705cd27665a0c66</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000021</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:35.546962+02:00</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Нікопольська міська лікарня №4" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>25539007</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>16482</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J447" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>c51fe554e4ed4998aa6a581a5250926c</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000046-b</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:38.224516+02:00</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КЗО "МАГДАЛИНІВСЬКИЙНАВЧАЛЬНО-РЕАБІЛІТАЦІЙНИЙ ЦЕНТР"ДОР" </t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>21910858</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>16545</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J448" t="n">
+        <v>1</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>b16aaa22f1ea4329b58c60763e167d9b</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000050-b</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:40.264357+02:00</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКЕ ОБЛАСНЕ ПАТОЛОГОАНАТОМІЧНЕ БЮРО"</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>24987654</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>52826</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J449" t="n">
+        <v>1</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>61eef11a71624e15a142cc72ea8c630c</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000180-b</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:31:53.813308+02:00</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>КЗ"Дніпропетровський дитячий протитуберкульозний санаторій №7"Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>01984004</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>65391.08</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>05ef9042fb4d4c5ca21489f1a2e5f70a</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000242-b</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:05.742484+02:00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "УРВЕНСЬКИЙ ПСИХОНЕВРОЛОГІЧНИЙ ІНТЕРНАТ" РІВНЕНСЬКОЇ ОБЛАСНОЇ РАДИ</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>03189297</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>40570</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1c14835b4c8f4df48ac67b762817b341</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>UA-2016-01-28-000257-b</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:06.378164+02:00</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>КУ "Першотравенська загальноосвітня спеціальна школа-інтернат"</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>20250549</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>63000</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J452" t="n">
+        <v>1</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>3b1e375a7e194999be263aaaedd43d3f</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000005</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:08.714766+02:00</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Відділ освіти,молоді та спорту Васильківської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>02142402</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>191080</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J453" t="n">
+        <v>1</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>3b24baa442a34908913372cab2eccfe0</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000013-a</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:09.726100+02:00</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Державне підприємство «Ізмаїльський морський торговельний порт»</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>01125815</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>262050</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J454" t="n">
+        <v>1</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>6a133b8ed3d34f348ecdac879bb790a0</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000045-a</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:16.308050+02:00</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Комунальний заклад освіти "Перещепинський НВК "Родина""Загальноосвітний навчальний заклад-дошкільний навчальний заклад І-ІІ ступенів з інтернатним відділенням для дітей -сиріт, дітей, позбавлених батьківського піклування, для дітей з кризових сімей" Новомосковської Районної Ради Дніпропетровської обл.</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>21928485</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>44058.04</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J455" t="n">
+        <v>1</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>5a8ae136730e4090ad11f43aae7a17af</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000061-b</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:17.843270+02:00</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>3555.9</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J456" t="n">
+        <v>1</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>a6854bf55471498db87733ff98702a76</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000075-b</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:20.794617+02:00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Криворізький дитячий санаторій ДОР</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>01986279</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>181471.82</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>de35c4ad9d5d4cd38c9d50f70720cd79</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000091-a</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:22.249572+02:00</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНЕ ПІДПРИЄМСТВО "КИЇВПАСТРАНС"</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>31725604</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>505296</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J458" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>c8b1d8597ad64d2b837bce46c246e275</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000106-a</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:23.446148+02:00</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня №7 Печерського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>01993842</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>8550</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>58670e0cf5ac494eaf6d144867e82199</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000113-b</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:24.161868+02:00</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Тернопільський міський територіальний центр соціального обслуговування населення (надання соціальних послуг)</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>39483390</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>6900</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J460" t="n">
+        <v>1</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>c900042b7430431cbba90478b70b20d5</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000131-b</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:25.505225+02:00</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Клінічний онкологічний диспансер" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>02007265</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>50300</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J461" t="n">
+        <v>1</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1967cee574be42e7b5dc35e97b839afb</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000143-b</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:26.061066+02:00</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>ДП "Відділ освіти Шевченківської РДА"</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>02146216</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>10813</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>e6ce7adccedc428f8164605958731971</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000168-b</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:28.065838+02:00</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Клінічний онкологічний диспансер" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>02007265</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>175559</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J463" t="n">
+        <v>1</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>6f165732fba14a7aa19e44e36b3569c3</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000177-b</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:28.576677+02:00</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>КУ "Першотравенська загальноосвітня спеціальна школа-інтернат"</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>20250549</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>60500</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J464" t="n">
+        <v>1</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>9897aeaaf5cb4e26beef8ed635b7ee40</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000208-b</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:29.906584+02:00</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Нікопольський професійний ліцей</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>02541728</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>883</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>0192adfbe40b49ecbf5e7939bb8c11f1</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>UA-2016-01-29-000256-b</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:32.102298+02:00</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна інфекційна лікарня</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>01993664</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>12795</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>a479c26dc3274d94a81b119c9b154b10</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>UA-2016-01-30-000002-b</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:33.094723+02:00</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД ОСВІТИ "КОТОВСЬКИЙ НАВЧАЛЬНО-РЕАБІЛІТАЦІЙНИЙ ЦЕНТР" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>23078513</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>40990.5</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J467" t="n">
+        <v>1</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>c40f8cd961084c5bac9a6f862aa01611</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UA-2016-02-01-000026</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:39.221146+02:00</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Державна організація Комбінат "Прогрес" Державного агентства резерву України</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>14373207</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J468" t="n">
+        <v>1</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>40901b559efa44edb319cc09f7f9916d</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>UA-2016-02-01-000057</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:44.935755+02:00</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Вінницька обласна дитяча клінічна лікарня</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>03082760</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>24677</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J469" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>ac111f34185148d185af5e522814247e</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>UA-2016-02-01-000062</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:46.007858+02:00</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Відділ освіти,молоді та спорту Васильківської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>02142402</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>182816</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J470" t="n">
+        <v>1</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ce3fa27672ac4dd9a52d4ea8be7281da</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UA-2016-02-01-000066-b</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:32:46.589761+02:00</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>КУ "Миколаївська спеціальна загальноосвітня школа-інтернат І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>22509425</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>38820</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J471" t="n">
+        <v>1</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:03.560307+00:00</t>
         </is>
       </c>
     </row>
@@ -50974,7 +57412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54453,6 +60891,164 @@
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-01-29T04:49:01+00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>{"bytes": 141092}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-30T04:51:49+00:00</t>
+          <t>2026-01-31T04:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478284368.973916.1.9eb3210fb26d70e7ab546128c65e86fc",
-  "updated_at": "2026-01-30T04:51:48.733653+00:00",
-  "pages_done": 475,
-  "tenders_scanned": 47500,
-  "tenders_fetched": 47500,
-  "milk_tenders": 470,
-  "milk_items": 507
+  "offset": "1478284564.913582.1.0cd772466fc28555a4aebb425a5df0f6",
+  "updated_at": "2026-01-31T04:44:11.051368+00:00",
+  "pages_done": 500,
+  "tenders_scanned": 50000,
+  "tenders_fetched": 50000,
+  "milk_tenders": 515,
+  "milk_items": 562
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M508"/>
+  <dimension ref="A1:M563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32420,6 +32420,3458 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>6459c5dc7c5546f19638d5bf20562bbd</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Молоко, 2,6%, пет/пл, 0,900 кг</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>660</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>2016-02-17T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:10.709610+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>7b5d2cf9b4f844e8a241686365a9226e</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Згущене молоко</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>150</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>с. Григорівка</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:10.736054+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>b22271a81259449f9ed0667d5505b2c3</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>70187</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені 10.51.1</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:23.961650+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>355ae8b3a47d40918dccb0e994a5d393</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>f9cc4f6e73424a68ac017397f91f8415</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>10.51.1 Молоко та вершки, рідинні, оброблені (15511000-3 Молоко) 
+ Молоко коров'яче сире, без домішок, з масовою часткою жиру  від 1.0% до 3,2%.</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Косів</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:25.111684+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>30d5fc1424cd4ea9b7e0cc86e5f275ce</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>233d27347c4a48399f2f10eb025337dd</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Товар: молоко коров"яче пастеризоване повинен мати масову частку жиру не менше 2,5% фасоване по 1,0л.</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:27.829587+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>83fac564a10b4a7b954ae5cb58fa5c37</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>0d6536b38e604390b4a89255e502357d</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>100</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>с.Тіньки Чигиринського району</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:28.515872+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>6d3ef8337c7a4a50b1cf59f47c345103</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>1d2589c0fbf94b46987dac60c573f044</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5-2,7% жирності (в пакетах по 900-1000г.)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F515" t="n">
+        <v>600</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>2016-02-14T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>2016-04-14T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:30.984368+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>9cda0eaa80054476b60c0195482d6eb8</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Згущене молоко</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>25</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>2016-02-15T10:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>с. Озера</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:33.889998+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>8c66618206b640d08f25452b08101d33</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>b71c75f950384337992eca5eaebfd160</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Молоко коров’яче питне пастеризоване, жирність 2,5%, масою нетто 1,0 л.</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>2016-02-25T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>2016-12-31T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:34.228744+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>6da005e0af5b403a9b22deaf11286080</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>8ccea67022134c63838d6281b57b30fa</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>2016-02-02T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Тернопольская область</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>м. Бережани</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:43.118896+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>0ad9c9bd175c42198969e6cf8b5cec19</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>80a7c67d41834505b87df6e3d5c57cb5</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Молоко сгущене,в ж /банках</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>80</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>2016-02-08T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>2016-02-09T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:43.933058+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>4588b2b9568645439286a7c4d3738a3d</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>bd656a193dde494891187521497ec776</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F520" t="n">
+        <v>100</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:49.281545+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>f749d392369e470ca77f6f7106af1a4b</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>cebd0415a4a94659b5fe58e9e595375d</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко питне пастеризоване жирністю 2,5%-3,2% паковане до 1000гр. </t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Новомосковск</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:55.003417+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>3b9d3ba8832b482297546f6fcb6f8830</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>9a5ad0e781aa4c60aec88b1038b75161</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>молоко сухе знежирене</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>800</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>2016-03-10T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>2016-07-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Кузнецовськ</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:55.074379+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>845c4e902858492c9bf90766a96417bd</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>fd2554cc5e3049d98c9139a54fd58895</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Молоко та вершки рідинні оброблені, молоко пастеризоване згідно з технічними вимогами</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:56.233179+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>67ea5167bd374667999d1a655317c712</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>859a2144c091469aaedd6a1e62d9c9e9</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Молоко  2,5 %</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>790</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>2016-02-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Тернівка</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:58.489038+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>74aa14cd6493448282edc749ae94f994</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>e8216f2a142042799f4cfcc4ed7baf17</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>100</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>2016-02-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:58.583723+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>b6214cd32a9640f890c358dd062e7c6f</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>29f528e010864aaaaf23bfc67852109b</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Згущене молоко</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>115</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>2016-02-11T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Тернівка</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.306497+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>a6391baef03844bc8ed7b224ae8729ba</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>3284799663ce41c1addf8a9aed19aec3</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>100</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>2016-02-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.326177+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>0516dcef483f4a5c873cb4a3f457cb43</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>74db4589db1947f28981b7cc1fb4f7b9</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F528" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>2016-02-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.878366+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>0516dcef483f4a5c873cb4a3f457cb43</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>e0626d528cb84b8fa3a01255890d643e</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>918</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>2016-02-04T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.878366+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>ec9c88100f9a40a3bf3ccf8c6508e3dc</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>327d86df6b7949ecb18fa133b56865f9</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Молоко коров’яче пастеризоване, питне (масова частка жиру 2,5 %) ДСТУ 2661-2010 поліетиленова упаковка вагою 1 кг.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:12.828005+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2cc6a7e2efd14e68be600e29e313b492</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>70884</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирн. (400 л в неділю)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F531" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Київська обл.</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Чернобыль</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:18.788145+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>17dfd5caec734e2c835afd4194f3d02a</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>a0a9b528f6ad4520856db01c87277dca</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Фенилкетанурия питание (Ф-АМ -2 500 г.)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F532" t="n">
+        <v>8</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>2016-02-09T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:18.803670+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>1ab12703030c48b49750dc7342d10cb4</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>9fac57ff1f264862a949371202b9b09a</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче пастеризоване</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F533" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:19.615932+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>44329242a0104765ad63922c872e4a90</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>375ba8e0a3be4ed4afd089a64e233f01</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Вершки сухі 8% 1 кг</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>30</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.893340+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>44329242a0104765ad63922c872e4a90</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>5f082692ae794ba2892ecd95e6352170</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Вершки порційні 10% 10гр</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.893340+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>44329242a0104765ad63922c872e4a90</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>e4062446f1e64a7fb3561695a4d83101</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Молоко згущене ж/б 370 гр "Первомайськ"</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>150</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.893340+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>0344f5cc98684e5f9cfdb7c30b85013b</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>7febdaa2194745c2a8b051b4c7b49f5f</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5% фас. п/ет.,1л</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F537" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>2016-02-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.970380+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>db0896178631493f9ac7432fc1837fb2</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>0de3674ef1074565a87f6562b353895f</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>молоко 2,5% жирності</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>940</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>2016-02-11T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Чернівці</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:45.525843+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>16c31a7886514d68ac9eed26bb97174e</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>69dff471599542bdb0cdb978e83bc73d</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Молоко пастерізоване 2,5% фас-1л</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F539" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:53.658646+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>e51f9b25d0974f8fbbaee45ff0d6450b</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>e1bb9fd6b0f84855a9b4435c94083c29</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">« Молоко рідке » - код за ДК-016:2010 – 10.51.1 (код CPV 2008 – 15511) </t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F540" t="n">
+        <v>900</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:58.478580+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>7ae3a12971cf44a498be29d23bd9b982</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>302ac82a7c1d48c9bfceb56e550034e9</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Кировоградская область</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Кіровоград</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:02.063127+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>7ae3a12971cf44a498be29d23bd9b982</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>614c1681168847f295845195e42c2e9a</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Молоко згущене залізні банки по 0,370 кг. ДСТУ</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F542" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>2016-12-30T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Кировоградская область</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Кіровоград</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:02.063127+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>b39df8587141426db67f097586a404fe</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>70245e8d63cf4f859dcf9e2e488a1656</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром 8,5% жирності згідно ДК 016:2010 код 10.51.1/ДК 021:2015 код 15511 (Згущене молоко) - 2645 шт., пакування - металева банка 370гр.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F543" t="n">
+        <v>2645</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>2016-03-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Нетішин</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:16.730618+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>6d9d507bd58941348754d24ead3b5303</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>c8f5dcd9817245b08726551f8330c76d</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>молоко свіже, детальна інформація в документації</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>2394</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:27.566846+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>6d9d507bd58941348754d24ead3b5303</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2272670deb214d06bf108a1c816004bd</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>сметана, детальна інформація в документації</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F545" t="n">
+        <v>44</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:27.566846+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>53f4f0d52f1a410ab568da075b700ad7</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>d602c0ef9d974ffbaa39db5fc8957faf</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>дивись документацію</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>250</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>2016-02-14T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:28.970218+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>bf25ccbea3bf48afa44601ca405cbbb4</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>0a260b68c919438988acf4d8fa451269</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване, розфасоване по 0,9 - 1 л, жирність 2,6%</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F547" t="n">
+        <v>480</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Вінницька</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Немирів</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:34.341987+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>fced270e7b264f15a918ca0ed46c594e</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2886627ada954f85b8f982b2621d67d7</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>згущене молоко</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>85</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>2016-02-09T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>г.Николаев</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:39.296654+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>fced270e7b264f15a918ca0ed46c594e</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>937345424ebd47a7a9870d026cc16834</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%  згущене молоко .</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F549" t="n">
+        <v>300</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>2016-02-09T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>г.Николаев</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:39.296654+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>56d10ef31c4b4aa8a6d2370bdd5af573</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>893051b4b02d4346a01a600414a952d4</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване, розфасоване по 0,9 - 1 л, жирність 2,6%</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>480</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Вінницька</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Немирів</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:44.666276+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>cc022677067f4f6cb426c0ae23690dab</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>item_15</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F551" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>с.Васильківка</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:48.908697+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>c7183a8f82da405caa406d5bbd06da3d</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>9ec2ce1039e04a74ae7ed0c0051c9766</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>1. Молоко коров'яче питне пастеризоване, збагачене білком і кальцієм, 2, 5 % жирності, фасоване у поліетиленову плівку, 1кг - 300 кг (ТУУ 15.5-19492247-020-2004); 2. Сметана 21% жирності, фасована у поліетиленову плівку по 0,450 - 30 кг (ДСТУ 4418:2005); 3. Сир кисломолочний (творог) 9% жирності в пачках  0,250 - 112,5 кг (ДСТУ 4554:2006); 4. Масло вершкове 73% вагове - 140 кг (ДСТУ 4399:2005); (Наявність Висновків та Посвідчень про якість завірені печаткою)</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>582</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>2016-02-17T18:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:51.625618+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>f0ed118d29ad478484505b3fd2ce21c2</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>3a9903f8f16441c5b7a2cfb74282cb93</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Молоко у твердих формах</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>380</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>2016-08-18T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>2016-12-12T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>м.Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:52.211188+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>36e269ea46e24dd68d688b3cd9e9adb5</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>de79ebdb14fb454a92334fb61922ec47</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Молоко в пакетах жирністю 2,5%</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Тернопольская область</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>місто Чортків</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.257758+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>e2d8154d8e7a403ebf6bd43ff035cb52</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром 8,5% жирності</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F555" t="n">
+        <v>200</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>2016-02-29T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>с.Макорти</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.784758+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>678b582b19c44a2bb89cfdec759d655a</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>c1602ed89cb944598cde22118f796b9e</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Молоко згущене незбиране з цукром. Фасоване не менш ніж по 370г .  Не містить  ГМО. Продавець повинен передати (поставити) Покупцеві товар, якість яких відповідає діючим ДСТУ 4774:2003, санітарним нормам та підтверджується документом, який підтверджує якість продукту харчування (копія висновку державної санітарно-епідеміологічної експертизи або якісне посвідчення тощо). Доставка продуктів здійснюється спеціалізованим транспортом "Постальника" на адресу "Замовника", за рахунок "Постачальника".Залишок терміну зберігання з моменту поставки, встановленого виробником продукції, повинен бути не менше 70% від загального терміну зберігання. Оплата одноразово після доставки, згідно накладної.</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F556" t="n">
+        <v>150</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>2016-04-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.933024+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>b9607ec41c344e52a18669220186d4a6</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>08ea2361863343369e68378f76c348f6</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Сметана жирністю не менше ніж 20%. Фасована в поліетиленові пакети.  Продавець повинен передати (поставити) Покупцеві товар, якість яких відповідає діючим ДСТУ (ТУ), санітарним нормам та підтверджується документом, який підтверджує якість продукту харчування (копія висновку державної санітарно-епідеміологічної експертизи або якісне посвідчення тощо). Доставка продуктів здійснюється спеціалізованим транспортом Постачальника на адресу Замовника, за рахунок Постачальника - один раз на тиждень. Оплата окремо за кожну партію товару після доставки, згідно накладної.</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F557" t="n">
+        <v>100</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:57.782065+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>b38e2ed2470345a680396d5117296029</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>c8325d6be5584c5d85c0f19885e92d82</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>молоко та вершки, рідинні, оброблені - 2500л</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F558" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>2016-07-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:00.526601+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>item_0</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Каша швидкого приготування «Малишка» молочна суміш рису, вівса, гречки, кукурудзи.</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F559" t="n">
+        <v>221</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>2016-02-19T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>item_1</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Суміш суха на молочно – зерновій основі «Малиш» з гречаним борошном.</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F560" t="n">
+        <v>174</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>2016-02-19T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>item_2</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Суміш суха на молочно – зерновій основі «Малиш» з вівсяним борошном.</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F561" t="n">
+        <v>175</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>2016-02-19T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>item_3</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Суміш суха молочна «Малютка 1» швидкого приготування.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>36</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>2016-02-19T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>item_4</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Суміш суха молочна «Малютка 2» швидкого приготування.</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F563" t="n">
+        <v>7</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>2016-02-19T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32431,7 +35883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K471"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57398,6 +60850,2391 @@
       <c r="K471" t="inlineStr">
         <is>
           <t>2026-01-30T04:51:03.560307+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>6459c5dc7c5546f19638d5bf20562bbd</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000001</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:10.709610+02:00</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Київмедспецтранс</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>01993807</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>7010</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J472" t="n">
+        <v>1</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>7b5d2cf9b4f844e8a241686365a9226e</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000001-a</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:10.736054+02:00</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Відділ освіти Світловодської РДА</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>02144174</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>86000</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J473" t="n">
+        <v>1</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>b22271a81259449f9ed0667d5505b2c3</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000089-a</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:23.961650+02:00</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Державне спеціалізоване підприємство «Чорнобильська АЕС»</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>14310862</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J474" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>355ae8b3a47d40918dccb0e994a5d393</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000098-a</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:25.111684+02:00</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Косівська центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>01993546</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>84000</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>30d5fc1424cd4ea9b7e0cc86e5f275ce</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000122-a</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:27.829587+02:00</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська клінічна лікарня №3"</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>02005763</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>55100</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J476" t="n">
+        <v>1</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>83fac564a10b4a7b954ae5cb58fa5c37</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000130-a</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:28.515872+02:00</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>89488</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J477" t="n">
+        <v>0</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>6d3ef8337c7a4a50b1cf59f47c345103</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000143-a</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:30.984368+02:00</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна шкірно-венерологічна лікарня</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>01994008</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J478" t="n">
+        <v>1</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>9cda0eaa80054476b60c0195482d6eb8</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000170-a</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:33.889998+02:00</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Відділ освіти Світловодської РДА</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>02144174</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>8c66618206b640d08f25452b08101d33</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000172-b</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:34.228744+02:00</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська дитяча поліклініка"</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>23248085</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>41100</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J480" t="n">
+        <v>1</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>6da005e0af5b403a9b22deaf11286080</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000324-b</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:43.118896+02:00</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Відділ освіти, молоді і спорту Бережанської міської ради</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>40211011</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>114775</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J481" t="n">
+        <v>1</v>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>0ad9c9bd175c42198969e6cf8b5cec19</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>UA-2016-02-02-000340-b</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:43.933058+02:00</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровський професійний залізничний ліцей "</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>05536107</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>30600</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J482" t="n">
+        <v>1</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>4588b2b9568645439286a7c4d3738a3d</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000006-a</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:49.281545+02:00</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>169275</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>f749d392369e470ca77f6f7106af1a4b</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000035-b</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:55.003417+02:00</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дитячий оздоровчий центр соціальної реабілітації санаторного типу "ПЕРЛИНА  ПРИДНІПРОВ'Я" Дніпропетровсткої обласної ради"</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>37179958</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>60440</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J484" t="n">
+        <v>1</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>3b9d3ba8832b482297546f6fcb6f8830</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000037-a</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:55.074379+02:00</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>відокремлений підрозділ „Рівненська АЕС” державного підприємства   „Національна атомна енергогенеруюча компанія “Енергоатом”</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>05425046</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>54720</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J485" t="n">
+        <v>1</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>845c4e902858492c9bf90766a96417bd</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000045-a</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:56.233179+02:00</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська лікарня №4"</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>02005778</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J486" t="n">
+        <v>1</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>67ea5167bd374667999d1a655317c712</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000067-b</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:58.489038+02:00</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>КУ "ТЕРНІВСЬКА ЦЕНТРАЛЬНА МІСЬКА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>01987445</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>8863.799999999999</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>74aa14cd6493448282edc749ae94f994</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000070-a</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:33:58.583723+02:00</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>90650</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>b6214cd32a9640f890c358dd062e7c6f</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000122-a</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.306497+02:00</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>КУ "ТЕРНІВСЬКА ЦЕНТРАЛЬНА МІСЬКА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>01987445</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>4249.25</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J489" t="n">
+        <v>1</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>a6391baef03844bc8ed7b224ae8729ba</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000122-b</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.326177+02:00</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>182225</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J490" t="n">
+        <v>0</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>0516dcef483f4a5c873cb4a3f457cb43</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000129-a</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:04.878366+02:00</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>КУ "Одеська загальноосвітня санаторна школа-інтернат №6 І-ІІ ступенів"</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>20986121</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>97305</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ec9c88100f9a40a3bf3ccf8c6508e3dc</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000154-a</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:12.828005+02:00</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>КУ "КЗ "Дніпропетровська МКЛ № 9" ДОР""</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>01984613</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2cc6a7e2efd14e68be600e29e313b492</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000201-b</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:18.788145+02:00</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Державне спеціалізоване Підприємство "Чорнобильський спецкомбінат"</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>37197165</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>390000</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J493" t="n">
+        <v>1</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>17dfd5caec734e2c835afd4194f3d02a</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000202-b</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:18.803670+02:00</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>КЗ "Дніпропетровський центр первинної медико-санітарної допомоги №2"</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>37899741</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>9790</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J494" t="n">
+        <v>1</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>1ab12703030c48b49750dc7342d10cb4</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UA-2016-02-03-000215-b</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:19.615932+02:00</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня №7" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>05411245</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>22578</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J495" t="n">
+        <v>1</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>44329242a0104765ad63922c872e4a90</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000126-b</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.893340+02:00</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>ДП ""НАФТОГАЗОБСЛУГОВУВАННЯ" НАЦІОНАЛЬНОЇ АКЦІОНЕРНОЇ КОМПАНІЇ "НАФТОГАЗ УКРАЇНИ""</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>31059253</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J496" t="n">
+        <v>1</v>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>0344f5cc98684e5f9cfdb7c30b85013b</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000127-a</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:44.970380+02:00</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>ДП "Дитяча клінічна лікарня №4 Соломянського району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>01994037</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>1</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>db0896178631493f9ac7432fc1837fb2</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000133-b</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:45.525843+02:00</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Комунальна медична установа "Міська поліклініка №1"</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>30311923</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>9100</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>16c31a7886514d68ac9eed26bb97174e</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000203-b</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:53.658646+02:00</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>КЗ "Дитяча лікарня м.Дніпродзержинська"ДОР"</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>01985848</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>77250</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>1</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>e51f9b25d0974f8fbbaee45ff0d6450b</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000268-b</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:34:58.478580+02:00</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровська міська дитяча клінічна лікарня №1"Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>01984464</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>9650</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>1</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>7ae3a12971cf44a498be29d23bd9b982</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>UA-2016-02-04-000340-b</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:02.063127+02:00</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Центр соціально-психологічної реабілітації дітей" Кіровоградської обласної ради</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>23683214</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>162500</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>1</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>b39df8587141426db67f097586a404fe</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000059-b</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:16.730618+02:00</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>ВП ХАЕС ДП "НАЕК "Енергоатом"</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>21313677</t>
+        </is>
+      </c>
+      <c r="H502" t="n">
+        <v>49990.5</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>1</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>6d9d507bd58941348754d24ead3b5303</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000151-b</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:27.566846+02:00</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Криворізький дитячий санаторій ДОР</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>01986279</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>181472</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>53f4f0d52f1a410ab568da075b700ad7</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000167-a</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:28.970218+02:00</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Олімпійський навчально-спортивний центр "КОНЧА-ЗАСПА"</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>38217021</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>5260</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>1</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>bf25ccbea3bf48afa44601ca405cbbb4</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000216-a</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:34.341987+02:00</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Брацлавський навчально-виховний комплекс:дошкільний навчальний заклад, загальноосвітня школа-інтернат І-ІІІ ступенів-гімназія Вінницької обласної  ради</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>20096812</t>
+        </is>
+      </c>
+      <c r="H505" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>fced270e7b264f15a918ca0ed46c594e</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000314-b</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:39.296654+02:00</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Міський пологовий будинок №1</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>05483138</t>
+        </is>
+      </c>
+      <c r="H506" t="n">
+        <v>7335</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>56d10ef31c4b4aa8a6d2370bdd5af573</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UA-2016-02-05-000397-b</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:44.666276+02:00</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Брацлавський навчально-виховний комплекс:дошкільний навчальний заклад, загальноосвітня школа-інтернат І-ІІІ ступенів-гімназія Вінницької обласної  ради</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>20096812</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>cc022677067f4f6cb426c0ae23690dab</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000008-b</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:48.908697+02:00</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Відділ освіти,молоді та спорту Васильківської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>02142402</t>
+        </is>
+      </c>
+      <c r="H508" t="n">
+        <v>196754</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J508" t="n">
+        <v>1</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>c7183a8f82da405caa406d5bbd06da3d</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000027-a</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:51.625618+02:00</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна туберкульозна лікарня</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>01993687</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>22505</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J509" t="n">
+        <v>1</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>f0ed118d29ad478484505b3fd2ce21c2</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000034-a</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:52.211188+02:00</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>КЗОЗ ДНІПРОДЗЕРЖИНСЬКОЇ МІСЬКОЇ РАДИ "ЦЕНТР ПЕРВИННОЇ МЕДИКО-САНІТАРНОЇ ДОПОМОГИ №2"</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>37906554</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>16609</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J510" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>36e269ea46e24dd68d688b3cd9e9adb5</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000044-a</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.257758+02:00</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>ЧОРТКІВСЬКА ЦЕНТРАЛЬНА КОМУНАЛЬНА РАЙОННА ЛІКАРНЯ</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>02001185</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>18700</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>e2d8154d8e7a403ebf6bd43ff035cb52</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000047-b</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.784758+02:00</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Софіївська виправна  колонія (№45)</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>08562973</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>678b582b19c44a2bb89cfdec759d655a</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000049-c</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:53.933024+02:00</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Тернопільський міський територіальний центр соціального обслуговування населення (надання соціальних послуг)</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>39483390</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>3225</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>b9607ec41c344e52a18669220186d4a6</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000067-c</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:35:57.782065+02:00</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Тернопільський міський територіальний центр соціального обслуговування населення (надання соціальних послуг)</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>39483390</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J514" t="n">
+        <v>1</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>b38e2ed2470345a680396d5117296029</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000090-b</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:00.526601+02:00</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Клінічна лікарня №15 Подільського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>26199074</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>23800</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>662030ec33944ef781393e58d93ea293</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000098-a</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:01.265315+02:00</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровський центр первинної медико-санітарної допомоги № 9"</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>37899715</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>20334.95</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:43:15.980609+00:00</t>
         </is>
       </c>
     </row>
@@ -57412,7 +63249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61049,6 +66886,164 @@
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-30T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>{"bytes": 159321}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-31T04:44:11+00:00</t>
+          <t>2026-02-01T05:09:53+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478284564.913582.1.0cd772466fc28555a4aebb425a5df0f6",
-  "updated_at": "2026-01-31T04:44:11.051368+00:00",
-  "pages_done": 500,
-  "tenders_scanned": 50000,
-  "tenders_fetched": 50000,
-  "milk_tenders": 515,
-  "milk_items": 562
+  "offset": "1478284765.04535.1.636d791b83fe95682d413889925e0857",
+  "updated_at": "2026-02-01T05:09:52.997693+00:00",
+  "pages_done": 525,
+  "tenders_scanned": 52500,
+  "tenders_fetched": 52500,
+  "milk_tenders": 554,
+  "milk_items": 625
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M563"/>
+  <dimension ref="A1:M626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35872,6 +35872,4038 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>7b35113d03c14c49a70bae5426f8ca4f</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>511e2b1b5b8f4f00ab0a5551ac186532</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F564" t="n">
+        <v>100</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:21.094962+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>a57123b42a0844c189b3ad15bacfbac1</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>781ec3efacca437b883afb280b0d76c1</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F565" t="n">
+        <v>10100</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Тернопольская область</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>м. Бережани</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:27.749495+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>662b345b5f9b485cbdf6c41a483d8734</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>b841d7362abf46eaa14c1f5474087afe</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Молоко згущене з цукром жирністю 8,5%</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F566" t="n">
+        <v>300</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:33.032943+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>670833ae50594260b1becb6ced860887</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>a9321c1742144aada2499f7cf321cae3</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Молоко коров`яче пастеризоване питне 2,5% жиру 500г</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F567" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:44.838916+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>670833ae50594260b1becb6ced860887</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>999ac1e2c81c4c3a9807946aa1ac9ea3</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Молоко коров`яче пастеризоване питне 2,5% жиру 1000г</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F568" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:44.838916+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>a2c35dc650ea4b2498e0f8c6d7cf69ab</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>8cf38e516a16434d9d856de4fad225e3</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирності фасоване по 1кг. Доставка кожний день</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F569" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>2016-02-15T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:50.459423+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>bf8fe605cc184b939a96e38c12221071</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>ce3ecebcbd584b75b6fb43d3660d17a8</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> молоко цільне</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F570" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2016-02-09T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>м. Кілія</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:52.614427+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>0193806608c2402890eb60e791a51b5e</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>d1eb32fe7e8c49099adc17aea9071aa5</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване 2,5% жир. 0,5 л пакетоване</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F571" t="n">
+        <v>900</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>2016-02-23T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>м. Ныкополь</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:59.384294+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>d17d37da562d4179823a485be1b662f4</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2e42499eea0d4f019bd27c62d4636c32</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Перелік згідно додатку:
+Молоко та вершки, згущені, підсолоджені- 500 банок
+Масло вершкове з умістом жиру не більше ніж 85 мас.%- 1000 кг</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F572" t="n">
+        <v>2</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:01.660269+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>ca53d3eefebb43c9bdd018dba4014000</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>9c7a647e7ac55495c8c5e7cb60d5b677</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>1.	Олія раф. Соняшникова 17,7 кг 2.	Сіль кам’яна 8,7 кг 3.	Картопля 370,8 кг  4.	Вироби кондитерські 35,5 кг 5.	Мед  6,1 кг 6.	Сухофрукти 9,6 кг 7.	Кавовий напій 3,2кг 8.	Цукор-пісок 62,5 кг 9.	Чай 0,4 кг 10.	Яблука 100,5 кг 11.	Апельсини 83,8 кг 12.	Банани 83,2 кг 13.	Борошно пшеничне 301,1 кг 14.	Риба с/м 89,3 кг 15.	Сосиски, 23,4 кг 16.	Ковбаса Сервелат «Столичний» 12,8 кг 17.	Соки фруктові, 176,6 л 18.	Крупа гречана 19,8 кг 19.	Рис 16,8 кг 20.	Крупа ячнєва 16,8 кг 21.	Макаронні вироби 17,6 кг 22.	Паста томатна 3,6 кг 23.	Яйця 1297шт 24.	М`ясо  77,3 кг 25.	Окорочка курячі 70,1 кг 26.	Молоко згущене 63,1 кг 27.	Кефір 17,3 л 28.	Дріжджі сухі 1,9 кг 29.	Сир твердий 17,9 кг 30.	Сир кисломолочний 62,8 кг 31.	Масло вершкове 44,7 кг 32.	Сметана 22,3 кг 33.	Капуста б/к 136,4 кг 34.	Буряк столовий 114,9 кг 35.	Морква столова  83,8 кг 36.	Цибуля ріпчаста 83,8 кг</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F573" t="n">
+        <v>3553</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>м.Новомосковськ</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:08.564677+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>778decc705f74411bd3ef1110fd8e7cc</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>bad2906bba3f40b7b6290ee851e60903</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Молоко питне пастеризоване 2,5% упаковки по 1 л.
+ Вимоги: відповідає вимогам Держ. Спожив. Стандарту України, супроводжується сертифікатами якості та зазначенням дати виготовлення та терміну придатності на упаковці.
+Постачання: автотранспорт обладнаний холодильним обладнанням.
+Місце знаходження (складів): м. Київ, Київська область.
+Водій (водій – експедитор): обов'язкова наявність медичної книжки.
+Замовлення: після замовлення продукту постачання на наступну добу, 3 рази на тиждень. Місце поставки :м.Київ, вул.Волинська,21</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F574" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>2016-02-15T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:18.224637+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>06307b0125744c068e936caf3d4587e2</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>55edfd24daee14f74703cd1ca94677ea</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване, жирність 2,5 %</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F575" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>2016-06-15T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Рівненська область</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>місто Острог</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:27.604977+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>81eb5e297f5b49c2b6a9827e1fed4114</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>8924f719255d44ecb6501abea55d8e38</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>молоко 2,5%</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F576" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2016-02-17T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>місто Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:32.516174+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>f08214f0507440a48f59b6a41c888831</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>1f65c8210eef446890eb2d80268b8a73</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Молоко,кефір,масло вершкове,сир твердий (детальний опис дивитись у оголошенні)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F577" t="n">
+        <v>4</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>м.Вознесенськ</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:40.795202+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>c31bd15422a54cdfb4feb66514ff5aee</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>8935e5afccc940aeb070fc0805a3e25c</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%, фасоване по 0,5л</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F578" t="n">
+        <v>1506</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Кировоградская область</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Олександрія</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:52.380217+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>da122ad65ef24eb7b72d5f62b3fab163</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>439d2c0b1b9a4b41a7a43ab86633f877</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Молоко коров’яче питне пастеризоване жирністю 2,6%</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F579" t="n">
+        <v>3440</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>2016-07-25T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>м. Жовті Води</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:52.483324+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>d15fab1a323a4fe18fb792218d33041a</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2.6% фасоване у пакети 1 л</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F580" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>2016-02-19T08:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>2016-08-31T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Миколаївська обл.</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>м. Миколаїв</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:53.027136+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>4fccf6e011da4c51ab94fc3fb9d761b1</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>45ef01d161354736bc680145083053d9</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Сосиски фірмові з молоком, вищий гатунок</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>15131130-5</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F581" t="n">
+        <v>162</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:53.079808+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>229be27e90604c7888eaa0e075fc376c</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>e539a128f3b2497e9738d35e7ac40634</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F582" t="n">
+        <v>128</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>2016-03-07T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Донецкая область</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>смт Мангуш</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:58.329048+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>d8e862b0b68843868a124a8bb1740a3f</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>45b72be611f645a18d74222f0d4ef48e</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче пастеризоване</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F583" t="n">
+        <v>2258</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:02.100013+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>d55bc7f117d8449581cd75da51e9818a</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>7ec1898fd55d4a25b73507b31ff27e40</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F584" t="n">
+        <v>100</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:03.975974+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ce35f28da6fc48c5b6fbafb0de2221f6</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>dfc5fa0f3531404687e7008371b9b5f6</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F585" t="n">
+        <v>100</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:04.089651+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>6223b20deb2444e491b551f0cd47c183</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>abb485f532ce4008ac3747835bed5e5f</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>100</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>с.Вітове</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:05.104324+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>34f3da006bad4df2b1406562a4494ce8</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>7aa7f766f6814e0faa5e7630b162b8b3</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>03212100-1</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F587" t="n">
+        <v>30</v>
+      </c>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:12.992990+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>54d1012f5c2b4f32bd1d5bddd4074bb7</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Молоко згущене для КДНЗ "Ромашка"</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F588" t="n">
+        <v>220</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>с. Михайлівка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>25554ac386b54fbb993f2558da2f3577</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ №2 "Барвінок"  </t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F589" t="n">
+        <v>240</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>b75a4d59400c4b14a66200fcd0d35f5c</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ "Ромашка" </t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F590" t="n">
+        <v>600</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>с. Кам'янка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>ed7993111687406ea17949092dfe8266</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ "Казка" </t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F591" t="n">
+        <v>68</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>с. Перше Травня, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>7e16d2794d0a47b18d549e29a94bbc6b</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ "Кульбабка" </t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F592" t="n">
+        <v>65</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>с. Запорізьке, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ea2d7acdd1b343b6844c3661611dc6d3</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Молоко згущене для КДНЗ "Казка"</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F593" t="n">
+        <v>296</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>с. Цемзавод (Жовте) Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>676e085af68e448680b1c0c739734f0d</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ "Українка" </t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>250</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>с. Українка. Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>da03603faf8349c6997835919a621378</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ №1 "Малятко" </t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F595" t="n">
+        <v>1002</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>м.Апостолове</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>f8725914bb1f4e97a0714a9ffb403913</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене для КДНЗ №3 "Струмочок" </t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F596" t="n">
+        <v>428</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>1115faadbda04bcd863ab3ac48b77ee6</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2db0a005ceb841fda926e03e981121ad</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>100</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>c.Галагінівка</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:39.823587+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>62665c28793d421596711ce89f3e96e0</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Молоко свіже для КДНЗ "Ромашка"</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
+        <v>450</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>с. Михайлівка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>36ad59ab0f084590b2e9352c4bd617bf</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №2 "Барвінок"  </t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F599" t="n">
+        <v>360</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>fe6b262c20084716a01d61ef9944302a</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Ромашка" </t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F600" t="n">
+        <v>600</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>с. Кам'янка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>475635de28ac461cb3af597af163e0e7</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Казка" </t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F601" t="n">
+        <v>40</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>с. Перше Травня, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>c362d97f478f4ded9dd4b4c7c42a4e82</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Кульбабка" </t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>60</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>с. Запорізьке, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>d305af2fd3674d6eae0dbc85eca4ba6f</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Українка" </t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F603" t="n">
+        <v>180</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>с. Українка. Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>5b7aae9578dd4458a5a259adcedd34bd</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №1 "Малятко" </t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F604" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>м.Апостолове</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>e9c072cfcf3c4186ae24d5cf12c2fd2f</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №3 "Струмочок" </t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F605" t="n">
+        <v>200</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>49894d5ba5f8452a88c4d28e2b165f4b</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Сметана для КДНЗ "Ромашка"</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F606" t="n">
+        <v>38</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>с. Михайлівка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>5158e8e358b04979918bdca68120eef7</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ №2 "Барвінок"  </t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F607" t="n">
+        <v>72</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>826562704aeb480a8fa137eb9f707f7b</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ "Ромашка" </t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F608" t="n">
+        <v>50</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>с. Кам'янка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>aba4db3a121049fa8dd368c92809cdb6</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ "Казка" </t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F609" t="n">
+        <v>13</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>с. Перше Травня, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>08c7510afc8544c4a94becbfd9ddff5e</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Сметана для КДНЗ "Казка"</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>40</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>с. Цемзавод (Жовте) Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>3448659d7fb445fbbb3e4ddc36ebff29</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ "Українка" </t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F611" t="n">
+        <v>24</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>с. Українка. Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>7d76fef3f78548ac959e71ccc3b6c148</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ №1 "Малятко" </t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F612" t="n">
+        <v>220</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>м.Апостолове</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>0036ed2a99494811bc9dbe408c2d1819</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сметана для КДНЗ №3 "Струмочок" </t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>48</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>52718e738fed4247a62af7b8f2a52029</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Сметана для КДНЗ "Кульбабка"</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>14</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>с. Запорізьке, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>4aa688198efa41488456cd421cc3e3ba</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>644e6f2a78844a948420ff60f11cf544</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Молоко жирністю не менше 2,5%</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Николаевская область</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Миколаїв</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:49.696922+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>80c93e450b604de2a9c401f6ef6d72fc</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>e1f248e38071417682d4dd28bcc4a645</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>100</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>с.Головківка</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:58.867267+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>9373a7e38871464abdfdb846e77261e3</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>43edce0761f04e14a5244e36af7ae00d</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>100</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>с.Трушівці</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:59.837133+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>bb8001c87fa140549096f3fa1e50d823</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>9f07b3991cc0441c85a6dd0993d2d137</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>100</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>с.Медведівка</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:00.115882+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>81418e4d3dc248f4a5e7531a3a12fbe7</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>ddf481e5190c4db7aa4fdfe7cf544d40</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>100</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>с.Топилівка</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:01.882949+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>491d6731604349b6af886bf40a335a12</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>cd2c34fd741348adb0760e5ae93a9978</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - 400	літрів. Скорочена процедура закупівлі в зв'язку з нагальною потребою для безперебійного лікувального процесу.</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>400</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>2016-02-21T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>2016-04-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:02.898752+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>3ab1cc57954c4624b040c896f4c3fc55</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>f674fc1cf9fa417fb303160b7c1e429f</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко незбиране в порошку (з умістом жиру 25 мас.%) </t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>100</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:10.028245+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>5178e4cb905948618e48112cce1b66a6</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>0117eb31801a4dc997e397a0435aff56</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:13.444804+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>abd39fcbc3fc4be6abbc56ad4dc68317</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>7b7d4fd3f0dd47c18ea914feb2cdbfe8</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>молоко коров’яче пастеризоване питне з масовою часткою жиру 2, 5%, детальний опис технічних (якісних) вимог викладено в окремо доданому документі</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>11880</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:15.709953+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>3257c292ef1d4691b3b44d6293d2cd3b</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>0397a87fc9ba4c6482d332ea50eb1423</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче питне пастеризоване, збагачене білком і кальцієм 2,5 % жиру, згідно ТУУ 15.5-19492247-020-2004 "Молоко коров'яче питне. Молоко коров'яче питне, збагачене білком і кальцієм". Фасоване в полиетиленові пакети, ємністю 1 кг. Строк придатності не більше 3-х діб при температурі 4+-2 град.С. Періодичність поставки 2 рази на тиждень (понеділок та четвер).</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:16.792965+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>cbc59c7df8e14aa1bdfde2f2f336abd4</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>b03b0df4879646beb79c9b2a44663be6</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, 2,5% - 5400 л. Пропозицію надавати відповідно до документації.</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>2016-02-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>2016-09-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:17.871423+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>609a436d62654b3d801011e8567afca3</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>de14b53ebecf49e6a9a1961acc341814</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%        0,9л.            5500 л
+Творог 5%           200гр.            300 кг
+Сметана 20%      400гр            100 кг</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>5900</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:21.924263+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35883,7 +39915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63235,6 +67267,2073 @@
       <c r="K516" t="inlineStr">
         <is>
           <t>2026-01-31T04:43:15.980609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>7b35113d03c14c49a70bae5426f8ca4f</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000192-b</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:21.094962+02:00</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКА ШОСТА МІСЬКА КЛІНІЧНА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ </t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>01984441</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J517" t="n">
+        <v>1</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>a57123b42a0844c189b3ad15bacfbac1</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>UA-2016-02-08-000247-b</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:27.749495+02:00</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Відділ освіти, молоді і спорту Бережанської міської ради</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>40211011</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>115140</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J518" t="n">
+        <v>1</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>662b345b5f9b485cbdf6c41a483d8734</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000009-b</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:33.032943+02:00</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКА ШОСТА МІСЬКА КЛІНІЧНА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ </t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>01984441</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>15450</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J519" t="n">
+        <v>1</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>670833ae50594260b1becb6ced860887</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000087-b</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:44.838916+02:00</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКА ШОСТА МІСЬКА КЛІНІЧНА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ </t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>01984441</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>35607.8</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J520" t="n">
+        <v>1</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>a2c35dc650ea4b2498e0f8c6d7cf69ab</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000118-c</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:50.459423+02:00</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Пуща-Водицький психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>03188795</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>77000</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J521" t="n">
+        <v>1</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>bf8fe605cc184b939a96e38c12221071</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000133-b</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:52.614427+02:00</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Комунальний заклад " Кілійська спеціальна  загальноосвітня школа-інтернат 1-11 ступенів"</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>20991955</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>35200</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>0193806608c2402890eb60e791a51b5e</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000173-b</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:36:59.384294+02:00</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Нікопольська центральна районна лікарня"Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>05494716</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>12132</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J523" t="n">
+        <v>1</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>d17d37da562d4179823a485be1b662f4</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000220-b</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:01.660269+02:00</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Перинатальний центр м.Києва</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>22964365</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>110000</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J524" t="n">
+        <v>1</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>ca53d3eefebb43c9bdd018dba4014000</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>UA-2016-02-09-000311-b</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:08.564677+02:00</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Професійно-технічне училище № 48 м. Новомосковська</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>02541763</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>65200</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>778decc705f74411bd3ef1110fd8e7cc</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000048-c</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:18.224637+02:00</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 3 Солом"янського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>01993747</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>78540</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>1</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>06307b0125744c068e936caf3d4587e2</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000069-c</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:27.604977+02:00</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>КЗ "Острозький обласний ліцей-інтерна з посиленою військово-фізичною підготовкою" Рівненської обласної ради</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>26062852</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>14625</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>81eb5e297f5b49c2b6a9827e1fed4114</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000088-a</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:32.516174+02:00</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровське дванадцяте територіальне медичне об`єднання" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>01984820</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>28010</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>f08214f0507440a48f59b6a41c888831</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000122-a</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:40.795202+02:00</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>КУ "Вознесенська центральна районна лікарня"</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>01998443</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>1</v>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>c31bd15422a54cdfb4feb66514ff5aee</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000218-a</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:52.380217+02:00</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Міська комунальна лікувально-профілактична установа - стоматологічна поліклініка</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>23230659</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>9100</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J530" t="n">
+        <v>1</v>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>da122ad65ef24eb7b72d5f62b3fab163</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000220-a</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:52.483324+02:00</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Комбінат шкільного харчування" Жовтоводської міської ради"</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>19139338</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>41280</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>d15fab1a323a4fe18fb792218d33041a</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000233-a</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:53.027136+02:00</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Миколаївська обласна психіатрична лікарня №1</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>01998325</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J532" t="n">
+        <v>1</v>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>4fccf6e011da4c51ab94fc3fb9d761b1</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000234-a</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:53.079808+02:00</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Середня загальноосвітня школа №18 м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>23370739</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>9224.280000000001</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J533" t="n">
+        <v>1</v>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>229be27e90604c7888eaa0e075fc376c</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>UA-2016-02-10-000312-a</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:37:58.329048+02:00</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Відділ освіти Першотравневої РДА</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>02142715</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>89700</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J534" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>d8e862b0b68843868a124a8bb1740a3f</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000030-a</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:02.100013+02:00</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня №7" Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>05411245</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>22580</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J535" t="n">
+        <v>1</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>d55bc7f117d8449581cd75da51e9818a</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000031-c</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:03.975974+02:00</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>76244</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J536" t="n">
+        <v>1</v>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ce35f28da6fc48c5b6fbafb0de2221f6</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000033-b</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:04.089651+02:00</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>142374</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>1</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>6223b20deb2444e491b551f0cd47c183</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000039-b</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:05.104324+02:00</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>54943</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
+        <v>1</v>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>34f3da006bad4df2b1406562a4494ce8</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000084-a</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:12.992990+02:00</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Першотравнева центральна районна лікарня</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>01989881</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J539" t="n">
+        <v>1</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ec1c523537e1491bbdf399a905ac937c</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000178-a</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:31.675659+02:00</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Виконавчий комітет Апостолівської міської ради</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>40209395</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>190325</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J540" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1115faadbda04bcd863ab3ac48b77ee6</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000192-a</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:39.823587+02:00</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>51436</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J541" t="n">
+        <v>1</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2ccd270e8ac449cd9f3b1cd3522a56ca</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000193-a</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:40.033222+02:00</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Виконавчий комітет Апостолівської міської ради</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>40209395</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>56870</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>705c467af3b44b5e819510780a282892</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000212-a</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:41.968767+02:00</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Виконавчий комітет Апостолівської міської ради</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>40209395</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>19073</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J543" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>4aa688198efa41488456cd421cc3e3ba</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>UA-2016-02-11-000326-a</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:49.696922+02:00</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Міська дитяча лікарня №2</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>05483121</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>64000</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>80c93e450b604de2a9c401f6ef6d72fc</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000028-b</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:58.867267+02:00</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>33901</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>9373a7e38871464abdfdb846e77261e3</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000035-b</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:38:59.837133+02:00</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>86506</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>bb8001c87fa140549096f3fa1e50d823</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000036-c</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:00.115882+02:00</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>71309</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J547" t="n">
+        <v>1</v>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>81418e4d3dc248f4a5e7531a3a12fbe7</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000050-c</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:01.882949+02:00</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>14028</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J548" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>491d6731604349b6af886bf40a335a12</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000058-c</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:02.898752+02:00</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>5440</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J549" t="n">
+        <v>1</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>3ab1cc57954c4624b040c896f4c3fc55</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000101-a</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:10.028245+02:00</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>КП "Дніпродзержинська міська лікарня №1 Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>01985794</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J550" t="n">
+        <v>1</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>5178e4cb905948618e48112cce1b66a6</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000116-b</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:13.444804+02:00</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>КИЇВСЬКА МІСЬКА КЛІНІЧНА ЛІКАРНЯ №4</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>30212155</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>46750</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J551" t="n">
+        <v>1</v>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>abd39fcbc3fc4be6abbc56ad4dc68317</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000131-c</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:15.709953+02:00</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Зеніт" Деснянського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>19027846</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>140000</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>3257c292ef1d4691b3b44d6293d2cd3b</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000139-a</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:16.792965+02:00</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Київський міський протитуберкульозний диспансер № 1</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>05416202</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J553" t="n">
+        <v>1</v>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>cbc59c7df8e14aa1bdfde2f2f336abd4</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000148-c</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:17.871423+02:00</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 5 Святошинського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>00185011</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>48600</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J554" t="n">
+        <v>1</v>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>609a436d62654b3d801011e8567afca3</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>UA-2016-02-12-000164-a</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:21.924263+02:00</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Київський міський центр репродуктивної та перинатальної медицини</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>02124976</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>94000</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J555" t="n">
+        <v>1</v>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:10.218334+00:00</t>
         </is>
       </c>
     </row>
@@ -63249,7 +69348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67044,6 +73143,164 @@
       </c>
       <c r="E144" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-31T04:44:11+00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>{"bytes": 172825}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-01T05:09:53+00:00</t>
+          <t>2026-02-02T05:07:33+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478284765.04535.1.636d791b83fe95682d413889925e0857",
-  "updated_at": "2026-02-01T05:09:52.997693+00:00",
-  "pages_done": 525,
-  "tenders_scanned": 52500,
-  "tenders_fetched": 52500,
-  "milk_tenders": 554,
-  "milk_items": 625
+  "offset": "1478284961.29498.1.79a84806281323773c9f5b3177e3b14b",
+  "updated_at": "2026-02-02T05:07:32.851001+00:00",
+  "pages_done": 550,
+  "tenders_scanned": 55000,
+  "tenders_fetched": 55000,
+  "milk_tenders": 599,
+  "milk_items": 677
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M626"/>
+  <dimension ref="A1:M678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39904,6 +39904,3306 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>e18112da9cf74f708a0adc1810cfebe2</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>b61e1eff63824a9eb7aac7193cd635f5</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване-1,5% жирності.</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:32.785660+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>35f6630b0cee4d259fd093f08e86fa5f</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>83f79b639771145108eb8aa2dfb6cb0a</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>50</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr"/>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>2016-03-02T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>смт. Вороновиця</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:37.556017+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>d00183dfd6594972812a85d36f9d5922</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>252c479b1b9d4c9ab7cdce21e6db29b9</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>120</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:40.791413+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>625b82d32ba4435bbc58af35cc75ce45</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>cae4452b702b4c8d8bd436ab3404831d</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Молоко 2,5-2,6% жирності фасоване по 1кг. Доставка кожний день</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:50.265927+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>1a971722ca114ab9b8fe32ab4635dad9</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>44d559a2670c408f92580e38fbc5bb66</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Борошно пш.,цукор,рис,крупи( гречана, пшенична, пшона , горох),макаронні вироби,дріжджі пресовані, хлібопекарські,чай,кофейний напиток,какао, молоко згущене,ковбасні вироби ( сарделі з вершками , ковбаса молочна , сосиськи, ковбаса полукопчена ),тушенка,м’ясо та харчові су продукції птиці ( філе куряче),м’ясо  свіже та заморожене (свинина, яловичина),риба с/м "Хек",печінка яловичина, субпродукти із м’яса,Масло вер.,олія та жири очищені,маргарин,овочі різні,томатна паста,вироби сухарні,концервації,та інше.</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>4962</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>2016-10-26T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:53.668642+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>861ee4b23884411096d5f9e1ac1217e3</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>4e74b052cb9447e8b7f1307395943182</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, жирністю не менше 2,6%, фасоване у поліетиленовий пакет по 1л, ТУ У 15.5-23063575-004-2003 - 1700л.;</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>15530000-2</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>2016-02-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:59.006300+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>be22a9e4e16245438d8b40fcee4333ea</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>433889391fb14897a8df4b6f6fece928</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Молоко згущене, жир.8,5%, фас. 380 г  ж/банка</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>57</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>2016-02-21T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:01.905142+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>19d65e25b58643e1b8faec8865b818e8</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>22bcadd07c8b44b68212aa68b3d01d1e</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>2016-03-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Полтавская область</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Полтава</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:03.435641+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>ea5c7e8dff134d8c8e44ba42c8694293</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>c64b599a50e64088825a4a7965080593</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Молоко незбиране згущене з цукром 8,5% жиру за ДСТУ 4274:2003(ж/б 0,370 гр)</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>832</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>2016-03-09T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:15.678153+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>1f6989cd7ba1492eb02da50a67d948f2</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>закупівля молока згущеного</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>100</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>2016-02-29T06:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>кіровоградська</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>м. новоукраїнка</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:23.623749+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>663c1973efe3446f8cce2373a0969f3f</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>ea9abed9a0c944b1ba6dad5bda72defe</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Молоко питне ультрапастерізоване, 2,6 % в упаковке по 0,5 л</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>928</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:23.712878+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>c04b57224333409fa3c56accd2680e90</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>bc8e390cdb084da28b7e563b75fa9c43</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, жирність не менше 2,5%, фасоване.</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:24.682458+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>774c15e8e84f4556ab0fa19c8603a7f0</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>aa5641e7b5b0498f8af9be7c32a5bdf2</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>нагальна потреба у закупівлі молока для харчування хворих, вимоги (Додаток 1)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>15120</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:25.617139+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>21a8a0a69dd8475797b461c1673f8df1</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>66245855f68e426582e9d1ee603f6b2a</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Сосиски з молоком 1гат.(вага сосиски приблизно 48-49гр)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>15131120-2</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>160</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:33.675083+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>acb4fafb2564409a8136abf4fa7ba074</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>8fc241549de74abfbc6e280dac66f665</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F641" t="n">
+        <v>335</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:34.530154+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>784775652bb74476bd54c8c9fd120e65</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>1acf2535839041ca841d8ecba83b4dc6</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Молоко згущене (300 бан. по 0,370 кг)</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>03000000-1</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>111</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>2016-02-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>2016-03-25T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:35.586977+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>fe6f4ada22fc4398bc1140a9868d0ff0</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>5c323bae21524cd88f1a69d1e095bc04</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Молоко постирезоване,жирністью не меньше 2,6% фасаване у політеленовий пакет по 1 л ТУ У 15.5-23063575-004-2003</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F643" t="n">
+        <v>278</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:39.417751+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>9c801c8b088142c3b7356bb814b8f3fd</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>9a38de34b6dc44edbc650edf69c5a8c1</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Дитяча молочна суміш з варкою</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>90</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Днепродзержинськ</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:42.119584+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>343c35b24c074c5e9d495528c461deb4</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>727e7fc08e8b4110921d52cb9d0bd87c</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Молоко сгущене з цукром, жирність 8,5%, фасоване у ж/б,1/370 г.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F645" t="n">
+        <v>500</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>2016-03-10T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>ніжин</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:42.320041+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>f4452c19042241b7a034f13dc0a5b735</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>3be6be5ab12c42329e864c64e8e088ba</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Молоко та вершки рідинні оброблені</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F646" t="n">
+        <v>864</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:43.091493+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>a260391dd088410a8e1802a8778dfd05</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>629987fe4db349a9ac603bc028553c94</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Молоко незбиране сухе 25 % жирності</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F647" t="n">
+        <v>600</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Чернігів</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:43.135557+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>8c6e4f1cbe4241e6bdfe9f608f806ff9</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>57a3a215780b493fb87bca0ff1f72383</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Перелік згідно додатку: Молоко та вершки, згущені, підсолоджені- 5000 банок Масло вершкове з умістом жиру не більше ніж 85 мас.%- 1000 кг
+Місце поставки – харчоблок КМКЛ №17 (провулок Лабораторний,- 14-20.
+Поставка протягом року, періодичність поставки -  1 раз на 2 тижня (за потребою)
+Скорочена закупівля у зв"язку з потребою.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F648" t="n">
+        <v>2</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>2016-02-21T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:54.550373+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>36cf89406d9b49c78ae568eb4dde8e3a</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>f5197afc86a048378fa04f6e2d072f6c</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>молоко пастерізоване 2,5 %, (пакети по 1л) 1290 літрів на рік з доставкою два рази на тиждень по 20літрів.договір на 1 рік.  тел 0673817577</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F649" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr"/>
+      <c r="J649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:55.915657+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>a2024e121d294d9c92a637d044225e90</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>a115c2240b5e496062d9d80a7530127a</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>107</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>2016-03-30T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>м Вінниця</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:57.115255+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>71cbb343487c42d78587ee2af092473c</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>dd8c76aefab44f2f8bce6a8e5defeebe</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Кури,мясо,вершкове масло,кефір,молоко пастерізовае,сметана, сир кисломолочний,сирок солодкий з ваніліном,сир твердий"Російський 50%",чай.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F651" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>2016-02-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Україна, м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:57.413488+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>e1753d06b85e4584acc8c6ada08df23c</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>a25f98de0c2444d0a9fb3d78e0b9d60b</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Сметана жирністю 15%</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Полтавская область</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Лохвицький район, село Токарі</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:04.643397+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>d3c6caedf0b7470b9c3c8e18e3be7f45</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>b79f93f96181dc19a10ce9849c24b116</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>936</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>2016-12-28T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Київська область</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:05.401862+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>a3d3a41b37b64e97a154a2e1111b0a5c</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>7f1d89a3aba640e581a98170d42e0921</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко  питне пастеризоване 2,6% фасоване 0,9 </t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>2664</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>м. Прилуки</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:08.352056+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>a3d3a41b37b64e97a154a2e1111b0a5c</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>1e0c09015b7d4c34b2655e69ca8a452f</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Молоко згущене  фасоване ж/б 0,38</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>158</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>м. Прилуки</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:08.352056+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>a3d3a41b37b64e97a154a2e1111b0a5c</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>bbe12b0823f84752a6d6ac3abd0eb9d9</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Молоко  сухе  незбиране  5% вологості</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>300</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>2016-02-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>м. Прилуки</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:08.352056+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>a5892dc1f53741358229e6548dce8b15</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>63c555e8642543a4b9f20cc45c0808c9</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>молоко згущене</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>18</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>2016-02-17T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>2016-02-29T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Орджонікідзе</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:12.244617+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>51eb7ca7ebda495aba798f3e7ac3cbbe</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>33c7c28214cd462e82a1090e3ba455ff</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>молоко пастеризоване, жирністю не менше 2,6%, фасоване у поліетиленовий пакет по 1л, ТУ У 15.5-23063575-004-2003</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>330</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:16.303702+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>93761d1f6b1844e6b2719fde19fda141</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>79e6d93913e14b868e57794b556c1a55</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Молоко згущене 8,5%</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F659" t="n">
+        <v>90</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:17.491543+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>367c0018fadf4340aafd0ac8b3b946a2</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>84ff7b542a0c4fb7a15a5360484ad5bf</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Сметана 15% жир. фасована  по 0,45 кг у поліетиленові пакети- 153,00 кг
+Скорочена закупівля в зв"язку з нагальною потребою для безперебійного лікувального процесу в лікарні</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>15512000-0</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>153</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:19.625911+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>8db18a6680e2455a98e40234c07be0f3</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>c1bd0c8e590549358ea035342f7add81</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>«молоко коров’яче питне,  збагачене білком і кальцієм», 3м.1,2; 2,5% жиру, пастеризоване - 5400 л. Заявка замовника -  від 20л.-80 л. щоденно, а також у вихідні дні (субота) з 6.30  - 7.30 години ранку. Заявка подається сьогодні на завтра, крім святкових днів. Пропозицію надавати відповідно до документації.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>2016-08-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:21.529738+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>6c80d6f80b064b45bdbf1e813206bd5d</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>a80fbef334ef4259ad6ba1de04037f07</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Рулет молочний з згущеним молоком із пшеничного борошна вищого сорту, 1/0,80 кг.</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>15811000-6</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>7385</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:23.260997+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>7672c53550ef4d7fa9c087377e6ae957</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>5027b80ac58546c48c0c74c9667c47c4</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 3,2% жиру вітамінізоване згідно
+ТУ У 15.8-21604587-002:2002</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>6218</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>2016-02-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>2016-03-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:28.171580+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>4cbceb75c06644d0b9606bc900a22f47</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>21292383b00441bea4aa793ece0f5b22</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>285</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:32.869274+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>77443b6beac24dbb99eb113171cd6ccd</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>9b871a72f4b74efc860e5ace751b6ade</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Борошно,цукор,рис,горох,гречка,макарони,дріжді,кофейний напій,какао,молоко згущене,сарделі з вершками, тушонка,мясо,риба,печінка,олія, маргарин,картопля,цибуля,морква,капуста свіжа,буряк,томатна,вироби сухарні,повидло яблочне,коцерви овочеві,,ікра кабачкова,капуста квашена,яйця курячі,печиво,зефір,вафлі,яблука свіжі,сухофрукти,сіль,сік фруктовий та овочевий, шоколад та вироби кондитерські цукрові.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>2467</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>2016-02-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Україна, м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:34.221996+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>9c792ae2b11d470390bc8785396496d7</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>b79ea71bcf8b4cdba5fbf66c7fd76849</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Піпетка Пастера, 3мл</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>33100000-1</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>2016-02-25T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>2016-02-26T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Харьковская область</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>м.Харків</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:34.932315+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>28f3df805cd44bb1bac72a5c5542c880</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>d393db8d76634d769f7d90a0ee60e1ad</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Молоко коров"яче пастеризоване 2,5% жир. фасоване у поліетиленові пакети по 1 кг - 900,00 кг
+Скорочена закупівля в зв"язку з нагальною потребою для безперебійного лікувального процесу в лікарні</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>900</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:36.480194+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>b5959bd28c0e412682fa3cd3f45f71f8</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>a6f37b6d33bc4eedab5080f8e7723b50</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>молоко з умістом жиру 3,2%)(фасоване</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F668" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="inlineStr"/>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:40.270596+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>b5959bd28c0e412682fa3cd3f45f71f8</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>85f86fcb45df4ffa8beb41ce446268ac</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>молоко з умістом жиру від 2,5%)(фасоване)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>13434</v>
+      </c>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="inlineStr"/>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:40.270596+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>0b60bb54dff546cf89bb05291a7a41e0</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>96d4f9b0cc8b4429a9cfd3e09a492e57</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>(10.51.1) Молоко та вершки, рідинні, оброблені (Молоко питне пастеризоване, 2,5% жирності, в поліетиленовому пакеті по 1л.)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>8900</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:41.281899+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>3a1b84b2cf7e4219b6094a678f81790a</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>89e922e724e544f78a29db77fe8a0447</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Сметана жирністю не менше ніж 20%. Фасована в поліетиленові пакети. Продавець повинен передати (поставити) Покупцеві товар, якість яких відповідає діючим ДСТУ (ТУ), санітарним нормам та підтверджується документом, який підтверджує якість продукту харчування (копія висновку державної санітарно-епідеміологічної експертизи або якісне посвідчення тощо). Доставка продуктів здійснюється спеціалізованим транспортом Постачальника на адресу Замовника, за рахунок Постачальника - один раз на тиждень. Оплата окремо за кожну партію товару після доставки, згідно накладної.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>15512100-1</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>70</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2016-03-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Тернопіль</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:48.176385+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>026066514401b6d8796349e5216b6999</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Каша швидкого приготування «Малишка» молочна суміш рису, вівса, гречки, кукурудзи.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>165</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>2016-03-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>49e1a58b49c0f4aa45da95d758029801</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Суміш суха на молочно – зерновій основі «Малиш» з гречаним борошном.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>145</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>2016-03-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>3439a3400ad3b7bc69e06c24bfccaa71</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Суміш суха на молочно – зерновій основі «Малиш» з вівсяним борошном.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>192</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>2016-03-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>04518112fc439953f559e5b701b59b2a</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Суміш суха молочна «Малютка 1» швидкого приготування.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>36</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>2016-03-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>4a80ff4a48e8d2972e87f6ecbf34bafb</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Суміш суха молочна «Малютка 2» швидкого приготування.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
+        <v>7</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>2016-03-04T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>c64e353b3ec34699b378f6c01babb1e9</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>9fb009cb03f746f0b464fe41cad52d2d</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Піпетка Пастера поліетиленова (стерильна) на 3 мл 
+Діаметр 7,8х150мм
+Піпетка має стандартну каплю. Призначено для капельного дозування і для забору різних речовин, насад очного шару в рідинах. 
+Для взяття крові з пальця у донора піпетка повинна бути одноразовою, стерильною, в індивідуальній упаковці.
+Термін придатності товару на момент поставки повинен становити не менше 75% від встановлених інструкцією термінів зберігання.
+Термін поставки протягом 3 днів з моменті підписання договору</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>38437000-7</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F677" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:15.689505+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>394b0db140c34f51a4ba6bf67365222b</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>edad604110984754856460397cd034a8</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Молоко 2,6 % жирності, Творог 5% жирності, Сметана 20 % жирності, 
+Йогурт 1,5% жирності, сирок дитячий ванільний, сир твердий 50% жирності, масло солодковершкове 73% жирності.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>817</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2016-03-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>2016-12-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:17.852980+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39915,7 +43215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K555"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69334,6 +72634,2391 @@
       <c r="K555" t="inlineStr">
         <is>
           <t>2026-02-01T05:09:10.218334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>e18112da9cf74f708a0adc1810cfebe2</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>UA-2016-02-13-000003-b</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:32.785660+02:00</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>КУ "Одесский областной противотуберкулезный диспансер"</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>01998495</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>127500</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J556" t="n">
+        <v>1</v>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>35f6630b0cee4d259fd093f08e86fa5f</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000010-b</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:37.556017+02:00</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>ДП Вороновицьке ПТУ №14</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>02539967</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>710</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J557" t="n">
+        <v>1</v>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>d00183dfd6594972812a85d36f9d5922</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000036-a</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:40.791413+02:00</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Середня загальноосвітня школа №18 м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>23370739</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>28350</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J558" t="n">
+        <v>1</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>625b82d32ba4435bbc58af35cc75ce45</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000050-c</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:50.265927+02:00</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Пуща-Водицький психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>03188795</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>77000</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J559" t="n">
+        <v>1</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>1a971722ca114ab9b8fe32ab4635dad9</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000071-c</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:53.668642+02:00</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровське вище професійне училище будівництва"</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>02541361</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>89757.17999999999</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J560" t="n">
+        <v>1</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>861ee4b23884411096d5f9e1ac1217e3</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000096-b</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:39:59.006300+02:00</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Державний заклад "Спеціалізована медико-санітарна частина №8 Міністерства охорони здоров'я України"</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>14280954</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>27700</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J561" t="n">
+        <v>1</v>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>be22a9e4e16245438d8b40fcee4333ea</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000117-b</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:01.905142+02:00</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Дошкільний заклад освіти №628 Державного управління справами</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>22864155</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J562" t="n">
+        <v>1</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>19d65e25b58643e1b8faec8865b818e8</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000128-c</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:03.435641+02:00</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2-а міська клінічна лікарня м. Полтави</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>01999721</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>37900</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J563" t="n">
+        <v>1</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>ea5c7e8dff134d8c8e44ba42c8694293</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>UA-2016-02-15-000205-b</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:15.678153+02:00</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Водоканал"</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>03327121</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>28500</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J564" t="n">
+        <v>1</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>1f6989cd7ba1492eb02da50a67d948f2</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000038-b</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:23.623749+02:00</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Відділ освіти Новоукраїнської РДА</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>02144111</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J565" t="n">
+        <v>1</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>663c1973efe3446f8cce2373a0969f3f</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000039-a</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:23.712878+02:00</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Київський центр спортивної медицини</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>26169972</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>12760</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J566" t="n">
+        <v>1</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>c04b57224333409fa3c56accd2680e90</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000044-b</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:24.682458+02:00</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Київський психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>26021206</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>48000</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J567" t="n">
+        <v>1</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>774c15e8e84f4556ab0fa19c8603a7f0</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000051-c</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:25.617139+02:00</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня № 9</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>25680295</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>167000</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J568" t="n">
+        <v>1</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>21a8a0a69dd8475797b461c1673f8df1</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000100-b</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:33.675083+02:00</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня швидкої медичної допомоги"ДОР</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>01985854</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>20250</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J569" t="n">
+        <v>1</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>acb4fafb2564409a8136abf4fa7ba074</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000105-b</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:34.530154+02:00</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпродзержинська міська лікарня швидкої медичної допомоги"ДОР</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>01985854</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>9254</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J570" t="n">
+        <v>1</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>784775652bb74476bd54c8c9fd120e65</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000114-c</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:35.586977+02:00</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровська міська клінічна лікарня №16 ДОР"</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>01984624</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>26864.2</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J571" t="n">
+        <v>0</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>fe6f4ada22fc4398bc1140a9868d0ff0</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000129-c</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:39.417751+02:00</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>КЗ "Середня загальноосвітня школа №42 м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>23362071</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>17340</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J572" t="n">
+        <v>1</v>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>9c801c8b088142c3b7356bb814b8f3fd</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000151-c</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:42.119584+02:00</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>4040</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J573" t="n">
+        <v>1</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>343c35b24c074c5e9d495528c461deb4</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000154-c</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:42.320041+02:00</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Ніжинський центр соціально-психологічної реабілітації дітей</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>26543591</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J574" t="n">
+        <v>1</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>f4452c19042241b7a034f13dc0a5b735</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000164-c</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:43.091493+02:00</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>КЗ Дніпродзержинський спеціалізований будинок дитини Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>01985624</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>17766</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J575" t="n">
+        <v>1</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>a260391dd088410a8e1802a8778dfd05</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000165-c</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:43.135557+02:00</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>КУ "Чернігівська обласна лікарня"</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>02006113</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>38400</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J576" t="n">
+        <v>1</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>8c6e4f1cbe4241e6bdfe9f608f806ff9</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000243-c</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:54.550373+02:00</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Перинатальний центр м.Києва</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>22964365</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>110000</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J577" t="n">
+        <v>1</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>36cf89406d9b49c78ae568eb4dde8e3a</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000271-c</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:55.915657+02:00</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Керуюча компанія з обслуговування житлового фонду Шевченківського району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>34966254</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>21120</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J578" t="n">
+        <v>1</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>a2024e121d294d9c92a637d044225e90</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000293-c</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:57.115255+02:00</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Вінницька обласна дитяча клінічна лікарня</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>03082760</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>8853.1</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J579" t="n">
+        <v>1</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>71cbb343487c42d78587ee2af092473c</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>UA-2016-02-16-000301-c</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:40:57.413488+02:00</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровське вище професійне училище будівництва"</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>02541361</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>26343</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J580" t="n">
+        <v>1</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>e1753d06b85e4584acc8c6ada08df23c</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000009-c</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:04.643397+02:00</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Токарівський психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>03189245</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J581" t="n">
+        <v>1</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>d3c6caedf0b7470b9c3c8e18e3be7f45</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000015-c</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:05.401862+02:00</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Державна організація Комбінат "Прогрес" Державного агентства резерву України</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>14373207</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>14040</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J582" t="n">
+        <v>1</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>a3d3a41b37b64e97a154a2e1111b0a5c</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000024-c</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:08.352056+02:00</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>КП "Прилуцький  протитуберкульозний  диспансер"</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>02774131</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>330000</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J583" t="n">
+        <v>1</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>a5892dc1f53741358229e6548dce8b15</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000054-c</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:12.244617+02:00</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>ДПТНЗ "Орджонікідзевське ПТУ"</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>02541792</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J584" t="n">
+        <v>1</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>51eb7ca7ebda495aba798f3e7ac3cbbe</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000072-a</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:16.303702+02:00</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>КЗ НАВЧАЛЬНО-ВИХОВНИЙ КОМПЛЕКС "ЗАГАЛЬНООСВІТНІЙ НАВЧАЛЬНИЙ ЗАКЛАД - ДОШКІЛЬНИЙ НАВЧАЛЬНИЙ ЗАКЛАД" №24 М.ДНІПРОДЗЕРЖИНСЬКА</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>23370840</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>29593</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J585" t="n">
+        <v>1</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>93761d1f6b1844e6b2719fde19fda141</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000079-a</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:17.491543+02:00</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Навчально-виховний комплекс "загальноосвітній навчальний заклад дошкільний навчальний заклад" № 7</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>23372371</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>18582</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J586" t="n">
+        <v>1</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>367c0018fadf4340aafd0ac8b3b946a2</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000093-b</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:19.625911+02:00</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №18</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>01993776</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>6085</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J587" t="n">
+        <v>1</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>8db18a6680e2455a98e40234c07be0f3</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000109-b</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:21.529738+02:00</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Дитяча клінічна лікарня № 5 Святошинського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>00185011</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>54000</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J588" t="n">
+        <v>1</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>6c80d6f80b064b45bdbf1e813206bd5d</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000111-a</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:23.260997+02:00</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Дніпродзержинська міська лікарня №5 Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>01985831</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>91024.03999999999</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J589" t="n">
+        <v>1</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>7672c53550ef4d7fa9c087377e6ae957</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000143-b</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:28.171580+02:00</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Святошинський психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>03188777</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>79590.39999999999</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J590" t="n">
+        <v>1</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>4cbceb75c06644d0b9606bc900a22f47</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000161-c</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:32.869274+02:00</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Навчально-виховний комплекс "загальноосвітній навчальний заклад дошкільний навчальний заклад" № 7</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>23372371</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>20794</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J591" t="n">
+        <v>1</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>77443b6beac24dbb99eb113171cd6ccd</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000186-c</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:34.221996+02:00</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровське вище професійне училище будівництва"</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>02541361</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>34098</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J592" t="n">
+        <v>1</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>9c792ae2b11d470390bc8785396496d7</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000203-c</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:34.932315+02:00</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>КЗОЗ "ОБЛАСНИЙ КЛІНІЧНИЙ ПРОТИТУБЕРКУЛЬОЗНИЙ ДИСПАНСЕР №7"</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>30655442</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>7520</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J593" t="n">
+        <v>1</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>28f3df805cd44bb1bac72a5c5542c880</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000226-c</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:36.480194+02:00</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №18</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>01993776</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>11785</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J594" t="n">
+        <v>1</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>b5959bd28c0e412682fa3cd3f45f71f8</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000281-c</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:40.270596+02:00</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Управління освіти Луцької міської ради</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>02141673</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>199896</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J595" t="n">
+        <v>1</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>0b60bb54dff546cf89bb05291a7a41e0</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>UA-2016-02-17-000296-c</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:41.281899+02:00</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Консультативно-діагностичний центр" Оболонського району м.Києва</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>05494828</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>117300</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J596" t="n">
+        <v>1</v>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>3a1b84b2cf7e4219b6094a678f81790a</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>UA-2016-02-18-000018-c</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:48.176385+02:00</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Тернопільський міський територіальний центр соціального обслуговування населення (надання соціальних послуг)</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>39483390</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>1092</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J597" t="n">
+        <v>1</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>7544d9d739174abd81e03be9a1b22bbd</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>UA-2016-02-18-000047-b</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:41:52.279514+02:00</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Дніпропетровський центр первинної медико-санітарної допомоги № 9"</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>37899715</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>22591.3</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J598" t="n">
+        <v>1</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>c64e353b3ec34699b378f6c01babb1e9</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>UA-2016-02-18-000136-a</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:15.689505+02:00</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Київський міський центр крові</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>01994066</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>29700</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J599" t="n">
+        <v>1</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>394b0db140c34f51a4ba6bf67365222b</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>UA-2016-02-18-000151-b</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:17.852980+02:00</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Територіальний центр соціального обслуговування населення Солом`янського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>22893688</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>32660</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J600" t="n">
+        <v>1</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:06:55.569629+00:00</t>
         </is>
       </c>
     </row>
@@ -69348,7 +75033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73301,6 +78986,164 @@
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-01T05:09:53+00:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>{"bytes": 186301}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02T05:07:33+00:00</t>
+          <t>2026-02-02T05:09:01+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478284961.29498.1.79a84806281323773c9f5b3177e3b14b",
-  "updated_at": "2026-02-02T05:07:32.851001+00:00",
-  "pages_done": 550,
-  "tenders_scanned": 55000,
-  "tenders_fetched": 55000,
-  "milk_tenders": 599,
-  "milk_items": 677
+  "offset": "1478285151.6425.1.abe45aa973287410a8ae353b55af3eda",
+  "updated_at": "2026-02-02T05:09:01.502438+00:00",
+  "pages_done": 575,
+  "tenders_scanned": 57500,
+  "tenders_fetched": 57500,
+  "milk_tenders": 643,
+  "milk_items": 731
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M678"/>
+  <dimension ref="A1:M732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43204,6 +43204,3624 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ee15f9c1eee6471bb9aae5294c8d8c54</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>1ac7b68406d042708a6e7a72b5018930</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>- Вершкове масло, жирністю  не менше 72%  -300 кг.
+-  Молоко пастеризоване в пакетах жирністю не менше 2,5%  - 2100 кг.
+ З детальним описом можна ознайомитись в оголошенні, що додається.
+СКОРОЧЕНА ПРОЦЕДУРА ЗАКУПІВЛЯ В ЗВЯЗКУ З НАГАЛЬНОЮ ПОТРЕБОЮ В ТОВАРІ ДЛЯ ХВОРИХ</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2016-02-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:42.171394+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>09e7d3c70f444b69b805cbd95172def0</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2.6% фасоване у пакети 1 л</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2016-02-29T08:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>2016-08-31T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Миколаївська обл.</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>м. Миколаїв</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:42.316922+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>41844f7e4aeb4e938c711efb03af8c3c</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>9974169769e74eaa0db6e8f5e602553a</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5% жирності у п/етиленових пакетах 1л</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>уп</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>2016-04-30T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:43.600554+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>9a4948efee0046ca827200e09cd7140a</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>3a6d80fee1e52a2cfda3890ab06d443d</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, жирністю 2,5%</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>388</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:50.717854+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>9a4948efee0046ca827200e09cd7140a</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>6fad433fcd66bf0056b324462e1c4a42</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>молоко згущене жирністю 8,5%</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>74</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:50.717854+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>59f5975b73e3401aac6d0961bf9dd8c5</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>75110803ea474353b7bff980580e52cc</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Молоко 3,2%  фасоване пастеризоване тривалого зберігання</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>600</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2016-02-22T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2016-02-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Вінницька</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Могилів-Подільський</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:56.971571+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>88d53cac27094684babda7848d907b11</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>594f9b8e183b41458bddf39446925721</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>900</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2016-03-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>2016-06-17T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>м.Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:00.401306+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>d153553f4b5748e0ad65c770e3e16bc8</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>72bdcdd413d84b6cb48438bb47e9f0b0</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Ковбаса фірмова з молоком 44,550кг, ковбаса напівкапчена 21кг, сосиски молочні 15кг</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>15131130-5</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>81</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:01.342132+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>a5b2a2da795b4d0ca3b203cdde6fe8cb</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>3e150f59db3f4b0f8e125f5537f18a86</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Молоко сухе</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>300</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>с.Часнівці</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:06.136045+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>3f4a42bc64ac4326b09d9e7bea63269e</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>8dc391c994964e8280b6574be027ade0</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>100</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Полтавская область</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>м.Полтава</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:20.728416+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>c3f4bf4b28654528bc7f3eae6e5bfdfa</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>72d093aa2cff446d968f1f5eb5b68447</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% - 2,6% жирності (фасоване, в пакетах по 1 л)</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Полтавская область</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>м.Полтава</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:20.898392+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>bbeb776eb3e34992b114be456de975e7</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>21226127a2be42e4bca679c3053fef64</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>200</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr"/>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>м. Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:22.046166+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>56a342f1545a481cab3da07e6193720e</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>b0c1f182f4744fb6a86f3131fb2f07d1</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Код ДК 016-2010 – 10.86.1 Продукти харчові готові гомогенізовані для дитячого та дієтичного харчування. (Код ДК 016-2015 – 15884000-8 Продукти дитячого харчування).
+№ п/п	Найменування предмету закупівлі	Вимоги виробу	Одиниці
+виміру	Кількість
+1	Суха адаптована молочна суміш «Малиш»	Суміш молочна суха „Малютка швидкого приготування” (початкова) наближена до грудного молока за властивостями та калорійністю. Збагачена таурином та біотином.Призначена для харчування дітей з перших днів життя.Склад: високоякісне коров’яче молоко нормалізоване по жиру та молочному цукру (60,17%), молочний цукор (16,5%), низькооцукрена патока (мальтодекстрин) (15,5%), рослинна олія: кукурудзяна (7,6%). Збагачено вітамінами (0,14%): холіном, біотином, А, Д, Е, С, РР, В1, В2, В5, В6, Вс, В12, таурином (0,04%) та мінеральними речовинами (0,05%): лимоннокислим калієм, лимоннокислим натрієм, сірчанокислим залізом, сірчанокислим  цинком, йодистим калієм, селенітом натрію.Без консервантів. Без барвників. Без ароматизаторів. Не містить ГМО/Строк придатності та умови зберігання – не більше 12 місяців з дня  виготовлення при температурі від 0 до 25˚С та відносній вологості повітря не вище 75%. Після розпакування пачки  суху суміш зберігати не більше двох тижнів, щільно закритою у сухому прохолодному місці.
+Упаковка (пачка) повинна містити мірну ємність для дозування.
+Уп.	
+50
+2	Молоко незбиране вітамінізоване	Молоко вітамінізоване 3,2% жирності
+Склад:
+молоко коров'яче нормалізоване, вітамінний комплекс (0,015%)
+Опис:
+вітаміни: А - 70-138 мкг, Д - 0,2-2,0 мкг, Е - 0,9-3,0мг
+ГОСТ/ТУ:
+ТУ У 15.8-21604587-002:2002
+Маса нетто: 200,00 г
+Термін придатності: 10 доб.
+Умови зберігання:
+При температурі від (4±2) С
+Не містить ГМО
+Енергетичний склад:
+Білки: 2,80 г
+Вуглеводи: 4,70 г
+Жири: 3,20 г
+Фасовка: скляні пляшки
+Уп.	
+170
+3	Каша суха молочна круп’яна «Малиш»	Каша суха молочна круп’яна швидкорозчинна  для дитячого харчування легко засвоюється та добре розчиняється. Містить вітаміни і мінерали. Без додавання цукру та солі. Не містить ГМО, штучних добавок, консервантів, барвників. Виготовлена з високоякісного українського молока.Упаковка повинна містити мірну ємність для дозування.
+Упаковка: 350 г
+Уп.	
+60
+4	Пюре мясне консервоване 
+	Гомогенізоване, дитячого харчування
+Не містить генно-модифікованих інгредієнтів, штучних консервантів, барвників та ароматизаторів 
+З низькоаллергенних м’ясом індички 
+Містить крохмаль і рослинне масло,виготовлено з продуктів з низькими алергенними властивостями 
+У складі —  м'ясо (яловичина, індичка, кріль, кури) 40%, вирощені з біоорганічної технології рис і цибулю, вода 
+Збагачене йодом за рахунок йодованої солі 
+Без кристалічного цукру, ароматизаторів, барвників, консервантів, загусників, молочного білка, глютену.
+ Упаковка: Скляна банка.
+Уп.	
+270
+5	Сік плодово-ягідний консервований	Для дітей з 5-ти місяців.
+Сік Малятко плодово-ягідний містить масу цінних і корисних речовин: вітаміни (каротин, В1, В2, В3, аскорбінову кислоту), мінерали (магній, кальцій, калій, фосфор, залізо, кобальт), органічні кислоти, а також глюкозу, фруктозу, клітковину, амінокислоти. 
+Скляна банка.	
+Уп.	
+150
+6	Пюре консервоване овочеве	Для дітей з  4-х місяців.
+Овочеве пюре смачне і корисне. Пюре  містить величезну кількість вітаміну С, групи В, а також вітаміни А, Е, D, К, Н, U. До складу овочевого пюре входять вуглеводи, клітковина, органічні і поліненасичені кислоти, крохмаль. Овоч містить мінеральні солі калію, кальцію, хлору, фосфору, магнію, сірки, натрію, міді, марганцю, заліза, цинк, молібдену, кобальту. Овочеве пюре не повинно дратувати слизову оболонку травних органів, повинна легко перетравлюватись і не навантажувати організм. Пюре легко засвоюється і переноситься.
+Вимоги до продукту:
+- виготовлений з органічних компонентів
+- не містить генетично модифікованих організмів
+- не містить крохмалю
+- не містить барвників, консервантів, штучних ароматизаторів
+- без глютену
+- без солі
+- нормалізує стілець.
+Скляна банка.	
+Уп.	
+240
+7	Пюре консервоване плодове	Пюре плодове ароматне, смачне і поживне. У його складі присутня велика кількість корисних речовин, необхідних для нормальної роботи організму: пектини, клітковина, моно- і дисахариди, органічні кислоти, вітаміни ряду А, В, Е, РР, В-каротин та мікроелементи - залізо, кальцій, калій,фосфор, магній, йод, цинк, мідь.. Пюре збагачене вітаміном С – важливим для імунної системи. Не містить ароматизаторів, барвників, консервантів, ГМО,глютену. 
+Скляна банка.
+Уп.	
+160
+На кожний товар надати :
+1.	Державний сертифікат якості продукту дитячого харчування.
+2.	Висновок Державної санітарно-гігієнічної експертизи;
+3.	Документи, які вказують на відповідність якості продуктів харчових готових гомогенізованих для дитячого харчування вимогам національних стандартів, що повинно підтверджуватися документами, які інформують про склад продуктів та про методи контролю показників безпеки.
+4.	 Гарантійний лист щодо терміну придатності товару.
+5.	Товар, представлений постачальником, має відповідати вітчизняним та міжнародним стандартам якості.
+6.	Товар має супроводжуватися документами, що підтверджують якість, кількість, вагу та ін.
+7.	Доставка товару  транспортом постачальника, завантажувальні та розвантажувальні роботи за рахунок постачальника.
+В технічній частині пропозиції конкурсних торгів обов'язково надається інформація про:
+- форму упаковки, вид розфасовки, термін та умови зберігання,
+- лист підтвердження щодо забезпечення умов належного зберігання до початку поставки та під час розвозки продуктів харчових готових гомогенізованих для дитячого та дієтичного харчування.
+Гарантійний термін придатності сумішей на момент постачання повинен складати не менше 75% зазначеного терміну придатності.
+Наявність інструкції на упаковці державною (українською) мовою.
+На етикетці дитячого харчування, призначеного для дітей грудного віку, зазначається інформація про необхідність попередньої (перед початком споживання) консультації лікаря, вік дитини, для якої рекомендовано суміш, склад суміші, характеристика продукту, рекомендації щодо її приготування та використання.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні бути придатними для вигодовування дітей від народження але не менше ніж до 6 місяців.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні бути розфасовані в герметично закритих упаковках виробника, без механічних пошкоджень тари та вагою нетто.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні містити демінералізовану або частково демінералізовану молочну сироватку.
+Збагачення продуктів харчових готових гомогенізованих для дитячого харчування такими біологічно активними компонентами як таурин, карнітин, селен.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні відповідати основним вимогам щодо повного забезпечення всіх фізіологічних потреб дитини у поживних речовинах і енергії.
+Продукти харчові готові гомогенізовані для дитячого харчування не повинні містити генетично модифікованих компонентів.</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>15884000-8</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>2016-12-19T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:22.393529+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>3c20eb0c354e4398b164e519500fa24f</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>06088865387246a98d27101adb80a366</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Молоко 2,5%, п/ет. плівка</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>16</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2016-02-26T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2016-11-04T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Черкасская область</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>м. Сміла</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:49.457308+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>58391d0ed8fa49478419c45d9b14bed0</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>83b43be9c035484cb413a7a43c6bb1f4</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване в пакетах</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2016-03-07T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Чернігівська</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>Понорниця</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:50.445467+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>9fe1452eb6f943eb88e84a832a92321b</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>a7874c34e4984b729ab1ab336192c10e</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Суміш молочна суха швидкого приготування "Малиш" з 3 місяців в асортименті по 350 г.</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>360</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>2016-03-11T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:57.268760+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>759cd67f340f471eb3fa06faa0497830</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>351ab3c6460e4a7d82847ada2f701605</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Молоко сгущене</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>220</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>2016-08-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>м. Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:57.712469+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>759cd67f340f471eb3fa06faa0497830</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>19790b1bd78940b5aed9d1cfa1cc56d2</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>2016-08-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>м. Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:57.712469+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>53e5d9492e8544a684f13b728920c177</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>64ff9d71a58140c9a3fdc9216ccb2182</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване  ДСТУ 2661:2010  фасовані   місткістю 1,0  л), упаковані в плівку , жирністю 2,5 %,  без домішок цукру та солі, без ГМО.; Відповідність вимогам діючого санітарного заканодавства України,нормам     хачування. Обов'язкова наявність посвідчення про  якість</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>100</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>2016-02-22T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>2016-02-23T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>Україна, Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:58.149689+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>7fda9f87ba0b46cea5a56fccceb5c2dd</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>8afd19fce5b0411a8bd997f828b7842b</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Код ДК 016-2010:  10.51.1. «Молоко та вершки, рідинні, оброблені» ,  10.51.3. «Масло вершкове та молочні пасти» , 10.51.4. «Сир сичужний та кисломолочний сир» , 10.51.5. «Продукти молочні, інші»  (більш детально в додатку до оголошення).</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>10</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>2016-03-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Іллічівськ</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:07.946536+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>52fb3bdf37a04800b231c632211e9345</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>458029d7efbd4d419a52dee98a5e3f8f</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>згущене молоко</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>15972</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>2016-09-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Львовская область</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>с. Угерсько, Стирийського р-н.</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:10.389049+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>8d48d9cf4de24ebc9377f5dd7bc4378d</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>9108630ed2a14df1b41a15a0fd0bc616</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>33) Сметана в асорт. - 150 кг		
+34) Молоко згущене незбиране в асорт. - 100 кг		
+35) Кефір в асорт. - 450 кг		
+36) Йогурт в асорт. - 30 кг	
+37) Ряжанка в асорт. - 500 кг	
+38) Біо-кефір - 50 кг	
+39) Біо-йогурт - 130 кг</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>15980000-1</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>2016-03-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Южне</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:10.775339+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>ccc9dfe955864cdaa510f2fed029c05f</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №3 "Струмочок" </t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>200</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>13279bd975b84cb3b84086c8cdde67cf</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №1 "Малятко" </t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>м.Апостолове</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>3283281bd3594e51894586365e29ef7b</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Українка" </t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>180</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>с. Українка. Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>ef321c92aa4c4dedae8260f169cbf5b7</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Кульбабка" </t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>60</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>с. Запорізьке, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>93eaf4b26bf147e1a139f437765fcc58</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Казка" </t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>40</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>с. Перше Травня, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>6329901c78054781a29cc23c48fc04ec</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ "Ромашка" </t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>600</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>с. Кам'янка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>e972c4f081c948f0b0da9ec48f402948</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко свіже для КДНЗ №2 "Барвінок"  </t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>360</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>м. Апостолове</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2e55ebe7e5bd464a9d0ef907f5fc4571</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Молоко свіже для КДНЗ "Ромашка"</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>450</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>с. Михайлівка, Апостолівський р-н</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>b4530cf9d4a9466bb690402e42d74a60</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>5bd0dc8b5c2e4d19894c589d57d42d29</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>молоко коров’яче ультрапастеризоване питне з масовою часткою жиру 2, 5%, довготривалого зберігання, детальний опис технічних (якісних) вимог викладено в окремо доданому документі</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>15511210-8</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F709" t="n">
+        <v>11880</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>2016-03-06T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>2016-05-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:34.080401+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2cfbfe858d26491181b94442a000ed94</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>392e0601882744e58cc5837333c24eef</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>1.Молоко коров`яче питне пастеризоване збагачене білком і кальцієм
+ 2,5 %-3000 л х 13,61=40830,00
+2.Кефір вітамінізований 2,5 % - 2600 кг х 17,25= 44850,00
+3.Сметана 21 % -202,5 кг х 39,77 = 8053,43
+4. Сир к/м 9 % - 600 кг х 64,99 = 38994,00
+5 Масло верш. вагове 73% -1000 кг х 107,25 = 107250,00
+6 Сир тверд. "Російський" 50%- 200 кг х 123,24 = 24648,00</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>7603</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:39.003997+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>658fefd89c1e4bcb903535c6c63b5ab1</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>f3ecd9aefd6b4ecfb05208a6237291c8</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко фас 2,5% жирності у п/етиленових пакетах по 1л. </t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F711" t="n">
+        <v>840</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Киевская область</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>м.Київ</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:44.267731+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>264417728a3442c4b45f57c37ef34aaf</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>91382883da954daeb51e5624153f2d46</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>сухе молоко</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F712" t="n">
+        <v>50</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>2016-03-03T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>м.Чернігів</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:48.318581+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>0053c448f0f347f4aa10b9bafa684a0e</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>b302723065d0e4523c0924b0b4f88fba</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Молоко 3,2% (фас.900г)</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F713" t="n">
+        <v>714</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>уп</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Чернігівська область</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>м.Чернігів</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:49.485026+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>1385bef6c3394bf0a2249f64c8a9e04c</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>81bb2216ca65f11472e9b4879e907237</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Молоко ультра пастеризоване 2,5 % жирності</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>13050</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>2016-03-09T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Чернігівська область</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>місто Ніжин</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:49.645833+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>dd06641d08c041c7ae3e4fc78ca8d1ad</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>59d0436a6fc64578a8ae2f538eb3e81e</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>2016-03-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>2016-03-11T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>м.Прилуки</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:50.469678+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>a36d6ccf366c431da1313bc02e8fc665</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>8525a5f73e9a4327b67f54037ec28a7d</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>молоко коров"яче 2,5%</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>140</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>м. Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:55.143488+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>4feb97e62e344e87a5caea5494129c31</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>052dc888925147d1b2345fce1dad4ad3</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Молоко цільне</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F717" t="n">
+        <v>250</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>м.Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:55.803212+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>4feb97e62e344e87a5caea5494129c31</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>02abac1e137f45fbbbf72adf6b2cf7c3</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Сгущене молоко</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>62</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>м.Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:55.803212+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>fab9fc2d3a27472cbf68714c16df7137</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>f0cacbf554f04cf0b089ee92ab8d4961</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% політелен.пакети 1,0л.</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>840</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>2016-03-02T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>2016-09-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Павлоград</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:07.378288+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>15b1f69052324234a9a0bfba4103b431</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>9f998b2bdfc3468c8c9aaed4be25c223</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Молоко  рідинне  2,6% ж. п/ет. пакетоване 0,9 кг</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>982</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>м. Прилуки</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.154681+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>d3c4fcf47c854625b21862b3ffc788ec</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>238f16e48d984958bbd2687f2de6f512</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Сухе незбиране молоко вагове в мішках по 25 кг</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>5</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>м. Прилуки</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.622393+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>b62142f99a8843bba50f495759dd9d2a</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>f333fc718fab481db22f2327ea37c7c9</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване жирність 2,5% поліетилен пакети 0,5 кг</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>800</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>2016-03-07T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>г. Днепропетровск</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.857855+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>b89ac6c626d943c99360c793b4744ac7</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>618c435403587cf5f83c516d68fcddb4</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване 2,5% в пакетах по 1л.</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F723" t="n">
+        <v>845</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>2016-03-21T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Миколаївська область</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>м. Миколаїв</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:12.777004+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>8d91eea253c449a0927c7a7c2db5fbf6</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>413342f101971bbd22a0e44694d5fe13</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Молоко</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2016-05-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Запорізька область</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:15.802231+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>c7d7acd599354164bca0d8f23bdf029b</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>e06ba68fb388488db98fa2f9e3c0a145</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, жирністю 2,6 %, фасоване по 0.5 л  в поліетиленових пакетах термін реалізації 5 діб</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>376</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:15.809489+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>a8de9f0da0704355b7ff5cdcb2ef5fc2</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>0cf2884f13b86f029cda55caeb3dca09</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>молоко коров'че питне пастеризоване 3,2%(2,5%)1000г.</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>2333</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>М.Бар</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:18.518631+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>714effddf0c6477d8cfedc406420615f</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>1f5985fe7eae40ff972023ea12c551c1</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Код за ДК 016-2010: 01.11.9. "Насіння інших олійних культур", 01.25.3. "Горіхи (крім дикорослих їстівних горіхів, арахісу та кокосів)", 01.49.2.  "Продукція  тваринництва,  інша" ("Мед  натуральний"),   10.39.2. «Плоди й горіхи, оброблені та законсервовані», 10.41.5. "Олії рафіновані",  10.42.1. "Маргарин і подібні харчові жири", 10.51.1. "Молоко та вершки, рідинні, оброблені", 10.51.4. «Сир сичужний та кисломолочний сир», 10.72.1. "Вироби хлібобулочні, зниженої вологості, та кондитерські, борошняні, тривалого зберігання», 10.82.1 «Какао терте, какао-масло, жири й олія, какао порошок», 10.84.1. «Оцет; соуси; суміші приправ», 10.84.2. «Прянощі, оброблені» ,  10.84.3. «Сіль харчова», 10.89.1. "Супи, яйця, дріжджі та інші харчові продукти"  (більш детально в додатку до оголошення).</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>15872200-3</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>32</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>2016-03-13T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Одеська</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Іллічівськ</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:30.334065+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>63d7f5321670467aa86144747a44c1e3</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>99b64734feba4cc8845cb9a5b8ee9f86</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>100</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>с.Стецівка</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:33.174466+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>59aabe9d580340eab7587c3af3a3ab2f</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>c0bc60e829e046a1ab84875bf7ac04ec</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F729" t="n">
+        <v>100</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>c.Вершанці</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:37.803795+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>7ec9a45598ad4e27996751093057eef5</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>25d435adfe0347c19da3952db92935cd</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>молоко</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>20</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:41.687156+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>7968a39bdd9048d58e076a3fb3242eed</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>8def573042f94eaf985d6e33684bfc9a</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>10.86.1 Продукти харчові готові гомогенізовані для дитячого та дієтичного харчування. (Код ДК 016-2015 – 15884000-8 Продукти дитячого харчування).
+Вимоги та найменування:
+1.Суха адаптована молочна суміш «Малиш»:Суміш молочна суха „Малютка швидкого приготування” (початкова) наближена до грудного молока за властивостями та калорійністю. Збагачена таурином та біотином.Призначена для харчування дітей з перших днів життя.Склад: високоякісне коров’яче молоко нормалізоване по жиру та молочному цукру (60,17%), молочний цукор (16,5%), низькооцукрена патока (мальтодекстрин) (15,5%), рослинна олія: кукурудзяна (7,6%). Збагачено вітамінами (0,14%): холіном, біотином, А, Д, Е, С, РР, В1, В2, В5, В6, Вс, В12, таурином (0,04%) та мінеральними речовинами (0,05%): лимоннокислим калієм, лимоннокислим натрієм, сірчанокислим залізом, сірчанокислим  цинком, йодистим калієм, селенітом натрію.Без консервантів. Без барвників. Без ароматизаторів. Не містить ГМО/Строк придатності та умови зберігання – не більше 12 місяців з дня  виготовлення при температурі від 0 до 25˚С та відносній вологості повітря не вище 75%. Після розпакування пачки  суху суміш зберігати не більше двох тижнів, щільно закритою у сухому прохолодному місці.
+Упаковка (пачка) повинна містити мірну ємність для дозування, 50 уп.
+2.Молоко незбиране вітамінізоване: Молоко вітамінізоване 3,2% жирності
+Склад:
+молоко коров'яче нормалізоване, вітамінний комплекс (0,015%)
+Опис:
+вітаміни: А - 70-138 мкг, Д - 0,2-2,0 мкг, Е - 0,9-3,0мг
+ГОСТ/ТУ:
+ТУ У 15.8-21604587-002:2002
+Маса нетто: 200,00 г
+Термін придатності: 10 доб.
+Умови зберігання:
+При температурі від (4±2) С
+Не містить ГМО
+Енергетичний склад:
+Білки: 2,80 г
+Вуглеводи: 4,70 г
+Жири: 3,20 г
+Фасовка: скляні пляшки, 170уп.;
+3.Каша суха молочна круп’яна «Малиш»:	Каша суха молочна круп’яна швидкорозчинна  для дитячого харчування легко засвоюється та добре розчиняється. Містить вітаміни і мінерали. Без додавання цукру та солі. Не містить ГМО, штучних добавок, консервантів, барвників. Виготовлена з високоякісного українського молока.Упаковка повинна містити мірну ємність для дозування.
+Упаковка: 350 г., 60 уп.;
+4.Пюре мясне консервоване 
+Гомогенізоване, дитячого харчування
+Не містить генно-модифікованих інгредієнтів, штучних консервантів, барвників та ароматизаторів 
+З низькоаллергенних м’ясом індички 
+Містить крохмаль і рослинне масло,виготовлено з продуктів з низькими алергенними властивостями 
+У складі —  м'ясо (яловичина, індичка, кріль, кури) 40%, вирощені з біоорганічної технології рис і цибулю, вода 
+Збагачене йодом за рахунок йодованої солі 
+Без кристалічного цукру, ароматизаторів, барвників, консервантів, загусників, молочного білка, глютену.
+ Упаковка: Скляна банка, 270 уп;
+5.Сік плодово-ягідний консервований,	Для дітей з 5-ти місяців.
+Сік Малятко плодово-ягідний містить масу цінних і корисних речовин: вітаміни (каротин, В1, В2, В3, аскорбінову кислоту), мінерали (магній, кальцій, калій, фосфор, залізо, кобальт), органічні кислоти, а також глюкозу, фруктозу, клітковину, амінокислоти. 
+Скляна банка., 150 уп.;
+6.Пюре консервоване овочеве, Для дітей з  4-х місяців.
+Овочеве пюре смачне і корисне. Пюре  містить величезну кількість вітаміну С, групи В, а також вітаміни А, Е, D, К, Н, U. До складу овочевого пюре входять вуглеводи, клітковина, органічні і поліненасичені кислоти, крохмаль. Овоч містить мінеральні солі калію, кальцію, хлору, фосфору, магнію, сірки, натрію, міді, марганцю, заліза, цинк, молібдену, кобальту. Овочеве пюре не повинно дратувати слизову оболонку травних органів, повинна легко перетравлюватись і не навантажувати організм. Пюре легко засвоюється і переноситься.
+Вимоги до продукту:
+- виготовлений з органічних компонентів
+- не містить генетично модифікованих організмів
+- не містить крохмалю
+- не містить барвників, консервантів, штучних ароматизаторів
+- без глютену
+- без солі
+- нормалізує стілець.
+Скляна банка.,  240 уп.;
+7.Пюре консервоване плодове:	Пюре плодове ароматне, смачне і поживне. У його складі присутня велика кількість корисних речовин, необхідних для нормальної роботи організму: пектини, клітковина, моно- і дисахариди, органічні кислоти, вітаміни ряду А, В, Е, РР, В-каротин та мікроелементи - залізо, кальцій, калій,фосфор, магній, йод, цинк, мідь.. Пюре збагачене вітаміном С – важливим для імунної системи. Не містить ароматизаторів, барвників, консервантів, ГМО,глютену. 
+Скляна банка, 160 уп.
+Місце поставки:04201 м.Київ. вул..Вишгородська,54-А
+Відповідальна особа: Мешкова Наталія Вікторівна
+За потребою згідно заявки Замовника сьогодні /на завтра, доставка до КНП ЦПМСД №2 Оболонського району м. Києва за вищевказаною адресою.
+На кожне найменування додати:
+1.	Державний сертифікат якості продукту дитячого харчування.
+2.	Висновок Державної санітарно-гігієнічної експертизи;
+3.	Документи, які вказують на відповідність якості продуктів харчових готових гомогенізованих для дитячого харчування вимогам національних стандартів, що повинно підтверджуватися документами, які інформують про склад продуктів та про методи контролю показників безпеки.
+4.	 Гарантійний лист щодо терміну придатності товару.
+5.	Товар, представлений постачальником, має відповідати вітчизняним та міжнародним стандартам якості.
+6.	Товар має супроводжуватися документами, що підтверджують якість, кількість, вагу та ін.
+7.	Доставка товару  транспортом постачальника, завантажувальні та розвантажувальні роботи за рахунок постачальника.
+В технічній частині пропозиції конкурсних торгів обов'язково надається інформація про:
+- форму упаковки, вид розфасовки, термін та умови зберігання,
+- лист підтвердження щодо забезпечення умов належного зберігання до початку поставки та під час розвозки продуктів харчових готових гомогенізованих для дитячого та дієтичного харчування.
+Гарантійний термін придатності сумішей на момент постачання повинен складати не менше 75% зазначеного терміну придатності.
+Наявність інструкції на упаковці державною (українською) мовою.
+На етикетці дитячого харчування, призначеного для дітей грудного віку, зазначається інформація про необхідність попередньої (перед початком споживання) консультації лікаря, вік дитини, для якої рекомендовано суміш, склад суміші, характеристика продукту, рекомендації щодо її приготування та використання.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні бути придатними для вигодовування дітей від народження але не менше ніж до 6 місяців.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні бути розфасовані в герметично закритих упаковках виробника, без механічних пошкоджень тари та вагою нетто.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні містити демінералізовану або частково демінералізовану молочну сироватку.
+Збагачення продуктів харчових готових гомогенізованих для дитячого харчування такими біологічно активними компонентами як таурин, карнітин, селен.
+Продукти харчові готові гомогенізовані для дитячого харчування повинні відповідати основним вимогам щодо повного забезпечення всіх фізіологічних потреб дитини у поживних речовинах і енергії.
+Продукти харчові готові гомогенізовані для дитячого харчування не повинні містити генетично модифікованих компонентів.
+В разі наявності в даному документі посилань на конкретні торговельну марку чи фірму, патент, конструкцію або тип предмета закупівлі, джерело його походження або виробника, після такого посилання слід вважати в наявності вираз «або еквівалент».</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>15884000-8</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F731" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>2016-12-19T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:44.589637+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>a0b006b976b143fc90afa70fab2db160</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>dc681d0caf9849cba9d28502bdb41ae1</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Продукти харчування різного асортименту. Хліб і хлібобулочні продукти, м'ясо та молоко поставляти щоденно.</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F732" t="n">
+        <v>100</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>набір</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Чигирин</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:45.515864+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43215,7 +46833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:K644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75019,6 +78637,2338 @@
       <c r="K600" t="inlineStr">
         <is>
           <t>2026-02-02T05:06:55.569629+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>ee15f9c1eee6471bb9aae5294c8d8c54</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000038-a</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:42.171394+02:00</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Київська міська туберкульозна лікарня №1 з диспансерним відділенням</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>01993960</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>52500</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J601" t="n">
+        <v>1</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>09e7d3c70f444b69b805cbd95172def0</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000038-b</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:42.316922+02:00</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Миколаївська обласна психіатрична лікарня №1</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>01998325</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J602" t="n">
+        <v>1</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>41844f7e4aeb4e938c711efb03af8c3c</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000049-a</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:43.600554+02:00</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>КУ "Одеська обласна дитяча клінічна лікарня"</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>01998532</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J603" t="n">
+        <v>1</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>9a4948efee0046ca827200e09cd7140a</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000087-b</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:50.717854+02:00</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>КЗ " Дніпропетровська МКЛ №11" ДОР"</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>01983944</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J604" t="n">
+        <v>1</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>59f5975b73e3401aac6d0961bf9dd8c5</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000119-b</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:42:56.971571+02:00</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Могилів - Подільський дитячий легеневий тубсаторій</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>05484617</t>
+        </is>
+      </c>
+      <c r="H605" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J605" t="n">
+        <v>1</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>88d53cac27094684babda7848d907b11</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000146-a</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:00.401306+02:00</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровський навчально-реабілітаційний центр № 1 Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>20199883</t>
+        </is>
+      </c>
+      <c r="H606" t="n">
+        <v>151547</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J606" t="n">
+        <v>1</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>d153553f4b5748e0ad65c770e3e16bc8</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000161-a</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:01.342132+02:00</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "СЕРЕДНЯ ЗАГАЛЬНООСВІТНЯ ШКОЛА №28 М.ДНІПРОДЗЕРЖИНСЬКА" ДНІПРОДЗЕРЖИНСЬКОЇ МІСЬКОЇ РАДИ</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>23642592</t>
+        </is>
+      </c>
+      <c r="H607" t="n">
+        <v>5126.58</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J607" t="n">
+        <v>1</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>a5b2a2da795b4d0ca3b203cdde6fe8cb</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000188-c</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:06.136045+02:00</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Козелецький геріатричний пансіонат</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>03189953</t>
+        </is>
+      </c>
+      <c r="H608" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J608" t="n">
+        <v>1</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>3f4a42bc64ac4326b09d9e7bea63269e</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000265-a</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:20.728416+02:00</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Горбанівський геріатричний пансіонат ветеранів війни та праці</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>13962350</t>
+        </is>
+      </c>
+      <c r="H609" t="n">
+        <v>5168</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J609" t="n">
+        <v>1</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>c3f4bf4b28654528bc7f3eae6e5bfdfa</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>UA-2016-02-19-000270-a</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:20.898392+02:00</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Горбанівський геріатричний пансіонат ветеранів війни та праці</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>13962350</t>
+        </is>
+      </c>
+      <c r="H610" t="n">
+        <v>89000</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J610" t="n">
+        <v>1</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>bbeb776eb3e34992b114be456de975e7</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>UA-2016-02-20-000013-b</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:22.046166+02:00</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Середня загальноосвітня школа №34 м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>23643382</t>
+        </is>
+      </c>
+      <c r="H611" t="n">
+        <v>182078.65</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J611" t="n">
+        <v>0</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>56a342f1545a481cab3da07e6193720e</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>UA-2016-02-21-000002-c</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:22.393529+02:00</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Центр первинної медико-санітарної допомоги №2" Оболонського району міста Києва</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>23379143</t>
+        </is>
+      </c>
+      <c r="H612" t="n">
+        <v>21100</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J612" t="n">
+        <v>1</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>3c20eb0c354e4398b164e519500fa24f</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>UA-2016-02-22-000170-b</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:49.457308+02:00</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Державна організація "Комбінат "Дніпро" Державного агентства резерву України</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>14373242</t>
+        </is>
+      </c>
+      <c r="H613" t="n">
+        <v>144</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J613" t="n">
+        <v>1</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>58391d0ed8fa49478419c45d9b14bed0</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>UA-2016-02-22-000175-b</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:50.445467+02:00</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Понорницький психоневрологічний інтернат</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>03189860</t>
+        </is>
+      </c>
+      <c r="H614" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J614" t="n">
+        <v>1</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>9fe1452eb6f943eb88e84a832a92321b</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>UA-2016-02-22-000237-b</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:57.268760+02:00</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>КУ "ДЦПМСП №10"</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>37899708</t>
+        </is>
+      </c>
+      <c r="H615" t="n">
+        <v>13540</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J615" t="n">
+        <v>1</v>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>759cd67f340f471eb3fa06faa0497830</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>UA-2016-02-22-000251-b</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:57.712469+02:00</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Комунальний заклад  «Навчально-виховне об’єднання «Дошкільний навчальний заклад – загальноосвітній навчальний заклад І-ІІ ступенів - ліцей нових інформаційних технологій  м. Дніпродзержинська»  Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>21910479</t>
+        </is>
+      </c>
+      <c r="H616" t="n">
+        <v>93122</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J616" t="n">
+        <v>0</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>53e5d9492e8544a684f13b728920c177</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>UA-2016-02-22-000262-b</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:43:58.149689+02:00</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровське вище професійне училище будівництва"</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>02541361</t>
+        </is>
+      </c>
+      <c r="H617" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J617" t="n">
+        <v>1</v>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>7fda9f87ba0b46cea5a56fccceb5c2dd</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000004-a</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:07.946536+02:00</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Іллічівська філія державного підприємства “Адміністрація морських портів України” (Адміністрація Іллічівського морського порту)</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>38728418</t>
+        </is>
+      </c>
+      <c r="H618" t="n">
+        <v>165000</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J618" t="n">
+        <v>0</v>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>52fb3bdf37a04800b231c632211e9345</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000022-b</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:10.389049+02:00</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>ПАТ "Укргазвидобування" в особі філії Львівгазвидобування"</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>39585756</t>
+        </is>
+      </c>
+      <c r="H619" t="n">
+        <v>270725</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J619" t="n">
+        <v>1</v>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>8d48d9cf4de24ebc9377f5dd7bc4378d</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000023-c</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:10.775339+02:00</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Южненська філія державного підприємства "Адміністрація морських портів України" (адміністрація морського порту "Южний")</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>38728549</t>
+        </is>
+      </c>
+      <c r="H620" t="n">
+        <v>216629.5</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J620" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>bd9de0e898dd469686b71d71d88ef8be</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000083-b</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:27.479695+02:00</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Виконавчий комітет Апостолівської міської ради</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>40209395</t>
+        </is>
+      </c>
+      <c r="H621" t="n">
+        <v>56870</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>b4530cf9d4a9466bb690402e42d74a60</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000116-c</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:34.080401+02:00</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Зеніт" Деснянського району м. Києва</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>19027846</t>
+        </is>
+      </c>
+      <c r="H622" t="n">
+        <v>170000</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J622" t="n">
+        <v>1</v>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2cfbfe858d26491181b94442a000ed94</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000138-a</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:39.003997+02:00</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Дитячий спеціалізований санаторій "Лісова поляна"</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>05415817</t>
+        </is>
+      </c>
+      <c r="H623" t="n">
+        <v>264626</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J623" t="n">
+        <v>1</v>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>658fefd89c1e4bcb903535c6c63b5ab1</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000186-b</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:44.267731+02:00</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Київська міська дитяча клінічна інфекційна лікарня</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>01993664</t>
+        </is>
+      </c>
+      <c r="H624" t="n">
+        <v>17260</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J624" t="n">
+        <v>1</v>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>264417728a3442c4b45f57c37ef34aaf</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000243-b</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:48.318581+02:00</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Пологовий будинок Чернігівської міської ради</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>02006610</t>
+        </is>
+      </c>
+      <c r="H625" t="n">
+        <v>3030</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J625" t="n">
+        <v>0</v>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>0053c448f0f347f4aa10b9bafa684a0e</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000272-b</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:49.485026+02:00</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>ДПТНЗ "Чернігівський центр професійно-технічної освіти"</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>01566790</t>
+        </is>
+      </c>
+      <c r="H626" t="n">
+        <v>55200</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J626" t="n">
+        <v>1</v>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>1385bef6c3394bf0a2249f64c8a9e04c</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000278-b</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:49.645833+02:00</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Ніжинський дитячий будинок-інтернат</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>03189883</t>
+        </is>
+      </c>
+      <c r="H627" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J627" t="n">
+        <v>1</v>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>dd06641d08c041c7ae3e4fc78ca8d1ad</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000302-b</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:50.469678+02:00</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Комунальне підприємство "Прилукитепловодопостачання" Прилуцької міської ради</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>32863684</t>
+        </is>
+      </c>
+      <c r="H628" t="n">
+        <v>10896</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J628" t="n">
+        <v>1</v>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>a36d6ccf366c431da1313bc02e8fc665</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000354-b</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:55.143488+02:00</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Навчально-виховний комплекс "Загальноосвітній навчальний заклад- дошкільний навчальний заклад" №12 м.Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>23642385</t>
+        </is>
+      </c>
+      <c r="H629" t="n">
+        <v>46030</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J629" t="n">
+        <v>1</v>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>4feb97e62e344e87a5caea5494129c31</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>UA-2016-02-23-000367-b</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:44:55.803212+02:00</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Середня загальноосвітня школа № 5 ім. Г. Романової м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>23370343</t>
+        </is>
+      </c>
+      <c r="H630" t="n">
+        <v>117985.61</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>fab9fc2d3a27472cbf68714c16df7137</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000067-b</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:07.378288+02:00</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>КУ "ПАВЛОГРАДСЬКА ЦЕНТРАЛЬНА РАЙОННА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>01988746</t>
+        </is>
+      </c>
+      <c r="H631" t="n">
+        <v>22722</v>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J631" t="n">
+        <v>1</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>15b1f69052324234a9a0bfba4103b431</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000079-b</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.154681+02:00</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>КП "Прилуцький  протитуберкульозний  диспансер"</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>02774131</t>
+        </is>
+      </c>
+      <c r="H632" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J632" t="n">
+        <v>1</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>d3c4fcf47c854625b21862b3ffc788ec</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000082-b</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.622393+02:00</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>КП "Прилуцький  протитуберкульозний  диспансер"</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>02774131</t>
+        </is>
+      </c>
+      <c r="H633" t="n">
+        <v>8750</v>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J633" t="n">
+        <v>1</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>b62142f99a8843bba50f495759dd9d2a</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000083-b</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:10.857855+02:00</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЗАКЛАД "ДНІПРОПЕТРОВСЬКА ОБЛАСНА КЛІНІЧНА ОФТАЛЬМОЛОГІЧНА ЛІКАРНЯ"</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>26508184</t>
+        </is>
+      </c>
+      <c r="H634" t="n">
+        <v>3840</v>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J634" t="n">
+        <v>1</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>b89ac6c626d943c99360c793b4744ac7</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000096-c</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:12.777004+02:00</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>міська лікарня №3</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>04592434</t>
+        </is>
+      </c>
+      <c r="H635" t="n">
+        <v>10985</v>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J635" t="n">
+        <v>1</v>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>8d91eea253c449a0927c7a7c2db5fbf6</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000118-a</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:15.802231+02:00</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Комунальна установа "Запорізький обласний протитуберкульозний клінічний диспансер" Запорізької обласної ради</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>02006707</t>
+        </is>
+      </c>
+      <c r="H636" t="n">
+        <v>18021</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J636" t="n">
+        <v>1</v>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>c7d7acd599354164bca0d8f23bdf029b</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000118-b</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:15.809489+02:00</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Об'эднання ветеринарної медицини в м.Києві</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>00699715</t>
+        </is>
+      </c>
+      <c r="H637" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J637" t="n">
+        <v>1</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>a8de9f0da0704355b7ff5cdcb2ef5fc2</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000123-c</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:18.518631+02:00</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>КЗ "Барська обласна туберкульозна лікарня"</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>33661899</t>
+        </is>
+      </c>
+      <c r="H638" t="n">
+        <v>54400</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J638" t="n">
+        <v>1</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>714effddf0c6477d8cfedc406420615f</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000158-a</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:30.334065+02:00</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Іллічівська філія державного підприємства “Адміністрація морських портів України” (Адміністрація Іллічівського морського порту)</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>38728418</t>
+        </is>
+      </c>
+      <c r="H639" t="n">
+        <v>276600</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J639" t="n">
+        <v>0</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>63d7f5321670467aa86144747a44c1e3</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000169-a</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:33.174466+02:00</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H640" t="n">
+        <v>81830</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J640" t="n">
+        <v>1</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>59aabe9d580340eab7587c3af3a3ab2f</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000222-c</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:37.803795+02:00</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H641" t="n">
+        <v>40915</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J641" t="n">
+        <v>1</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>7ec9a45598ad4e27996751093057eef5</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000275-b</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:41.687156+02:00</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Комунальний заклад "Середня загальноосвітня школа № 6 м.Дніпродзержинська" Дніпродзержинської міської ради "</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>23641799</t>
+        </is>
+      </c>
+      <c r="H642" t="n">
+        <v>2890</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J642" t="n">
+        <v>1</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>7968a39bdd9048d58e076a3fb3242eed</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000343-b</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:44.589637+02:00</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Центр первинної медико-санітарної допомоги №2" Оболонського району міста Києва</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>23379143</t>
+        </is>
+      </c>
+      <c r="H643" t="n">
+        <v>21100</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J643" t="n">
+        <v>1</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>a0b006b976b143fc90afa70fab2db160</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>UA-2016-02-24-000370-b</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:45.515864+02:00</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Відділ освіти Чигиринської районної державної адміністрації</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>02146966</t>
+        </is>
+      </c>
+      <c r="H644" t="n">
+        <v>76244</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J644" t="n">
+        <v>1</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:08:13.700206+00:00</t>
         </is>
       </c>
     </row>
@@ -75033,7 +80983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79144,6 +85094,164 @@
       </c>
       <c r="E156" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>{"bytes": 200822}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:01+00:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:01+00:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:02+00:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:02+00:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:02+00:00</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prozorro-milk.xlsx
+++ b/data/prozorro-milk.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02T05:09:01+00:00</t>
+          <t>2026-02-03T04:58:29+00:00</t>
         </is>
       </c>
     </row>
@@ -488,13 +488,13 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>{
-  "offset": "1478285151.6425.1.abe45aa973287410a8ae353b55af3eda",
-  "updated_at": "2026-02-02T05:09:01.502438+00:00",
-  "pages_done": 575,
-  "tenders_scanned": 57500,
-  "tenders_fetched": 57500,
-  "milk_tenders": 643,
-  "milk_items": 731
+  "offset": "1478285333.976573.1.8bb098b780bc848e1202e0b636d03b87",
+  "updated_at": "2026-02-03T04:58:29.537740+00:00",
+  "pages_done": 600,
+  "tenders_scanned": 60000,
+  "tenders_fetched": 60000,
+  "milk_tenders": 674,
+  "milk_items": 765
 }</t>
         </is>
       </c>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M732"/>
+  <dimension ref="A1:M766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46822,6 +46822,2170 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>dd3898af1fe04d25a659917099b416f7</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>0e92e0bb4b5a43189f496ae95cb1248f</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче сире свіже</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>03333000-4</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>смт. Завалля</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:52.474344+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>ffcfdc07bdf34294ac51f6d1f9b72442</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>126aa126ba4c42d08546e59c47f3b3c8</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>молоко коров’яче 2,6% П/Є фасовка по 0,9 л. сметана 15% П/Є фасовка по 0,4 кг</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F734" t="n">
+        <v>2</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>лот</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>2016-08-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>ніжин</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:02.373639+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>e52c39ff5ef044a589196aae17ba1154</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>c147c6a1d093c5347c1e2ea5dcb5e267</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Молоко згущене 8,5%</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>15511600-9</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F735" t="n">
+        <v>150</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>2016-05-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Запорізька область</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:02.837468+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>8bc6291351cf4314ade66483482f7e5c</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>a1d573aca25ba6ca9f06a75e103ed111</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>сухе молоко</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>15511700-0</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F736" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>місто Балта</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:06.627280+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>86e6125f371145678ca79dc0c3ee18e8</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>719622d9361e4e26bd84284277f94eb9</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Молоко жирністю 2,5% - 400	літрів. Скорочена процедура закупівлі в зв'язку з нагальною потребою для безперебійного лікувального процесу.</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F737" t="n">
+        <v>400</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>2016-03-06T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:07.472364+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>4f873b211bb5419ea83caa55cf913e5a</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>c4ebc1b5314440e0bcbd50bd20fa354b</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче питне пастеризоване, жирність  2,5%, або 2,6%, або 2,7 %,
+фас. в п/е пакети вагою від 900 г до 1000 г</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>2016-03-08T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>2016-08-30T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:13.013884+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>7cd52f8a29e943aab77695f223df4e78</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>a2c8bf1a59ab464abc7b8137f4fa56c1</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>молоко коров'яче питне 3,2% тетрапак</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F739" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Київська обл.</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:18.821026+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>280b0b38943b40e4a830b2e84db85f66</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>21e00d16a11b45b3ba85f1f352bf726e</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Молоко 2,5% жирності. фасоване в п\е плівку по 1,0кг-12800л</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F740" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:19.549489+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>3422f4ca99094f1f96f31d9454bdce55</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>aeecac766af4442babb8ca299b7c992c</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>товар: молоко пастеризоване, жирність 3.2%, упаковка - поліетиленовий пакет, вага 1000 гр., умови поставки: поставка товару партіями, на вимогу замовника, тричі на тиждень. Замовлення через стаціонарний телефон без між міського зв’язку. Прийом товару з 09 до 12 год.</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>15510000-6</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F741" t="n">
+        <v>8683</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>2016-02-29T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr"/>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:21.728234+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>badf6d3a53f2497d82d1bccefdfcac60</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>7ee1ce0ec08b44dbba3e59c469069af6</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване  п/е,2,5%-жиру (1000г), Молоко пастеризоване  п/е,3,2%-жиру (1000г),Сметана 15% жирності</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F742" t="n">
+        <v>9130</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>2016-12-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Полтавская область</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Полтава</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:32.564527+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>812ad59eaf874bc89016aa1615ad5b8e</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>c5f3a8704ec547e4b55c05b7a0a0ea9d</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>молоко рідке</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F743" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Черниговская область</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Халявин</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:33.349551+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>c174a94cb057488081c2f5fb672012ed</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>5437e49a792340989123ae8cd8a859ed</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Молоко сгущене "Полтавочка" ж/б</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F744" t="n">
+        <v>45</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>2016-03-02T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>2016-03-03T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:33.680200+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>a7555c1f3dd84f5aa301fad42d1a6813</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>b39f183b8af24bbeaeec87e0573f999f</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>1 Гель діагностичний для УЗД (ECO SUPERGEL або еквівалент), 5л- 2уп; 2 Гель для ЕКГ (EKG SUPERGEL або еквівалент) , 260г. - 5уп; 3 Крем (гель) для ЕЕГ (EEG SUPERCREAM або еквівалент), 260г - 5уп; 4 Озокерит медичний, 5кг - 2уп; 5 Парафін медичний П2 ГОСТ 23683-89, 5кг - 2уп.</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>24321000-0</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>16</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>упаковка</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:54.180783+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>22b8ca44347c4f8f867b9d556daea2b6</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>8a5251dfcace44d8843bd3f01110511d</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко згущене </t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>15550000-8</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>50</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>2016-03-17T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:03.061887+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>3f8a77d365844090824bf53372e20817</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>6816bb1341fd4582b9a78a4a70d6b804</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Рулет молочний з згущеним молоком із пшеничного борошна вищого сорту, 1/0,80 кг.</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>15811000-6</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>7385</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:14.038649+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>be24c88ebcdd4281904f926d88a46f68</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>722f4f730f004a2fbf265087756b1688</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Молоко пастеризоване, жирністю 2,7%, фасоване у поліетиленовий пакет по 1 л</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>7340</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr"/>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>м.Чернігів</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:16.317154+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2955a191125e48788196f8417da2a12f</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>683b572f2e1e4db0961bf61dfad2b014</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Молоко рідинне 2,5%</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>150</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>2016-03-01T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Одесская область</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Ананьїв</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:21.600777+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>39538eeb204744b2bec3bbb637f22f26</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>9e04f3f0c103efc26db4a2d36726daf2</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>молоко та вершки,рідинні оброблені</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>5032</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Вінницька область</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>м. Хмільник</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:22.494024+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2c7607e1a64d4832bbf9b5696972f53b</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>0df26ccfc8ba4976bb74648419f1a804</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Молоко 1 л.
+Молоко 0,5л</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>літр</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>2016-03-08T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>2016-12-30T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:43.934869+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>0941774c8a1143af8c39e48008191ee2</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>22f7a048a1dc480e8ea97f3b09da30d3</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Масло вершкове, сметана, творог кисломолочний, сир твердий, кефір, молоко свіже</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>205</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>2016-03-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:00.060814+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>61bda0ea83fe41f3978c4734e7ba2e1a</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>0e3ba01ef3b742079a8421de519c6ae5</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Молоко та вершки, рідинні, оброблені 10.51.1, Масло вершкове та молочні пасти 10.51.30., Сир сичужний та кисломолочний сир 10.51.4, Продукти молочні, інші 10.51.5</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>2940</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>пачок</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>2016-03-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>2016-06-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>м.Новомосковськ</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:07.741046+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>035d9cd496c74e78a7cf6e0158f295e9</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>a0934574c88240e9a8fd8c0120b3ec40</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Молоко пастеризоване, жирність не менше 2.5 %, плівка </t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>15511100-4</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>384</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>2016-03-21T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>2016-12-31T23:59:59.999999+02:00</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>м. Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:08.809946+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>44afe8dca0dd44fc9e7d7f0605630af7</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>045426e899f009e5b35813d8304c7a39</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Молоко 2,5 (2,6)% жироності</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>15511000-3</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>500</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>2016-12-31T16:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Одеська область</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>м. Білгород-Дністровський</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:11.380302+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>02e624ad5df24e35baacffde801ad331</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>e836657e0f9046e6b1eda016a1d48c4d</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>1. Олія рослинна (10.41.5) фас.920,00г.(1л.)-10б,
+2. Молоко 2,5 %(10.51.1)--1200,00л,
+3.Сметана21% жиру по 0,450 гр.в пакетах,40,00 пак.,
+4.Крупа манна(10.61.3)---50,00кг,
+5.Крупа ячнева (10.61.3)50,00кг,
+6.Рис(10.61.3)75,00кг,
+7.Пшоно(10.61.3)---50,00кг,
+8.Пластівці вівсяні «Геркулес»(10.61.3)---50,00кг,
+9.Макарони(10.73.1)150,00кг,
+10.Сухофрукти(10.39.2)---70,00кг,
+11.Чай(10.83.1)9,60кгх130,00=1248,00;
+12.Картопля(01.13.5)---1000,00кг,
+13.Цибуля(01.13.4)---70,00кг,
+14. Морква(01.13.4)---120,00кг,
+15.Буряк(01.13.7)---70,00кг,
+16.Яйця(  01.47.2   )—600,00 шт.,
+17.Сіль кухонна ( 10.84.3  )—50,00кг,
+18.Капуста (01.13.1)  80,00кг,
+19.Зелений горошок ( 10.39.1)  36 бан.,
+20.Томатна паста ( 10.39.1 )48 бан.,
+21.Борошно пшеничне в/г.(10.61.2)50,00кг.</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>15890000-3</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:16.851099+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>857947abf76f4ef98aab9b20ef44bfb3</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>83dd6647118a4a1f9e890a387302b96a</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Олія, яйця,борошно, цукор, сіль, крупи, макаронні вироби, дріжджі, чай, кавовий напій, какао, ванілін, повидло, родзинки, згущене молоко, іриска, оцет, сода, лимонна кислота, сік, мак, томат паста, сухарі панірувальні, цукрова пудра</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>2236</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>2016-03-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>2016-05-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Дніпродзержинськ</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:21.822226+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>9f7213e2a17e498e8751b84905b8f886</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>a474b2bb44c897ab9fc905f5a175c1f9</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Молоко згущене варене 500м гр.</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>36</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>с.Макорти</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:22.854842+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>d1f7bdfb97184854bfc6fd093ae40c8e</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>c241a73203c14801985ce1c21bed9d22</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Продукти харчування. ДК 021:2015 (15511000-3) "Молоко" (дитяче, 0,5 л., 5151 шт.); ДК 021:2015 (15321000-4) "Фруктові соки" (дитячі, 0,2 л., 3868 шт.); ДК 021:2015 (15881000-7) "Гомогенізовані продукти харчування" (суміш молочна, 350 гр., 165 шт.). Вимоги до якості товару і кваліфікації учасників - в Додатках №1 і №2 до Закупівлі.
+Постачання і транспортування продукції на склад Замовника здійснюється
+транспортом  постачальника і за рахунок постачальника.
+Дана закупівля передбачає собою  поетапну доставку і оплату товару з 
+відповідною щомісячною розбивкою на період квітень-грудень, 2016 р.</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>9184</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>2016-12-22T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Київська</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:25.080219+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>dbbd1aad917c4fbfab0e7405a0c93562</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>cfd03572fe8c4584b83f2247849cb098</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Згущене молоко (в залізній банці 370 г)</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>150</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>смт. Завалля</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:32.395458+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>dbbd1aad917c4fbfab0e7405a0c93562</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>00e8570a3431453cb91b277338a2fe3a</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Згущене молоко (варене)</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>15500000-3</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>150</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>кілограми</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>2016-03-31T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>2016-06-29T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Кіровоградська</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>смт. Завалля</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:32.395458+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>63205da5723d47ebab6c73f2dbf05641</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>03a995b4e1ec78e0b3ef72924b10ad25</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Молоко вагове незбирене згущене з цукром 8,5%жирності</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>200</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>2016-03-31T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Дніпропетровська область</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>с.Макорти</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:47.088052+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>f0fcaf5e26ad4daeaa6c81fb121906d4</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>02822e67e87a4b0990ecd96b8652dede</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Молоко довгострокове 2,5% жир.</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>240</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>2016-03-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:51.315925+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>f0fcaf5e26ad4daeaa6c81fb121906d4</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>7f95c508e9b848ecbbe8fe5029483540</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Молоко згущене</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>15800000-6</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>148</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>килограммы</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>2016-03-14T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>2016-04-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>м.Першотравенськ</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:51.315925+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>a443196bd34346e18da466c390afe5a2</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>359a456d539344b7951e8b7244e40622</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Молоко коров'яче пастеризоване 2,5%</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>500</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>2016-03-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>2016-09-30T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:53.976573+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>a443196bd34346e18da466c390afe5a2</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>8021f91946d840e691aee5f55ce981ee</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Молоко згущене незбиране з цукром 8,5%, 370г</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>15000000-8</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>155</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>штуки</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>H87</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>2016-03-15T00:00:00+02:00</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>2016-03-31T23:59:59.999999+03:00</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Днепропетровская область</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>м. Дніпропетровськ</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:53.976573+02:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46833,7 +48997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K644"/>
+  <dimension ref="A1:K675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80969,6 +83133,1649 @@
       <c r="K644" t="inlineStr">
         <is>
           <t>2026-02-02T05:08:13.700206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>dd3898af1fe04d25a659917099b416f7</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000042-c</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:45:52.474344+02:00</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>ЗАВАЛЛІВСЬКА ЗАГАЛЬНООСВІТНЯ ШКОЛА-ІНТЕРНАТ I-III СТУПЕНІВ ГАЙВОРОНСЬКОГО РАЙОНУ</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>13761568</t>
+        </is>
+      </c>
+      <c r="H645" t="n">
+        <v>12650</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J645" t="n">
+        <v>1</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>ffcfdc07bdf34294ac51f6d1f9b72442</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000095-b</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:02.373639+02:00</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Ніжинський центр соціально-психологічної реабілітації дітей</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>26543591</t>
+        </is>
+      </c>
+      <c r="H646" t="n">
+        <v>55650</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J646" t="n">
+        <v>1</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>e52c39ff5ef044a589196aae17ba1154</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000098-c</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:02.837468+02:00</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Комунальна установа "Запорізький обласний протитуберкульозний клінічний диспансер" Запорізької обласної ради</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>02006707</t>
+        </is>
+      </c>
+      <c r="H647" t="n">
+        <v>2925</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J647" t="n">
+        <v>1</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>8bc6291351cf4314ade66483482f7e5c</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000126-a</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:06.627280+02:00</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Балтський психоневрологічний будинок-інтернат</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>03189073</t>
+        </is>
+      </c>
+      <c r="H648" t="n">
+        <v>125000</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J648" t="n">
+        <v>1</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>86e6125f371145678ca79dc0c3ee18e8</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000131-c</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:07.472364+02:00</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №7</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>05494840</t>
+        </is>
+      </c>
+      <c r="H649" t="n">
+        <v>5440</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J649" t="n">
+        <v>1</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>4f873b211bb5419ea83caa55cf913e5a</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000151-b</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:13.013884+02:00</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Дошкільний заклад освіти №628 Державного управління справами</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>22864155</t>
+        </is>
+      </c>
+      <c r="H650" t="n">
+        <v>89500</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J650" t="n">
+        <v>1</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>7cd52f8a29e943aab77695f223df4e78</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000198-c</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:18.821026+02:00</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Державне підприємство "Готельний комплекс "Київ" Управління справами Апарату Верховної Ради України"</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>03539018</t>
+        </is>
+      </c>
+      <c r="H651" t="n">
+        <v>62000</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J651" t="n">
+        <v>1</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>280b0b38943b40e4a830b2e84db85f66</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000205-c</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:19.549489+02:00</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №10</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>01993931</t>
+        </is>
+      </c>
+      <c r="H652" t="n">
+        <v>214250</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J652" t="n">
+        <v>1</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>3422f4ca99094f1f96f31d9454bdce55</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000232-c</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:21.728234+02:00</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Дарницький дитячий будинок-інтернат</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>03188808</t>
+        </is>
+      </c>
+      <c r="H653" t="n">
+        <v>91171</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J653" t="n">
+        <v>1</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>badf6d3a53f2497d82d1bccefdfcac60</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000262-b</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:32.564527+02:00</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>КУ "ДИТЯЧА МІСЬКА КЛІНІЧНА ЛІКАРНЯ м. ПОЛТАВИ"</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>01999684</t>
+        </is>
+      </c>
+      <c r="H654" t="n">
+        <v>131400</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J654" t="n">
+        <v>1</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>812ad59eaf874bc89016aa1615ad5b8e</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000272-b</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:33.349551+02:00</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>КП "КЛПЗ Чернігівська обласна психоневрологічна лікарня"</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>02006076</t>
+        </is>
+      </c>
+      <c r="H655" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J655" t="n">
+        <v>1</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>c174a94cb057488081c2f5fb672012ed</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>UA-2016-02-25-000280-b</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:33.680200+02:00</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровський професійний залізничний ліцей "</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>05536107</t>
+        </is>
+      </c>
+      <c r="H656" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J656" t="n">
+        <v>1</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>a7555c1f3dd84f5aa301fad42d1a6813</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>UA-2016-02-26-000071-b</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:46:54.180783+02:00</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>КУ "Дніпропетровська клінічна психіатрична лікарня Дніпропетровської обласної ради"</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>01985400</t>
+        </is>
+      </c>
+      <c r="H657" t="n">
+        <v>1886</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J657" t="n">
+        <v>1</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>22b8ca44347c4f8f867b9d556daea2b6</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>UA-2016-02-26-000120-b</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:03.061887+02:00</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>ДП "Дніпропетровське вище професійне училище будівництва"</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>02541361</t>
+        </is>
+      </c>
+      <c r="H658" t="n">
+        <v>933</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J658" t="n">
+        <v>1</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>3f8a77d365844090824bf53372e20817</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>UA-2016-02-26-000198-b</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:14.038649+02:00</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Комунальний заклад Дніпродзержинська міська лікарня №5 Дніпропетровської обласної ради</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>01985831</t>
+        </is>
+      </c>
+      <c r="H659" t="n">
+        <v>91024.03999999999</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J659" t="n">
+        <v>1</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>be24c88ebcdd4281904f926d88a46f68</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>UA-2016-02-26-000251-b</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:16.317154+02:00</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>КОМУНАЛЬНИЙ ЛІКУВАЛЬНО-ПРОФІЛАКТИЧНИЙ ЗАКЛАД "ЧЕРНІГІВСЬКИЙ ОБЛАСНИЙ ГОСПІТАЛЬ ВЕТЕРАНІВ ВІЙНИ"</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>26211473</t>
+        </is>
+      </c>
+      <c r="H660" t="n">
+        <v>69730</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J660" t="n">
+        <v>1</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2955a191125e48788196f8417da2a12f</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>UA-2016-02-26-000331-b</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:21.600777+02:00</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Ананьївський дитячий будинок-інтернат</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>03190604</t>
+        </is>
+      </c>
+      <c r="H661" t="n">
+        <v>1824</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J661" t="n">
+        <v>1</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>39538eeb204744b2bec3bbb637f22f26</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>UA-2016-02-27-000001-a</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:22.494024+02:00</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>КУ "Хмільницька центральна районна лікарня"</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>01982695</t>
+        </is>
+      </c>
+      <c r="H662" t="n">
+        <v>36971</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J662" t="n">
+        <v>1</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2c7607e1a64d4832bbf9b5696972f53b</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>UA-2016-02-29-000074-a</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:47:43.934869+02:00</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Київська міська клінічна лікарня №12</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>25680639</t>
+        </is>
+      </c>
+      <c r="H663" t="n">
+        <v>126000</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J663" t="n">
+        <v>1</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>0941774c8a1143af8c39e48008191ee2</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>UA-2016-02-29-000166-c</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:00.060814+02:00</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>КЗ "Середня загальноосвітня школа №31 з класами вечірньої форми навчання м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>23642161</t>
+        </is>
+      </c>
+      <c r="H664" t="n">
+        <v>12351</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J664" t="n">
+        <v>0</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>61bda0ea83fe41f3978c4734e7ba2e1a</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>UA-2016-02-29-000232-c</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:07.741046+02:00</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>КУ "НОВОМОСКОВСЬКА ЦЕНТРАЛЬНА РАЙОННА ЛІКАРНЯ" ДНІПРОПЕТРОВСЬКОЇ ОБЛАСНОЇ РАДИ"</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>26137707</t>
+        </is>
+      </c>
+      <c r="H665" t="n">
+        <v>40350</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J665" t="n">
+        <v>1</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>035d9cd496c74e78a7cf6e0158f295e9</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>UA-2016-02-29-000262-c</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:08.809946+02:00</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>ОКЗ Криворізький шкірно-венерологічний диспансер</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>01986210</t>
+        </is>
+      </c>
+      <c r="H666" t="n">
+        <v>16858.5</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J666" t="n">
+        <v>1</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>44afe8dca0dd44fc9e7d7f0605630af7</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000014-b</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:11.380302+02:00</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>КУ "Обласний протитуберкульозний диспансер № 2"</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>05446545</t>
+        </is>
+      </c>
+      <c r="H667" t="n">
+        <v>14800</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J667" t="n">
+        <v>1</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>02e624ad5df24e35baacffde801ad331</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000042-a</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:16.851099+02:00</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>active.awarded</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Київський міський пологовий будинок № 1</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>01993859</t>
+        </is>
+      </c>
+      <c r="H668" t="n">
+        <v>32300</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J668" t="n">
+        <v>0</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>857947abf76f4ef98aab9b20ef44bfb3</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000066-c</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:21.822226+02:00</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>КЗ "Середня загальноосвітня школа №31 з класами вечірньої форми навчання м. Дніпродзержинська" Дніпродзержинської міської ради</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>23642161</t>
+        </is>
+      </c>
+      <c r="H669" t="n">
+        <v>25665</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>9f7213e2a17e498e8751b84905b8f886</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000071-b</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:22.854842+02:00</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Софіївська виправна  колонія (№45)</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>08562973</t>
+        </is>
+      </c>
+      <c r="H670" t="n">
+        <v>66000</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J670" t="n">
+        <v>1</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>d1f7bdfb97184854bfc6fd093ae40c8e</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000090-a</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:25.080219+02:00</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Комунальне некомерційне підприємство "Центр первинної медико - санітарної допомоги № 3 Дарницького району м. Києва"</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>30300749</t>
+        </is>
+      </c>
+      <c r="H671" t="n">
+        <v>95990</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J671" t="n">
+        <v>1</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>dbbd1aad917c4fbfab0e7405a0c93562</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000131-a</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:32.395458+02:00</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>ЗАВАЛЛІВСЬКА ЗАГАЛЬНООСВІТНЯ ШКОЛА-ІНТЕРНАТ I-III СТУПЕНІВ ГАЙВОРОНСЬКОГО РАЙОНУ</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>13761568</t>
+        </is>
+      </c>
+      <c r="H672" t="n">
+        <v>32160</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J672" t="n">
+        <v>1</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>63205da5723d47ebab6c73f2dbf05641</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000183-b</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:47.088052+02:00</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>unsuccessful</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Софіївська виправна  колонія (№45)</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>08562973</t>
+        </is>
+      </c>
+      <c r="H673" t="n">
+        <v>6480</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J673" t="n">
+        <v>1</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>f0fcaf5e26ad4daeaa6c81fb121906d4</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000263-c</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:51.315925+02:00</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>КУ "Першотравенська загальноосвітня спеціальна школа-інтернат"</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>20250549</t>
+        </is>
+      </c>
+      <c r="H674" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J674" t="n">
+        <v>1</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>a443196bd34346e18da466c390afe5a2</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>UA-2016-03-01-000316-c</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2016-11-04T20:48:53.976573+02:00</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>belowThreshold</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Професійно-технічне училище № 6</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>02541378</t>
+        </is>
+      </c>
+      <c r="H675" t="n">
+        <v>32691.5</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="J675" t="n">
+        <v>1</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:57:49.262251+00:00</t>
         </is>
       </c>
     </row>
@@ -80983,7 +84790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85252,6 +89059,164 @@
       </c>
       <c r="E162" t="inlineStr"/>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:09:02+00:00</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>XLSX export done</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>{"bytes": 222070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:58:29+00:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Start XLSX export</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>{"db": "data/prozorro_milk.sqlite", "xlsx": "data/prozorro-milk.xlsx"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:58:29+00:00</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Discovered tables</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>{"tables": ["milk_items", "milk_tenders"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:58:30+00:00</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>{"table": "milk_items"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:58:30+00:00</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Export table</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>{"table": "milk_tenders"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-02-03T04:58:30+00:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Attach logs sheet</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
